--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc1839e5dfca2ccd/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{60C074BA-9212-4351-BDA2-AD1946ADFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1078,11 +1078,11 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1879,7 +1879,7 @@
         <f>HYPERLINK("https://my.payos.vn/", "🔗 Pay_os")</f>
         <v>🔗 Pay_os</v>
       </c>
-      <c r="B7" s="25" t="e" vm="1">
+      <c r="B7" s="26" t="e" vm="1">
         <f>_xlfn.IMAGE(B5)</f>
         <v>#VALUE!</v>
       </c>
@@ -1913,7 +1913,7 @@
         <f>HYPERLINK("https://my.vietqr.io/", "🔗 Template")</f>
         <v>🔗 Template</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="9" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="11"/>
-      <c r="B9" s="26"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="10" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2"/>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="11" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2"/>
-      <c r="B11" s="26"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="12" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2"/>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2"/>
-      <c r="B13" s="26"/>
+      <c r="B13" s="27"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="14" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2"/>
-      <c r="B14" s="26"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="15" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2"/>
-      <c r="B15" s="26"/>
+      <c r="B15" s="27"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="16" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2"/>
-      <c r="B16" s="26"/>
+      <c r="B16" s="27"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="17" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2"/>
-      <c r="B17" s="26"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="18" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2"/>
-      <c r="B18" s="26"/>
+      <c r="B18" s="27"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="19" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="2"/>
-      <c r="B19" s="26"/>
+      <c r="B19" s="27"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="20" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="2"/>
-      <c r="B20" s="26"/>
+      <c r="B20" s="27"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -32928,7 +32928,7 @@
       <c r="G6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="25" t="s">
         <v>256</v>
       </c>
     </row>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc1839e5dfca2ccd/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60C074BA-9212-4351-BDA2-AD1946ADFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7945384-786B-4823-BB04-B02BDA59EEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viet_qr_Gsheet" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="259">
   <si>
     <t>BIN</t>
   </si>
@@ -829,6 +829,12 @@
   <si>
     <t>qr_only</t>
   </si>
+  <si>
+    <t>name_ac</t>
+  </si>
+  <si>
+    <t>Huynh Tran Tuan Kiet</t>
+  </si>
 </sst>
 </file>
 
@@ -1078,16 +1084,19 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1325,16 +1334,16 @@
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="API-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="18"/>
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="19"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="firstRowStripe" dxfId="17"/>
+      <tableStyleElement type="secondRowStripe" dxfId="16"/>
     </tableStyle>
     <tableStyle name="Trang tính1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="14"/>
-      <tableStyleElement type="headerRow" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="secondRowStripe" dxfId="11"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1401,7 +1410,6 @@
 <webImagesSrd xmlns="http://schemas.microsoft.com/office/spreadsheetml/2020/richdatawebimage" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <webImageSrd>
     <address r:id="rId1"/>
-    <blip r:id="rId2"/>
   </webImageSrd>
 </webImagesSrd>
 </file>
@@ -1429,28 +1437,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7F0749FA-984C-46C9-AAB8-7ABB595D4FB8}" name="Table1" displayName="Table1" ref="A1:I101" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I101" xr:uid="{7F0749FA-984C-46C9-AAB8-7ABB595D4FB8}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F8D53C57-7078-4EF6-9C73-35B4D8C4988B}" name="data__id" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{390DCB3F-4D6D-4198-B590-711049680796}" name="list_name" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{576DFB3C-BE82-459C-804A-245AC638C8B8}" name="data_num" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{2B86B3E1-90A9-4410-87A1-76EA940DC021}" name="data__name" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7F0749FA-984C-46C9-AAB8-7ABB595D4FB8}" name="Table1" displayName="Table1" ref="A1:J101" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J101" xr:uid="{7F0749FA-984C-46C9-AAB8-7ABB595D4FB8}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{F8D53C57-7078-4EF6-9C73-35B4D8C4988B}" name="data__id" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{390DCB3F-4D6D-4198-B590-711049680796}" name="list_name" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{576DFB3C-BE82-459C-804A-245AC638C8B8}" name="data_num" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{A98793EC-C017-48A1-96BE-B60CD452DAC7}" name="name_ac" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{2B86B3E1-90A9-4410-87A1-76EA940DC021}" name="data__name" dataDxfId="6">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,2,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D4B6D36E-F5B4-4050-84DA-B62E678E55BF}" name="data__code" dataDxfId="4">
+    <tableColumn id="4" xr3:uid="{D4B6D36E-F5B4-4050-84DA-B62E678E55BF}" name="data__code" dataDxfId="5">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,3,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F102E323-9AC5-4420-B847-1C14F7757293}" name="data__bin" dataDxfId="3">
+    <tableColumn id="5" xr3:uid="{F102E323-9AC5-4420-B847-1C14F7757293}" name="data__bin" dataDxfId="4">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DB8F4E18-D2FD-4EA2-B28D-DA53D8A12D89}" name="data__shortName" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{DB8F4E18-D2FD-4EA2-B28D-DA53D8A12D89}" name="data__shortName" dataDxfId="3">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{EA429D0C-4231-435B-91FE-DAD0B13369DF}" name="data__logo" dataDxfId="1">
+    <tableColumn id="7" xr3:uid="{EA429D0C-4231-435B-91FE-DAD0B13369DF}" name="data__logo" dataDxfId="2">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BD47F35F-8B5D-4304-BED9-AA9B06C54ACA}" name="data__short_name" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{BD47F35F-8B5D-4304-BED9-AA9B06C54ACA}" name="data__short_name" dataDxfId="1">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1688,7 +1697,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>13</v>
       </c>
       <c r="B1" s="23">
         <v>25000</v>
@@ -1721,9 +1730,9 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5">
-        <f>+VLOOKUP($A$1,List_bank!$B:$F,5,0)</f>
-        <v>970407</v>
+      <c r="B2" s="5" t="str">
+        <f>+VLOOKUP($A$1,List_bank!$B:$G,5,0)</f>
+        <v>ACB</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1753,8 +1762,8 @@
         <v>1</v>
       </c>
       <c r="B3" s="5">
-        <f>+VLOOKUP($A$1,List_bank!$B:$F,2,0)</f>
-        <v>44699999999</v>
+        <f>+VLOOKUP($A$1,List_bank!$B:$G,2,0)</f>
+        <v>81051</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1816,7 +1825,7 @@
       </c>
       <c r="B5" s="7" t="str">
         <f>"https://img.vietqr.io/image/"&amp;B2&amp;"-"&amp;B3&amp;"-"&amp;B4&amp;".png?amount="&amp;B1&amp;""</f>
-        <v>https://img.vietqr.io/image/970407-44699999999-BdT8CDO.png?amount=25000</v>
+        <v>https://img.vietqr.io/image/ACB-81051-BdT8CDO.png?amount=25000</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1879,8 +1888,8 @@
         <f>HYPERLINK("https://my.payos.vn/", "🔗 Pay_os")</f>
         <v>🔗 Pay_os</v>
       </c>
-      <c r="B7" s="25" t="e" vm="1">
-        <f>_xlfn.IMAGE(B5)</f>
+      <c r="B7" s="26" t="e" vm="1">
+        <f ca="1">_xlfn.IMAGE(B5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="C7" s="2"/>
@@ -1913,7 +1922,7 @@
         <f>HYPERLINK("https://my.vietqr.io/", "🔗 Template")</f>
         <v>🔗 Template</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1941,7 +1950,7 @@
     </row>
     <row r="9" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="11"/>
-      <c r="B9" s="26"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1969,7 +1978,7 @@
     </row>
     <row r="10" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2"/>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1997,7 +2006,7 @@
     </row>
     <row r="11" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2"/>
-      <c r="B11" s="26"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2025,7 +2034,7 @@
     </row>
     <row r="12" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2"/>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -2053,7 +2062,7 @@
     </row>
     <row r="13" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2"/>
-      <c r="B13" s="26"/>
+      <c r="B13" s="27"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -2081,7 +2090,7 @@
     </row>
     <row r="14" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2"/>
-      <c r="B14" s="26"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -2109,7 +2118,7 @@
     </row>
     <row r="15" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2"/>
-      <c r="B15" s="26"/>
+      <c r="B15" s="27"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -2137,7 +2146,7 @@
     </row>
     <row r="16" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2"/>
-      <c r="B16" s="26"/>
+      <c r="B16" s="27"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -2165,7 +2174,7 @@
     </row>
     <row r="17" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2"/>
-      <c r="B17" s="26"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -2193,7 +2202,7 @@
     </row>
     <row r="18" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2"/>
-      <c r="B18" s="26"/>
+      <c r="B18" s="27"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -2221,7 +2230,7 @@
     </row>
     <row r="19" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="2"/>
-      <c r="B19" s="26"/>
+      <c r="B19" s="27"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -2249,7 +2258,7 @@
     </row>
     <row r="20" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="2"/>
-      <c r="B20" s="26"/>
+      <c r="B20" s="27"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -29689,21 +29698,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5594F79D-0025-4BD8-87B0-D6778D468807}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="72" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="39" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="17" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="17" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>3</v>
       </c>
@@ -29713,26 +29723,29 @@
       <c r="C1" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -29742,32 +29755,35 @@
       <c r="C2" s="19">
         <v>81051</v>
       </c>
-      <c r="D2" s="19" t="str">
+      <c r="D2" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="19" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,2,0)),"-")</f>
         <v>Ngân hàng TMCP Á Châu</v>
       </c>
-      <c r="E2" s="19" t="str">
+      <c r="F2" s="19" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,3,0)),"-")</f>
         <v>ACB</v>
       </c>
-      <c r="F2" s="19">
+      <c r="G2" s="19">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
         <v>970416</v>
       </c>
-      <c r="G2" s="19" t="str">
+      <c r="H2" s="19" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</f>
         <v>ACB</v>
       </c>
-      <c r="H2" s="20" t="str">
+      <c r="I2" s="20" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</f>
         <v>https://cdn.vietqr.io/img/ACB.png</v>
       </c>
-      <c r="I2" s="19" t="str">
+      <c r="J2" s="19" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</f>
         <v>ACB</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
         <v>38</v>
       </c>
@@ -29777,2980 +29793,3081 @@
       <c r="C3" s="21">
         <v>44699999999</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" s="19" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,2,0)),"-")</f>
         <v>Ngân hàng TMCP Kỹ thương Việt Nam</v>
       </c>
-      <c r="E3" s="19" t="str">
+      <c r="F3" s="19" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,3,0)),"-")</f>
         <v>TCB</v>
       </c>
-      <c r="F3" s="19">
+      <c r="G3" s="19">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
         <v>970407</v>
       </c>
-      <c r="G3" s="19" t="str">
+      <c r="H3" s="19" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,5,0)),"-")</f>
         <v>Techcombank</v>
       </c>
-      <c r="H3" s="20" t="str">
+      <c r="I3" s="20" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,6,0)),"-")</f>
         <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
-      <c r="I3" s="19" t="str">
+      <c r="J3" s="19" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,7,0)),"-")</f>
         <v>Techcombank</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
-      <c r="D4" s="19" t="str">
+      <c r="D4" s="22"/>
+      <c r="E4" s="19" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E4" s="19" t="str">
+      <c r="F4" s="19" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F4" s="19" t="str">
+      <c r="G4" s="19" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G4" s="19" t="str">
+      <c r="H4" s="19" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H4" s="20" t="str">
+      <c r="I4" s="20" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I4" s="19" t="str">
+      <c r="J4" s="19" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
-      <c r="D5" s="19" t="str">
+      <c r="D5" s="19"/>
+      <c r="E5" s="19" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E5" s="19" t="str">
+      <c r="F5" s="19" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F5" s="19" t="str">
+      <c r="G5" s="19" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G5" s="19" t="str">
+      <c r="H5" s="19" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H5" s="20" t="str">
+      <c r="I5" s="20" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I5" s="19" t="str">
+      <c r="J5" s="19" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
-      <c r="D6" s="19" t="str">
+      <c r="D6" s="19"/>
+      <c r="E6" s="19" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="19" t="str">
+      <c r="F6" s="19" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F6" s="19" t="str">
+      <c r="G6" s="19" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G6" s="19" t="str">
+      <c r="H6" s="19" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H6" s="20" t="str">
+      <c r="I6" s="20" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I6" s="19" t="str">
+      <c r="J6" s="19" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19"/>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
-      <c r="D7" s="19" t="str">
+      <c r="D7" s="19"/>
+      <c r="E7" s="19" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E7" s="19" t="str">
+      <c r="F7" s="19" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F7" s="19" t="str">
+      <c r="G7" s="19" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G7" s="19" t="str">
+      <c r="H7" s="19" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H7" s="20" t="str">
+      <c r="I7" s="20" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I7" s="19" t="str">
+      <c r="J7" s="19" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
-      <c r="D8" s="19" t="str">
+      <c r="D8" s="19"/>
+      <c r="E8" s="19" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E8" s="19" t="str">
+      <c r="F8" s="19" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F8" s="19" t="str">
+      <c r="G8" s="19" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G8" s="19" t="str">
+      <c r="H8" s="19" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H8" s="20" t="str">
+      <c r="I8" s="20" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I8" s="19" t="str">
+      <c r="J8" s="19" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
-      <c r="D9" s="19" t="str">
+      <c r="D9" s="19"/>
+      <c r="E9" s="19" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E9" s="19" t="str">
+      <c r="F9" s="19" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F9" s="19" t="str">
+      <c r="G9" s="19" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G9" s="19" t="str">
+      <c r="H9" s="19" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H9" s="20" t="str">
+      <c r="I9" s="20" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I9" s="19" t="str">
+      <c r="J9" s="19" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
-      <c r="D10" s="19" t="str">
+      <c r="D10" s="19"/>
+      <c r="E10" s="19" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E10" s="19" t="str">
+      <c r="F10" s="19" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F10" s="19" t="str">
+      <c r="G10" s="19" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G10" s="19" t="str">
+      <c r="H10" s="19" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H10" s="20" t="str">
+      <c r="I10" s="20" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I10" s="19" t="str">
+      <c r="J10" s="19" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19"/>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
-      <c r="D11" s="19" t="str">
+      <c r="D11" s="19"/>
+      <c r="E11" s="19" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E11" s="19" t="str">
+      <c r="F11" s="19" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F11" s="19" t="str">
+      <c r="G11" s="19" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G11" s="19" t="str">
+      <c r="H11" s="19" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H11" s="20" t="str">
+      <c r="I11" s="20" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I11" s="19" t="str">
+      <c r="J11" s="19" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
-      <c r="D12" s="19" t="str">
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="str">
         <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E12" s="19" t="str">
+      <c r="F12" s="19" t="str">
         <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F12" s="19" t="str">
+      <c r="G12" s="19" t="str">
         <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G12" s="19" t="str">
+      <c r="H12" s="19" t="str">
         <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H12" s="20" t="str">
+      <c r="I12" s="20" t="str">
         <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I12" s="19" t="str">
+      <c r="J12" s="19" t="str">
         <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
-      <c r="D13" s="19" t="str">
+      <c r="D13" s="19"/>
+      <c r="E13" s="19" t="str">
         <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E13" s="19" t="str">
+      <c r="F13" s="19" t="str">
         <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F13" s="19" t="str">
+      <c r="G13" s="19" t="str">
         <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G13" s="19" t="str">
+      <c r="H13" s="19" t="str">
         <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H13" s="20" t="str">
+      <c r="I13" s="20" t="str">
         <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I13" s="19" t="str">
+      <c r="J13" s="19" t="str">
         <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
-      <c r="D14" s="19" t="str">
+      <c r="D14" s="19"/>
+      <c r="E14" s="19" t="str">
         <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E14" s="19" t="str">
+      <c r="F14" s="19" t="str">
         <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F14" s="19" t="str">
+      <c r="G14" s="19" t="str">
         <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G14" s="19" t="str">
+      <c r="H14" s="19" t="str">
         <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H14" s="20" t="str">
+      <c r="I14" s="20" t="str">
         <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I14" s="19" t="str">
+      <c r="J14" s="19" t="str">
         <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19"/>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
-      <c r="D15" s="19" t="str">
+      <c r="D15" s="19"/>
+      <c r="E15" s="19" t="str">
         <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E15" s="19" t="str">
+      <c r="F15" s="19" t="str">
         <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F15" s="19" t="str">
+      <c r="G15" s="19" t="str">
         <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G15" s="19" t="str">
+      <c r="H15" s="19" t="str">
         <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H15" s="20" t="str">
+      <c r="I15" s="20" t="str">
         <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I15" s="19" t="str">
+      <c r="J15" s="19" t="str">
         <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="19" t="str">
+      <c r="D16" s="22"/>
+      <c r="E16" s="19" t="str">
         <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E16" s="19" t="str">
+      <c r="F16" s="19" t="str">
         <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F16" s="19" t="str">
+      <c r="G16" s="19" t="str">
         <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G16" s="19" t="str">
+      <c r="H16" s="19" t="str">
         <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H16" s="20" t="str">
+      <c r="I16" s="20" t="str">
         <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I16" s="19" t="str">
+      <c r="J16" s="19" t="str">
         <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="19" t="str">
+      <c r="D17" s="22"/>
+      <c r="E17" s="19" t="str">
         <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E17" s="19" t="str">
+      <c r="F17" s="19" t="str">
         <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F17" s="19" t="str">
+      <c r="G17" s="19" t="str">
         <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G17" s="19" t="str">
+      <c r="H17" s="19" t="str">
         <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H17" s="20" t="str">
+      <c r="I17" s="20" t="str">
         <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I17" s="19" t="str">
+      <c r="J17" s="19" t="str">
         <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="22"/>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="19" t="str">
+      <c r="D18" s="22"/>
+      <c r="E18" s="19" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E18" s="19" t="str">
+      <c r="F18" s="19" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F18" s="19" t="str">
+      <c r="G18" s="19" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G18" s="19" t="str">
+      <c r="H18" s="19" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H18" s="20" t="str">
+      <c r="I18" s="20" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I18" s="19" t="str">
+      <c r="J18" s="19" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
-      <c r="D19" s="19" t="str">
+      <c r="D19" s="22"/>
+      <c r="E19" s="19" t="str">
         <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E19" s="19" t="str">
+      <c r="F19" s="19" t="str">
         <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F19" s="19" t="str">
+      <c r="G19" s="19" t="str">
         <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G19" s="19" t="str">
+      <c r="H19" s="19" t="str">
         <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H19" s="20" t="str">
+      <c r="I19" s="20" t="str">
         <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I19" s="19" t="str">
+      <c r="J19" s="19" t="str">
         <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="19" t="str">
+      <c r="D20" s="22"/>
+      <c r="E20" s="19" t="str">
         <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E20" s="19" t="str">
+      <c r="F20" s="19" t="str">
         <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F20" s="19" t="str">
+      <c r="G20" s="19" t="str">
         <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G20" s="19" t="str">
+      <c r="H20" s="19" t="str">
         <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H20" s="20" t="str">
+      <c r="I20" s="20" t="str">
         <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I20" s="19" t="str">
+      <c r="J20" s="19" t="str">
         <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="19" t="str">
+      <c r="D21" s="22"/>
+      <c r="E21" s="19" t="str">
         <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E21" s="19" t="str">
+      <c r="F21" s="19" t="str">
         <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F21" s="19" t="str">
+      <c r="G21" s="19" t="str">
         <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G21" s="19" t="str">
+      <c r="H21" s="19" t="str">
         <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H21" s="20" t="str">
+      <c r="I21" s="20" t="str">
         <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I21" s="19" t="str">
+      <c r="J21" s="19" t="str">
         <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="19" t="str">
+      <c r="D22" s="22"/>
+      <c r="E22" s="19" t="str">
         <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E22" s="19" t="str">
+      <c r="F22" s="19" t="str">
         <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F22" s="19" t="str">
+      <c r="G22" s="19" t="str">
         <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G22" s="19" t="str">
+      <c r="H22" s="19" t="str">
         <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H22" s="20" t="str">
+      <c r="I22" s="20" t="str">
         <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I22" s="19" t="str">
+      <c r="J22" s="19" t="str">
         <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
-      <c r="D23" s="19" t="str">
+      <c r="D23" s="22"/>
+      <c r="E23" s="19" t="str">
         <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E23" s="19" t="str">
+      <c r="F23" s="19" t="str">
         <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F23" s="19" t="str">
+      <c r="G23" s="19" t="str">
         <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G23" s="19" t="str">
+      <c r="H23" s="19" t="str">
         <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H23" s="20" t="str">
+      <c r="I23" s="20" t="str">
         <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I23" s="19" t="str">
+      <c r="J23" s="19" t="str">
         <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="19" t="str">
+      <c r="D24" s="22"/>
+      <c r="E24" s="19" t="str">
         <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E24" s="19" t="str">
+      <c r="F24" s="19" t="str">
         <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F24" s="19" t="str">
+      <c r="G24" s="19" t="str">
         <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G24" s="19" t="str">
+      <c r="H24" s="19" t="str">
         <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H24" s="20" t="str">
+      <c r="I24" s="20" t="str">
         <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I24" s="19" t="str">
+      <c r="J24" s="19" t="str">
         <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
-      <c r="D25" s="19" t="str">
+      <c r="D25" s="22"/>
+      <c r="E25" s="19" t="str">
         <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E25" s="19" t="str">
+      <c r="F25" s="19" t="str">
         <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F25" s="19" t="str">
+      <c r="G25" s="19" t="str">
         <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G25" s="19" t="str">
+      <c r="H25" s="19" t="str">
         <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H25" s="20" t="str">
+      <c r="I25" s="20" t="str">
         <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I25" s="19" t="str">
+      <c r="J25" s="19" t="str">
         <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
-      <c r="D26" s="19" t="str">
+      <c r="D26" s="22"/>
+      <c r="E26" s="19" t="str">
         <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E26" s="19" t="str">
+      <c r="F26" s="19" t="str">
         <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F26" s="19" t="str">
+      <c r="G26" s="19" t="str">
         <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G26" s="19" t="str">
+      <c r="H26" s="19" t="str">
         <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H26" s="20" t="str">
+      <c r="I26" s="20" t="str">
         <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I26" s="19" t="str">
+      <c r="J26" s="19" t="str">
         <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="22"/>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
-      <c r="D27" s="19" t="str">
+      <c r="D27" s="22"/>
+      <c r="E27" s="19" t="str">
         <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E27" s="19" t="str">
+      <c r="F27" s="19" t="str">
         <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F27" s="19" t="str">
+      <c r="G27" s="19" t="str">
         <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G27" s="19" t="str">
+      <c r="H27" s="19" t="str">
         <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H27" s="20" t="str">
+      <c r="I27" s="20" t="str">
         <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I27" s="19" t="str">
+      <c r="J27" s="19" t="str">
         <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
-      <c r="D28" s="19" t="str">
+      <c r="D28" s="22"/>
+      <c r="E28" s="19" t="str">
         <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E28" s="19" t="str">
+      <c r="F28" s="19" t="str">
         <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F28" s="19" t="str">
+      <c r="G28" s="19" t="str">
         <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G28" s="19" t="str">
+      <c r="H28" s="19" t="str">
         <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H28" s="20" t="str">
+      <c r="I28" s="20" t="str">
         <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I28" s="19" t="str">
+      <c r="J28" s="19" t="str">
         <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
-      <c r="D29" s="19" t="str">
+      <c r="D29" s="22"/>
+      <c r="E29" s="19" t="str">
         <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E29" s="19" t="str">
+      <c r="F29" s="19" t="str">
         <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F29" s="19" t="str">
+      <c r="G29" s="19" t="str">
         <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G29" s="19" t="str">
+      <c r="H29" s="19" t="str">
         <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H29" s="20" t="str">
+      <c r="I29" s="20" t="str">
         <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I29" s="19" t="str">
+      <c r="J29" s="19" t="str">
         <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="19" t="str">
+      <c r="D30" s="22"/>
+      <c r="E30" s="19" t="str">
         <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E30" s="19" t="str">
+      <c r="F30" s="19" t="str">
         <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F30" s="19" t="str">
+      <c r="G30" s="19" t="str">
         <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G30" s="19" t="str">
+      <c r="H30" s="19" t="str">
         <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H30" s="20" t="str">
+      <c r="I30" s="20" t="str">
         <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I30" s="19" t="str">
+      <c r="J30" s="19" t="str">
         <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="19" t="str">
+      <c r="D31" s="22"/>
+      <c r="E31" s="19" t="str">
         <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E31" s="19" t="str">
+      <c r="F31" s="19" t="str">
         <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F31" s="19" t="str">
+      <c r="G31" s="19" t="str">
         <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G31" s="19" t="str">
+      <c r="H31" s="19" t="str">
         <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H31" s="20" t="str">
+      <c r="I31" s="20" t="str">
         <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I31" s="19" t="str">
+      <c r="J31" s="19" t="str">
         <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="19" t="str">
+      <c r="D32" s="22"/>
+      <c r="E32" s="19" t="str">
         <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E32" s="19" t="str">
+      <c r="F32" s="19" t="str">
         <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F32" s="19" t="str">
+      <c r="G32" s="19" t="str">
         <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G32" s="19" t="str">
+      <c r="H32" s="19" t="str">
         <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H32" s="20" t="str">
+      <c r="I32" s="20" t="str">
         <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I32" s="19" t="str">
+      <c r="J32" s="19" t="str">
         <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="19" t="str">
+      <c r="D33" s="22"/>
+      <c r="E33" s="19" t="str">
         <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E33" s="19" t="str">
+      <c r="F33" s="19" t="str">
         <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F33" s="19" t="str">
+      <c r="G33" s="19" t="str">
         <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G33" s="19" t="str">
+      <c r="H33" s="19" t="str">
         <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H33" s="20" t="str">
+      <c r="I33" s="20" t="str">
         <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I33" s="19" t="str">
+      <c r="J33" s="19" t="str">
         <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="19" t="str">
+      <c r="D34" s="22"/>
+      <c r="E34" s="19" t="str">
         <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E34" s="19" t="str">
+      <c r="F34" s="19" t="str">
         <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F34" s="19" t="str">
+      <c r="G34" s="19" t="str">
         <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G34" s="19" t="str">
+      <c r="H34" s="19" t="str">
         <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H34" s="20" t="str">
+      <c r="I34" s="20" t="str">
         <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I34" s="19" t="str">
+      <c r="J34" s="19" t="str">
         <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="19" t="str">
+      <c r="D35" s="22"/>
+      <c r="E35" s="19" t="str">
         <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E35" s="19" t="str">
+      <c r="F35" s="19" t="str">
         <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F35" s="19" t="str">
+      <c r="G35" s="19" t="str">
         <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G35" s="19" t="str">
+      <c r="H35" s="19" t="str">
         <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H35" s="20" t="str">
+      <c r="I35" s="20" t="str">
         <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I35" s="19" t="str">
+      <c r="J35" s="19" t="str">
         <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="22"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="19" t="str">
+      <c r="D36" s="22"/>
+      <c r="E36" s="19" t="str">
         <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E36" s="19" t="str">
+      <c r="F36" s="19" t="str">
         <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F36" s="19" t="str">
+      <c r="G36" s="19" t="str">
         <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G36" s="19" t="str">
+      <c r="H36" s="19" t="str">
         <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H36" s="20" t="str">
+      <c r="I36" s="20" t="str">
         <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I36" s="19" t="str">
+      <c r="J36" s="19" t="str">
         <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="22"/>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="19" t="str">
+      <c r="D37" s="22"/>
+      <c r="E37" s="19" t="str">
         <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E37" s="19" t="str">
+      <c r="F37" s="19" t="str">
         <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F37" s="19" t="str">
+      <c r="G37" s="19" t="str">
         <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G37" s="19" t="str">
+      <c r="H37" s="19" t="str">
         <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H37" s="20" t="str">
+      <c r="I37" s="20" t="str">
         <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I37" s="19" t="str">
+      <c r="J37" s="19" t="str">
         <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="22"/>
       <c r="B38" s="22"/>
       <c r="C38" s="22"/>
-      <c r="D38" s="19" t="str">
+      <c r="D38" s="22"/>
+      <c r="E38" s="19" t="str">
         <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E38" s="19" t="str">
+      <c r="F38" s="19" t="str">
         <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F38" s="19" t="str">
+      <c r="G38" s="19" t="str">
         <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G38" s="19" t="str">
+      <c r="H38" s="19" t="str">
         <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H38" s="20" t="str">
+      <c r="I38" s="20" t="str">
         <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I38" s="19" t="str">
+      <c r="J38" s="19" t="str">
         <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
-      <c r="D39" s="19" t="str">
+      <c r="D39" s="22"/>
+      <c r="E39" s="19" t="str">
         <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E39" s="19" t="str">
+      <c r="F39" s="19" t="str">
         <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F39" s="19" t="str">
+      <c r="G39" s="19" t="str">
         <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G39" s="19" t="str">
+      <c r="H39" s="19" t="str">
         <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H39" s="20" t="str">
+      <c r="I39" s="20" t="str">
         <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I39" s="19" t="str">
+      <c r="J39" s="19" t="str">
         <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="22"/>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
-      <c r="D40" s="19" t="str">
+      <c r="D40" s="22"/>
+      <c r="E40" s="19" t="str">
         <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E40" s="19" t="str">
+      <c r="F40" s="19" t="str">
         <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F40" s="19" t="str">
+      <c r="G40" s="19" t="str">
         <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G40" s="19" t="str">
+      <c r="H40" s="19" t="str">
         <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H40" s="20" t="str">
+      <c r="I40" s="20" t="str">
         <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I40" s="19" t="str">
+      <c r="J40" s="19" t="str">
         <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="22"/>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
-      <c r="D41" s="19" t="str">
+      <c r="D41" s="22"/>
+      <c r="E41" s="19" t="str">
         <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E41" s="19" t="str">
+      <c r="F41" s="19" t="str">
         <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F41" s="19" t="str">
+      <c r="G41" s="19" t="str">
         <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G41" s="19" t="str">
+      <c r="H41" s="19" t="str">
         <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H41" s="20" t="str">
+      <c r="I41" s="20" t="str">
         <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I41" s="19" t="str">
+      <c r="J41" s="19" t="str">
         <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="22"/>
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
-      <c r="D42" s="19" t="str">
+      <c r="D42" s="22"/>
+      <c r="E42" s="19" t="str">
         <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E42" s="19" t="str">
+      <c r="F42" s="19" t="str">
         <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F42" s="19" t="str">
+      <c r="G42" s="19" t="str">
         <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G42" s="19" t="str">
+      <c r="H42" s="19" t="str">
         <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H42" s="20" t="str">
+      <c r="I42" s="20" t="str">
         <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I42" s="19" t="str">
+      <c r="J42" s="19" t="str">
         <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="22"/>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
-      <c r="D43" s="19" t="str">
+      <c r="D43" s="22"/>
+      <c r="E43" s="19" t="str">
         <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E43" s="19" t="str">
+      <c r="F43" s="19" t="str">
         <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F43" s="19" t="str">
+      <c r="G43" s="19" t="str">
         <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G43" s="19" t="str">
+      <c r="H43" s="19" t="str">
         <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H43" s="20" t="str">
+      <c r="I43" s="20" t="str">
         <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I43" s="19" t="str">
+      <c r="J43" s="19" t="str">
         <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
-      <c r="D44" s="19" t="str">
+      <c r="D44" s="22"/>
+      <c r="E44" s="19" t="str">
         <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E44" s="19" t="str">
+      <c r="F44" s="19" t="str">
         <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F44" s="19" t="str">
+      <c r="G44" s="19" t="str">
         <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G44" s="19" t="str">
+      <c r="H44" s="19" t="str">
         <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H44" s="20" t="str">
+      <c r="I44" s="20" t="str">
         <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I44" s="19" t="str">
+      <c r="J44" s="19" t="str">
         <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="22"/>
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
-      <c r="D45" s="19" t="str">
+      <c r="D45" s="22"/>
+      <c r="E45" s="19" t="str">
         <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E45" s="19" t="str">
+      <c r="F45" s="19" t="str">
         <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F45" s="19" t="str">
+      <c r="G45" s="19" t="str">
         <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G45" s="19" t="str">
+      <c r="H45" s="19" t="str">
         <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H45" s="20" t="str">
+      <c r="I45" s="20" t="str">
         <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I45" s="19" t="str">
+      <c r="J45" s="19" t="str">
         <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="22"/>
       <c r="B46" s="22"/>
       <c r="C46" s="22"/>
-      <c r="D46" s="19" t="str">
+      <c r="D46" s="22"/>
+      <c r="E46" s="19" t="str">
         <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E46" s="19" t="str">
+      <c r="F46" s="19" t="str">
         <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F46" s="19" t="str">
+      <c r="G46" s="19" t="str">
         <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G46" s="19" t="str">
+      <c r="H46" s="19" t="str">
         <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H46" s="20" t="str">
+      <c r="I46" s="20" t="str">
         <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I46" s="19" t="str">
+      <c r="J46" s="19" t="str">
         <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="22"/>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
-      <c r="D47" s="19" t="str">
+      <c r="D47" s="22"/>
+      <c r="E47" s="19" t="str">
         <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E47" s="19" t="str">
+      <c r="F47" s="19" t="str">
         <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F47" s="19" t="str">
+      <c r="G47" s="19" t="str">
         <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G47" s="19" t="str">
+      <c r="H47" s="19" t="str">
         <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H47" s="20" t="str">
+      <c r="I47" s="20" t="str">
         <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I47" s="19" t="str">
+      <c r="J47" s="19" t="str">
         <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="22"/>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
-      <c r="D48" s="19" t="str">
+      <c r="D48" s="22"/>
+      <c r="E48" s="19" t="str">
         <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E48" s="19" t="str">
+      <c r="F48" s="19" t="str">
         <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F48" s="19" t="str">
+      <c r="G48" s="19" t="str">
         <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G48" s="19" t="str">
+      <c r="H48" s="19" t="str">
         <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H48" s="20" t="str">
+      <c r="I48" s="20" t="str">
         <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I48" s="19" t="str">
+      <c r="J48" s="19" t="str">
         <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="22"/>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
-      <c r="D49" s="19" t="str">
+      <c r="D49" s="22"/>
+      <c r="E49" s="19" t="str">
         <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E49" s="19" t="str">
+      <c r="F49" s="19" t="str">
         <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F49" s="19" t="str">
+      <c r="G49" s="19" t="str">
         <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G49" s="19" t="str">
+      <c r="H49" s="19" t="str">
         <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H49" s="20" t="str">
+      <c r="I49" s="20" t="str">
         <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I49" s="19" t="str">
+      <c r="J49" s="19" t="str">
         <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="22"/>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
-      <c r="D50" s="19" t="str">
+      <c r="D50" s="22"/>
+      <c r="E50" s="19" t="str">
         <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E50" s="19" t="str">
+      <c r="F50" s="19" t="str">
         <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F50" s="19" t="str">
+      <c r="G50" s="19" t="str">
         <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G50" s="19" t="str">
+      <c r="H50" s="19" t="str">
         <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H50" s="20" t="str">
+      <c r="I50" s="20" t="str">
         <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I50" s="19" t="str">
+      <c r="J50" s="19" t="str">
         <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="22"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
-      <c r="D51" s="19" t="str">
+      <c r="D51" s="22"/>
+      <c r="E51" s="19" t="str">
         <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E51" s="19" t="str">
+      <c r="F51" s="19" t="str">
         <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F51" s="19" t="str">
+      <c r="G51" s="19" t="str">
         <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G51" s="19" t="str">
+      <c r="H51" s="19" t="str">
         <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H51" s="20" t="str">
+      <c r="I51" s="20" t="str">
         <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I51" s="19" t="str">
+      <c r="J51" s="19" t="str">
         <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
-      <c r="D52" s="19" t="str">
+      <c r="D52" s="22"/>
+      <c r="E52" s="19" t="str">
         <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E52" s="19" t="str">
+      <c r="F52" s="19" t="str">
         <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F52" s="19" t="str">
+      <c r="G52" s="19" t="str">
         <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G52" s="19" t="str">
+      <c r="H52" s="19" t="str">
         <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H52" s="20" t="str">
+      <c r="I52" s="20" t="str">
         <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I52" s="19" t="str">
+      <c r="J52" s="19" t="str">
         <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="22"/>
       <c r="B53" s="22"/>
       <c r="C53" s="22"/>
-      <c r="D53" s="19" t="str">
+      <c r="D53" s="22"/>
+      <c r="E53" s="19" t="str">
         <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E53" s="19" t="str">
+      <c r="F53" s="19" t="str">
         <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F53" s="19" t="str">
+      <c r="G53" s="19" t="str">
         <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G53" s="19" t="str">
+      <c r="H53" s="19" t="str">
         <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H53" s="20" t="str">
+      <c r="I53" s="20" t="str">
         <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I53" s="19" t="str">
+      <c r="J53" s="19" t="str">
         <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="22"/>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
-      <c r="D54" s="19" t="str">
+      <c r="D54" s="22"/>
+      <c r="E54" s="19" t="str">
         <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E54" s="19" t="str">
+      <c r="F54" s="19" t="str">
         <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F54" s="19" t="str">
+      <c r="G54" s="19" t="str">
         <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G54" s="19" t="str">
+      <c r="H54" s="19" t="str">
         <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H54" s="20" t="str">
+      <c r="I54" s="20" t="str">
         <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I54" s="19" t="str">
+      <c r="J54" s="19" t="str">
         <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="22"/>
       <c r="B55" s="22"/>
       <c r="C55" s="22"/>
-      <c r="D55" s="19" t="str">
+      <c r="D55" s="22"/>
+      <c r="E55" s="19" t="str">
         <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E55" s="19" t="str">
+      <c r="F55" s="19" t="str">
         <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F55" s="19" t="str">
+      <c r="G55" s="19" t="str">
         <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G55" s="19" t="str">
+      <c r="H55" s="19" t="str">
         <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H55" s="20" t="str">
+      <c r="I55" s="20" t="str">
         <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I55" s="19" t="str">
+      <c r="J55" s="19" t="str">
         <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="22"/>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
-      <c r="D56" s="19" t="str">
+      <c r="D56" s="22"/>
+      <c r="E56" s="19" t="str">
         <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E56" s="19" t="str">
+      <c r="F56" s="19" t="str">
         <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F56" s="19" t="str">
+      <c r="G56" s="19" t="str">
         <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G56" s="19" t="str">
+      <c r="H56" s="19" t="str">
         <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H56" s="20" t="str">
+      <c r="I56" s="20" t="str">
         <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I56" s="19" t="str">
+      <c r="J56" s="19" t="str">
         <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="22"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
-      <c r="D57" s="19" t="str">
+      <c r="D57" s="22"/>
+      <c r="E57" s="19" t="str">
         <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E57" s="19" t="str">
+      <c r="F57" s="19" t="str">
         <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F57" s="19" t="str">
+      <c r="G57" s="19" t="str">
         <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G57" s="19" t="str">
+      <c r="H57" s="19" t="str">
         <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H57" s="20" t="str">
+      <c r="I57" s="20" t="str">
         <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I57" s="19" t="str">
+      <c r="J57" s="19" t="str">
         <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="22"/>
       <c r="B58" s="22"/>
       <c r="C58" s="22"/>
-      <c r="D58" s="19" t="str">
+      <c r="D58" s="22"/>
+      <c r="E58" s="19" t="str">
         <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E58" s="19" t="str">
+      <c r="F58" s="19" t="str">
         <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F58" s="19" t="str">
+      <c r="G58" s="19" t="str">
         <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G58" s="19" t="str">
+      <c r="H58" s="19" t="str">
         <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H58" s="20" t="str">
+      <c r="I58" s="20" t="str">
         <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I58" s="19" t="str">
+      <c r="J58" s="19" t="str">
         <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="22"/>
       <c r="B59" s="22"/>
       <c r="C59" s="22"/>
-      <c r="D59" s="19" t="str">
+      <c r="D59" s="22"/>
+      <c r="E59" s="19" t="str">
         <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E59" s="19" t="str">
+      <c r="F59" s="19" t="str">
         <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F59" s="19" t="str">
+      <c r="G59" s="19" t="str">
         <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G59" s="19" t="str">
+      <c r="H59" s="19" t="str">
         <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H59" s="20" t="str">
+      <c r="I59" s="20" t="str">
         <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I59" s="19" t="str">
+      <c r="J59" s="19" t="str">
         <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="22"/>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
-      <c r="D60" s="19" t="str">
+      <c r="D60" s="22"/>
+      <c r="E60" s="19" t="str">
         <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E60" s="19" t="str">
+      <c r="F60" s="19" t="str">
         <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F60" s="19" t="str">
+      <c r="G60" s="19" t="str">
         <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G60" s="19" t="str">
+      <c r="H60" s="19" t="str">
         <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H60" s="20" t="str">
+      <c r="I60" s="20" t="str">
         <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I60" s="19" t="str">
+      <c r="J60" s="19" t="str">
         <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="22"/>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
-      <c r="D61" s="19" t="str">
+      <c r="D61" s="22"/>
+      <c r="E61" s="19" t="str">
         <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E61" s="19" t="str">
+      <c r="F61" s="19" t="str">
         <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F61" s="19" t="str">
+      <c r="G61" s="19" t="str">
         <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G61" s="19" t="str">
+      <c r="H61" s="19" t="str">
         <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H61" s="20" t="str">
+      <c r="I61" s="20" t="str">
         <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I61" s="19" t="str">
+      <c r="J61" s="19" t="str">
         <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="22"/>
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
-      <c r="D62" s="19" t="str">
+      <c r="D62" s="22"/>
+      <c r="E62" s="19" t="str">
         <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E62" s="19" t="str">
+      <c r="F62" s="19" t="str">
         <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F62" s="19" t="str">
+      <c r="G62" s="19" t="str">
         <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G62" s="19" t="str">
+      <c r="H62" s="19" t="str">
         <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H62" s="20" t="str">
+      <c r="I62" s="20" t="str">
         <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I62" s="19" t="str">
+      <c r="J62" s="19" t="str">
         <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="22"/>
       <c r="B63" s="22"/>
       <c r="C63" s="22"/>
-      <c r="D63" s="19" t="str">
+      <c r="D63" s="22"/>
+      <c r="E63" s="19" t="str">
         <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E63" s="19" t="str">
+      <c r="F63" s="19" t="str">
         <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F63" s="19" t="str">
+      <c r="G63" s="19" t="str">
         <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G63" s="19" t="str">
+      <c r="H63" s="19" t="str">
         <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H63" s="20" t="str">
+      <c r="I63" s="20" t="str">
         <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I63" s="19" t="str">
+      <c r="J63" s="19" t="str">
         <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="22"/>
       <c r="B64" s="22"/>
       <c r="C64" s="22"/>
-      <c r="D64" s="19" t="str">
+      <c r="D64" s="22"/>
+      <c r="E64" s="19" t="str">
         <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E64" s="19" t="str">
+      <c r="F64" s="19" t="str">
         <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F64" s="19" t="str">
+      <c r="G64" s="19" t="str">
         <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G64" s="19" t="str">
+      <c r="H64" s="19" t="str">
         <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H64" s="20" t="str">
+      <c r="I64" s="20" t="str">
         <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I64" s="19" t="str">
+      <c r="J64" s="19" t="str">
         <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="22"/>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
-      <c r="D65" s="19" t="str">
+      <c r="D65" s="22"/>
+      <c r="E65" s="19" t="str">
         <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E65" s="19" t="str">
+      <c r="F65" s="19" t="str">
         <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F65" s="19" t="str">
+      <c r="G65" s="19" t="str">
         <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G65" s="19" t="str">
+      <c r="H65" s="19" t="str">
         <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H65" s="20" t="str">
+      <c r="I65" s="20" t="str">
         <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I65" s="19" t="str">
+      <c r="J65" s="19" t="str">
         <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="22"/>
       <c r="B66" s="22"/>
       <c r="C66" s="22"/>
-      <c r="D66" s="19" t="str">
+      <c r="D66" s="22"/>
+      <c r="E66" s="19" t="str">
         <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E66" s="19" t="str">
+      <c r="F66" s="19" t="str">
         <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F66" s="19" t="str">
+      <c r="G66" s="19" t="str">
         <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G66" s="19" t="str">
+      <c r="H66" s="19" t="str">
         <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H66" s="20" t="str">
+      <c r="I66" s="20" t="str">
         <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I66" s="19" t="str">
+      <c r="J66" s="19" t="str">
         <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="22"/>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
-      <c r="D67" s="19" t="str">
+      <c r="D67" s="22"/>
+      <c r="E67" s="19" t="str">
         <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E67" s="19" t="str">
+      <c r="F67" s="19" t="str">
         <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F67" s="19" t="str">
+      <c r="G67" s="19" t="str">
         <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G67" s="19" t="str">
+      <c r="H67" s="19" t="str">
         <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H67" s="20" t="str">
+      <c r="I67" s="20" t="str">
         <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I67" s="19" t="str">
+      <c r="J67" s="19" t="str">
         <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="22"/>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
-      <c r="D68" s="19" t="str">
+      <c r="D68" s="22"/>
+      <c r="E68" s="19" t="str">
         <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E68" s="19" t="str">
+      <c r="F68" s="19" t="str">
         <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F68" s="19" t="str">
+      <c r="G68" s="19" t="str">
         <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G68" s="19" t="str">
+      <c r="H68" s="19" t="str">
         <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H68" s="20" t="str">
+      <c r="I68" s="20" t="str">
         <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I68" s="19" t="str">
+      <c r="J68" s="19" t="str">
         <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="22"/>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
-      <c r="D69" s="19" t="str">
+      <c r="D69" s="22"/>
+      <c r="E69" s="19" t="str">
         <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E69" s="19" t="str">
+      <c r="F69" s="19" t="str">
         <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F69" s="19" t="str">
+      <c r="G69" s="19" t="str">
         <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G69" s="19" t="str">
+      <c r="H69" s="19" t="str">
         <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H69" s="20" t="str">
+      <c r="I69" s="20" t="str">
         <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I69" s="19" t="str">
+      <c r="J69" s="19" t="str">
         <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="22"/>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
-      <c r="D70" s="19" t="str">
+      <c r="D70" s="22"/>
+      <c r="E70" s="19" t="str">
         <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E70" s="19" t="str">
+      <c r="F70" s="19" t="str">
         <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F70" s="19" t="str">
+      <c r="G70" s="19" t="str">
         <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G70" s="19" t="str">
+      <c r="H70" s="19" t="str">
         <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H70" s="20" t="str">
+      <c r="I70" s="20" t="str">
         <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I70" s="19" t="str">
+      <c r="J70" s="19" t="str">
         <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="22"/>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
-      <c r="D71" s="19" t="str">
+      <c r="D71" s="22"/>
+      <c r="E71" s="19" t="str">
         <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E71" s="19" t="str">
+      <c r="F71" s="19" t="str">
         <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F71" s="19" t="str">
+      <c r="G71" s="19" t="str">
         <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G71" s="19" t="str">
+      <c r="H71" s="19" t="str">
         <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H71" s="20" t="str">
+      <c r="I71" s="20" t="str">
         <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I71" s="19" t="str">
+      <c r="J71" s="19" t="str">
         <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="22"/>
       <c r="B72" s="22"/>
       <c r="C72" s="22"/>
-      <c r="D72" s="19" t="str">
+      <c r="D72" s="22"/>
+      <c r="E72" s="19" t="str">
         <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E72" s="19" t="str">
+      <c r="F72" s="19" t="str">
         <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F72" s="19" t="str">
+      <c r="G72" s="19" t="str">
         <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G72" s="19" t="str">
+      <c r="H72" s="19" t="str">
         <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H72" s="20" t="str">
+      <c r="I72" s="20" t="str">
         <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I72" s="19" t="str">
+      <c r="J72" s="19" t="str">
         <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="22"/>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
-      <c r="D73" s="19" t="str">
+      <c r="D73" s="22"/>
+      <c r="E73" s="19" t="str">
         <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E73" s="19" t="str">
+      <c r="F73" s="19" t="str">
         <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F73" s="19" t="str">
+      <c r="G73" s="19" t="str">
         <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G73" s="19" t="str">
+      <c r="H73" s="19" t="str">
         <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H73" s="20" t="str">
+      <c r="I73" s="20" t="str">
         <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I73" s="19" t="str">
+      <c r="J73" s="19" t="str">
         <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="22"/>
       <c r="B74" s="22"/>
       <c r="C74" s="22"/>
-      <c r="D74" s="19" t="str">
+      <c r="D74" s="22"/>
+      <c r="E74" s="19" t="str">
         <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E74" s="19" t="str">
+      <c r="F74" s="19" t="str">
         <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F74" s="19" t="str">
+      <c r="G74" s="19" t="str">
         <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G74" s="19" t="str">
+      <c r="H74" s="19" t="str">
         <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H74" s="20" t="str">
+      <c r="I74" s="20" t="str">
         <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I74" s="19" t="str">
+      <c r="J74" s="19" t="str">
         <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="22"/>
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
-      <c r="D75" s="19" t="str">
+      <c r="D75" s="22"/>
+      <c r="E75" s="19" t="str">
         <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E75" s="19" t="str">
+      <c r="F75" s="19" t="str">
         <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F75" s="19" t="str">
+      <c r="G75" s="19" t="str">
         <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G75" s="19" t="str">
+      <c r="H75" s="19" t="str">
         <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H75" s="20" t="str">
+      <c r="I75" s="20" t="str">
         <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I75" s="19" t="str">
+      <c r="J75" s="19" t="str">
         <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="22"/>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
-      <c r="D76" s="19" t="str">
+      <c r="D76" s="22"/>
+      <c r="E76" s="19" t="str">
         <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E76" s="19" t="str">
+      <c r="F76" s="19" t="str">
         <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F76" s="19" t="str">
+      <c r="G76" s="19" t="str">
         <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G76" s="19" t="str">
+      <c r="H76" s="19" t="str">
         <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H76" s="20" t="str">
+      <c r="I76" s="20" t="str">
         <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I76" s="19" t="str">
+      <c r="J76" s="19" t="str">
         <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="22"/>
       <c r="B77" s="22"/>
       <c r="C77" s="22"/>
-      <c r="D77" s="19" t="str">
+      <c r="D77" s="22"/>
+      <c r="E77" s="19" t="str">
         <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E77" s="19" t="str">
+      <c r="F77" s="19" t="str">
         <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F77" s="19" t="str">
+      <c r="G77" s="19" t="str">
         <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G77" s="19" t="str">
+      <c r="H77" s="19" t="str">
         <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H77" s="20" t="str">
+      <c r="I77" s="20" t="str">
         <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I77" s="19" t="str">
+      <c r="J77" s="19" t="str">
         <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="22"/>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
-      <c r="D78" s="19" t="str">
+      <c r="D78" s="22"/>
+      <c r="E78" s="19" t="str">
         <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E78" s="19" t="str">
+      <c r="F78" s="19" t="str">
         <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F78" s="19" t="str">
+      <c r="G78" s="19" t="str">
         <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G78" s="19" t="str">
+      <c r="H78" s="19" t="str">
         <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H78" s="20" t="str">
+      <c r="I78" s="20" t="str">
         <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I78" s="19" t="str">
+      <c r="J78" s="19" t="str">
         <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="22"/>
       <c r="B79" s="22"/>
       <c r="C79" s="22"/>
-      <c r="D79" s="19" t="str">
+      <c r="D79" s="22"/>
+      <c r="E79" s="19" t="str">
         <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E79" s="19" t="str">
+      <c r="F79" s="19" t="str">
         <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F79" s="19" t="str">
+      <c r="G79" s="19" t="str">
         <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G79" s="19" t="str">
+      <c r="H79" s="19" t="str">
         <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H79" s="20" t="str">
+      <c r="I79" s="20" t="str">
         <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I79" s="19" t="str">
+      <c r="J79" s="19" t="str">
         <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="22"/>
       <c r="B80" s="22"/>
       <c r="C80" s="22"/>
-      <c r="D80" s="19" t="str">
+      <c r="D80" s="22"/>
+      <c r="E80" s="19" t="str">
         <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E80" s="19" t="str">
+      <c r="F80" s="19" t="str">
         <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F80" s="19" t="str">
+      <c r="G80" s="19" t="str">
         <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G80" s="19" t="str">
+      <c r="H80" s="19" t="str">
         <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H80" s="20" t="str">
+      <c r="I80" s="20" t="str">
         <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I80" s="19" t="str">
+      <c r="J80" s="19" t="str">
         <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="22"/>
       <c r="B81" s="22"/>
       <c r="C81" s="22"/>
-      <c r="D81" s="19" t="str">
+      <c r="D81" s="22"/>
+      <c r="E81" s="19" t="str">
         <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E81" s="19" t="str">
+      <c r="F81" s="19" t="str">
         <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F81" s="19" t="str">
+      <c r="G81" s="19" t="str">
         <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G81" s="19" t="str">
+      <c r="H81" s="19" t="str">
         <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H81" s="20" t="str">
+      <c r="I81" s="20" t="str">
         <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I81" s="19" t="str">
+      <c r="J81" s="19" t="str">
         <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="22"/>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
-      <c r="D82" s="19" t="str">
+      <c r="D82" s="22"/>
+      <c r="E82" s="19" t="str">
         <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E82" s="19" t="str">
+      <c r="F82" s="19" t="str">
         <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F82" s="19" t="str">
+      <c r="G82" s="19" t="str">
         <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G82" s="19" t="str">
+      <c r="H82" s="19" t="str">
         <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H82" s="20" t="str">
+      <c r="I82" s="20" t="str">
         <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I82" s="19" t="str">
+      <c r="J82" s="19" t="str">
         <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="22"/>
       <c r="B83" s="22"/>
       <c r="C83" s="22"/>
-      <c r="D83" s="19" t="str">
+      <c r="D83" s="22"/>
+      <c r="E83" s="19" t="str">
         <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E83" s="19" t="str">
+      <c r="F83" s="19" t="str">
         <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F83" s="19" t="str">
+      <c r="G83" s="19" t="str">
         <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G83" s="19" t="str">
+      <c r="H83" s="19" t="str">
         <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H83" s="20" t="str">
+      <c r="I83" s="20" t="str">
         <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I83" s="19" t="str">
+      <c r="J83" s="19" t="str">
         <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="22"/>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
-      <c r="D84" s="19" t="str">
+      <c r="D84" s="22"/>
+      <c r="E84" s="19" t="str">
         <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E84" s="19" t="str">
+      <c r="F84" s="19" t="str">
         <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F84" s="19" t="str">
+      <c r="G84" s="19" t="str">
         <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G84" s="19" t="str">
+      <c r="H84" s="19" t="str">
         <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H84" s="20" t="str">
+      <c r="I84" s="20" t="str">
         <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I84" s="19" t="str">
+      <c r="J84" s="19" t="str">
         <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="22"/>
       <c r="B85" s="22"/>
       <c r="C85" s="22"/>
-      <c r="D85" s="19" t="str">
+      <c r="D85" s="22"/>
+      <c r="E85" s="19" t="str">
         <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E85" s="19" t="str">
+      <c r="F85" s="19" t="str">
         <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F85" s="19" t="str">
+      <c r="G85" s="19" t="str">
         <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G85" s="19" t="str">
+      <c r="H85" s="19" t="str">
         <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H85" s="20" t="str">
+      <c r="I85" s="20" t="str">
         <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I85" s="19" t="str">
+      <c r="J85" s="19" t="str">
         <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="22"/>
       <c r="B86" s="22"/>
       <c r="C86" s="22"/>
-      <c r="D86" s="19" t="str">
+      <c r="D86" s="22"/>
+      <c r="E86" s="19" t="str">
         <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E86" s="19" t="str">
+      <c r="F86" s="19" t="str">
         <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F86" s="19" t="str">
+      <c r="G86" s="19" t="str">
         <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G86" s="19" t="str">
+      <c r="H86" s="19" t="str">
         <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H86" s="20" t="str">
+      <c r="I86" s="20" t="str">
         <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I86" s="19" t="str">
+      <c r="J86" s="19" t="str">
         <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="22"/>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
-      <c r="D87" s="19" t="str">
+      <c r="D87" s="22"/>
+      <c r="E87" s="19" t="str">
         <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E87" s="19" t="str">
+      <c r="F87" s="19" t="str">
         <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F87" s="19" t="str">
+      <c r="G87" s="19" t="str">
         <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G87" s="19" t="str">
+      <c r="H87" s="19" t="str">
         <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H87" s="20" t="str">
+      <c r="I87" s="20" t="str">
         <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I87" s="19" t="str">
+      <c r="J87" s="19" t="str">
         <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="22"/>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
-      <c r="D88" s="19" t="str">
+      <c r="D88" s="22"/>
+      <c r="E88" s="19" t="str">
         <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E88" s="19" t="str">
+      <c r="F88" s="19" t="str">
         <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F88" s="19" t="str">
+      <c r="G88" s="19" t="str">
         <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G88" s="19" t="str">
+      <c r="H88" s="19" t="str">
         <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H88" s="20" t="str">
+      <c r="I88" s="20" t="str">
         <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I88" s="19" t="str">
+      <c r="J88" s="19" t="str">
         <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="22"/>
       <c r="B89" s="22"/>
       <c r="C89" s="22"/>
-      <c r="D89" s="19" t="str">
+      <c r="D89" s="22"/>
+      <c r="E89" s="19" t="str">
         <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E89" s="19" t="str">
+      <c r="F89" s="19" t="str">
         <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F89" s="19" t="str">
+      <c r="G89" s="19" t="str">
         <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G89" s="19" t="str">
+      <c r="H89" s="19" t="str">
         <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H89" s="20" t="str">
+      <c r="I89" s="20" t="str">
         <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I89" s="19" t="str">
+      <c r="J89" s="19" t="str">
         <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="22"/>
       <c r="B90" s="22"/>
       <c r="C90" s="22"/>
-      <c r="D90" s="19" t="str">
+      <c r="D90" s="22"/>
+      <c r="E90" s="19" t="str">
         <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E90" s="19" t="str">
+      <c r="F90" s="19" t="str">
         <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F90" s="19" t="str">
+      <c r="G90" s="19" t="str">
         <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G90" s="19" t="str">
+      <c r="H90" s="19" t="str">
         <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H90" s="20" t="str">
+      <c r="I90" s="20" t="str">
         <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I90" s="19" t="str">
+      <c r="J90" s="19" t="str">
         <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="22"/>
       <c r="B91" s="22"/>
       <c r="C91" s="22"/>
-      <c r="D91" s="19" t="str">
+      <c r="D91" s="22"/>
+      <c r="E91" s="19" t="str">
         <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E91" s="19" t="str">
+      <c r="F91" s="19" t="str">
         <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F91" s="19" t="str">
+      <c r="G91" s="19" t="str">
         <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G91" s="19" t="str">
+      <c r="H91" s="19" t="str">
         <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H91" s="20" t="str">
+      <c r="I91" s="20" t="str">
         <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I91" s="19" t="str">
+      <c r="J91" s="19" t="str">
         <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="22"/>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
-      <c r="D92" s="19" t="str">
+      <c r="D92" s="22"/>
+      <c r="E92" s="19" t="str">
         <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E92" s="19" t="str">
+      <c r="F92" s="19" t="str">
         <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F92" s="19" t="str">
+      <c r="G92" s="19" t="str">
         <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G92" s="19" t="str">
+      <c r="H92" s="19" t="str">
         <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H92" s="20" t="str">
+      <c r="I92" s="20" t="str">
         <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I92" s="19" t="str">
+      <c r="J92" s="19" t="str">
         <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="22"/>
       <c r="B93" s="22"/>
       <c r="C93" s="22"/>
-      <c r="D93" s="19" t="str">
+      <c r="D93" s="22"/>
+      <c r="E93" s="19" t="str">
         <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E93" s="19" t="str">
+      <c r="F93" s="19" t="str">
         <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F93" s="19" t="str">
+      <c r="G93" s="19" t="str">
         <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G93" s="19" t="str">
+      <c r="H93" s="19" t="str">
         <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H93" s="20" t="str">
+      <c r="I93" s="20" t="str">
         <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I93" s="19" t="str">
+      <c r="J93" s="19" t="str">
         <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="22"/>
       <c r="B94" s="22"/>
       <c r="C94" s="22"/>
-      <c r="D94" s="19" t="str">
+      <c r="D94" s="22"/>
+      <c r="E94" s="19" t="str">
         <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E94" s="19" t="str">
+      <c r="F94" s="19" t="str">
         <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F94" s="19" t="str">
+      <c r="G94" s="19" t="str">
         <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G94" s="19" t="str">
+      <c r="H94" s="19" t="str">
         <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H94" s="20" t="str">
+      <c r="I94" s="20" t="str">
         <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I94" s="19" t="str">
+      <c r="J94" s="19" t="str">
         <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="22"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22"/>
-      <c r="D95" s="19" t="str">
+      <c r="D95" s="22"/>
+      <c r="E95" s="19" t="str">
         <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E95" s="19" t="str">
+      <c r="F95" s="19" t="str">
         <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F95" s="19" t="str">
+      <c r="G95" s="19" t="str">
         <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G95" s="19" t="str">
+      <c r="H95" s="19" t="str">
         <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H95" s="20" t="str">
+      <c r="I95" s="20" t="str">
         <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I95" s="19" t="str">
+      <c r="J95" s="19" t="str">
         <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="22"/>
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
-      <c r="D96" s="19" t="str">
+      <c r="D96" s="22"/>
+      <c r="E96" s="19" t="str">
         <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E96" s="19" t="str">
+      <c r="F96" s="19" t="str">
         <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F96" s="19" t="str">
+      <c r="G96" s="19" t="str">
         <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G96" s="19" t="str">
+      <c r="H96" s="19" t="str">
         <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H96" s="20" t="str">
+      <c r="I96" s="20" t="str">
         <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I96" s="19" t="str">
+      <c r="J96" s="19" t="str">
         <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="22"/>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
-      <c r="D97" s="19" t="str">
+      <c r="D97" s="22"/>
+      <c r="E97" s="19" t="str">
         <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E97" s="19" t="str">
+      <c r="F97" s="19" t="str">
         <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F97" s="19" t="str">
+      <c r="G97" s="19" t="str">
         <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G97" s="19" t="str">
+      <c r="H97" s="19" t="str">
         <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H97" s="20" t="str">
+      <c r="I97" s="20" t="str">
         <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I97" s="19" t="str">
+      <c r="J97" s="19" t="str">
         <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="22"/>
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
-      <c r="D98" s="19" t="str">
+      <c r="D98" s="22"/>
+      <c r="E98" s="19" t="str">
         <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E98" s="19" t="str">
+      <c r="F98" s="19" t="str">
         <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F98" s="19" t="str">
+      <c r="G98" s="19" t="str">
         <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G98" s="19" t="str">
+      <c r="H98" s="19" t="str">
         <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H98" s="20" t="str">
+      <c r="I98" s="20" t="str">
         <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I98" s="19" t="str">
+      <c r="J98" s="19" t="str">
         <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="22"/>
       <c r="B99" s="22"/>
       <c r="C99" s="22"/>
-      <c r="D99" s="19" t="str">
+      <c r="D99" s="22"/>
+      <c r="E99" s="19" t="str">
         <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E99" s="19" t="str">
+      <c r="F99" s="19" t="str">
         <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F99" s="19" t="str">
+      <c r="G99" s="19" t="str">
         <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G99" s="19" t="str">
+      <c r="H99" s="19" t="str">
         <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H99" s="20" t="str">
+      <c r="I99" s="20" t="str">
         <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I99" s="19" t="str">
+      <c r="J99" s="19" t="str">
         <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="22"/>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
-      <c r="D100" s="19" t="str">
+      <c r="D100" s="22"/>
+      <c r="E100" s="19" t="str">
         <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E100" s="19" t="str">
+      <c r="F100" s="19" t="str">
         <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F100" s="19" t="str">
+      <c r="G100" s="19" t="str">
         <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G100" s="19" t="str">
+      <c r="H100" s="19" t="str">
         <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H100" s="20" t="str">
+      <c r="I100" s="20" t="str">
         <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I100" s="19" t="str">
+      <c r="J100" s="19" t="str">
         <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="22"/>
       <c r="B101" s="22"/>
       <c r="C101" s="22"/>
-      <c r="D101" s="19" t="str">
+      <c r="D101" s="22"/>
+      <c r="E101" s="19" t="str">
         <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,2,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="E101" s="19" t="str">
+      <c r="F101" s="19" t="str">
         <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="F101" s="19" t="str">
+      <c r="G101" s="19" t="str">
         <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G101" s="19" t="str">
+      <c r="H101" s="19" t="str">
         <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="H101" s="20" t="str">
+      <c r="I101" s="20" t="str">
         <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="I101" s="19" t="str">
+      <c r="J101" s="19" t="str">
         <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F101 A4 A2:C3 A5:C15" xr:uid="{A89C4704-896A-47DC-A7B5-29F469ADEA0A}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G101 A4 A2:D3 A5:D15" xr:uid="{A89C4704-896A-47DC-A7B5-29F469ADEA0A}">
       <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0FCBDF7F-DBCD-449D-AA2E-06185888F985}"/>
-    <hyperlink ref="H3" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FF73F192-9590-488D-A75A-2E0B31E9222F}"/>
-    <hyperlink ref="H4" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2DB990CC-FAC5-45FF-945E-3759CDA1E0A2}"/>
-    <hyperlink ref="H5" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{25973EA4-5900-4AC9-8D4F-CA1C33271EB7}"/>
-    <hyperlink ref="H6" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF1DEE4C-DA5A-4C09-B41B-009247983E60}"/>
-    <hyperlink ref="H7" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5F752DEE-B49F-4390-ABF1-6BB2F79E5304}"/>
-    <hyperlink ref="H8" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5469E140-AFE5-46EC-9612-45B45C6161A9}"/>
-    <hyperlink ref="H9" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DE74E478-E6A1-4292-9E54-DAF048A34D02}"/>
-    <hyperlink ref="H10" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4487A71F-4709-4920-ACB1-91E07B9D18B8}"/>
-    <hyperlink ref="H11" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FFFA4705-F484-4B3E-93A1-A9E47BB54CB9}"/>
-    <hyperlink ref="H12" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{88612F3B-E50E-4D82-B45F-A793DDF84A37}"/>
-    <hyperlink ref="H13" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CAE279EC-B962-42D3-9529-7851F75A61F8}"/>
-    <hyperlink ref="H14" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{ADF08FAB-2C1D-440D-BBBD-83F01ADFD5AA}"/>
-    <hyperlink ref="H15" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DBF2AF88-58FD-4DBE-B8E9-75831EE171CD}"/>
-    <hyperlink ref="H16" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0C6E3BF0-AC54-4B80-90F8-33D9B305172B}"/>
-    <hyperlink ref="H17" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8F0CB904-1B5D-437D-BF55-F9F69DD30167}"/>
-    <hyperlink ref="H18" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C238411D-AA75-4757-8DB0-7FFF69DDFB8A}"/>
-    <hyperlink ref="H19" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2CF67AD9-AC37-4A2C-9F0C-B88919CE0F0B}"/>
-    <hyperlink ref="H20" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2365DA53-A1B6-4663-84F1-81578502F133}"/>
-    <hyperlink ref="H21" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{27C7D044-2183-4716-89B4-C8035A5BDACD}"/>
-    <hyperlink ref="H22" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9E80976F-467A-4B3F-BCF7-5FEF9BF0C8AE}"/>
-    <hyperlink ref="H23" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF8104DA-29E5-48F8-AFED-A25C0810F9F1}"/>
-    <hyperlink ref="H24" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B3E70961-470C-4C29-85A5-D74EDE38D151}"/>
-    <hyperlink ref="H25" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{38E86826-A211-494A-B6B9-1B69DDA2EFF7}"/>
-    <hyperlink ref="H26" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1F20F8DA-CB16-474B-A4B9-E1DE8EF7B09B}"/>
-    <hyperlink ref="H27" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2FD70308-BDB7-4249-A039-5D067660BFD6}"/>
-    <hyperlink ref="H28" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EA7880BB-4407-4622-9350-159221423B3B}"/>
-    <hyperlink ref="H29" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DB53A627-9823-4A01-A33A-A9D5FE8B2AAC}"/>
-    <hyperlink ref="H30" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F0F55E47-3169-4DEA-8A5D-DAE098E7AA0E}"/>
-    <hyperlink ref="H31" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{73A5B96C-ED9A-4AD1-9E59-E94722FC6C4A}"/>
-    <hyperlink ref="H32" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{69FD3ECA-E6CA-451D-B9DC-3E388750B256}"/>
-    <hyperlink ref="H33" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{334F12FE-5699-40ED-A7EF-B9FDF8878812}"/>
-    <hyperlink ref="H34" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{696173DE-241C-4BEF-8A3A-85997AEEDB99}"/>
-    <hyperlink ref="H35" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{55928F6D-FAA5-45BC-B738-422AD9F475DF}"/>
-    <hyperlink ref="H36" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A1DF03D6-97B6-4086-B93A-954D2A825E10}"/>
-    <hyperlink ref="H37" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4D5F3AF4-2725-43BD-AA9B-9523987533AC}"/>
-    <hyperlink ref="H38" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8A208B5A-1C1B-43DD-B2B2-FE5CBAD35495}"/>
-    <hyperlink ref="H39" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C529394C-3620-4427-A2BF-4292E38557FC}"/>
-    <hyperlink ref="H40" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BDDECC2B-E9AE-47C6-A23C-2DA7B59E7077}"/>
-    <hyperlink ref="H41" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FD5C0161-5CEB-4F94-82B3-E067DE66ED04}"/>
-    <hyperlink ref="H42" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{143ECA98-C8BA-4897-B755-588898AC192E}"/>
-    <hyperlink ref="H43" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8F88F95-8B05-4AB3-9866-9C70E9B2A4E4}"/>
-    <hyperlink ref="H44" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F124A78A-547A-48A0-B7F2-BCD018B97195}"/>
-    <hyperlink ref="H45" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{62A5BAA4-50D8-4BF4-AE64-6D2CC7E9DE07}"/>
-    <hyperlink ref="H46" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{84982593-6A7A-48C4-929C-73648C3B107A}"/>
-    <hyperlink ref="H47" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E607F40D-AB62-490A-9B14-A32A120E28A5}"/>
-    <hyperlink ref="H48" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{71AFF0FF-4AFD-4274-9B0C-B518AE9D4FBB}"/>
-    <hyperlink ref="H49" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{22943615-22F6-43D7-8D6B-D83D57A9668E}"/>
-    <hyperlink ref="H50" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{513EACCF-D581-414C-9FE6-7D531B61A162}"/>
-    <hyperlink ref="H51" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C6ECBB6-FF10-4B7E-9D81-A42EF84AA8E1}"/>
-    <hyperlink ref="H52" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A44F4C23-317F-411D-97DE-90D8A4FB33E9}"/>
-    <hyperlink ref="H53" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F680E46D-8C1F-4821-8B8A-DDB1C60E2649}"/>
-    <hyperlink ref="H54" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B47BF1C6-4B29-4841-BC81-7A9F9167CEA0}"/>
-    <hyperlink ref="H55" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F15A7166-2A15-4E22-976C-5C9DEEE00387}"/>
-    <hyperlink ref="H56" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{03311C28-542E-4A06-8A69-E0753F94342C}"/>
-    <hyperlink ref="H57" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B89816E6-2DB1-4559-8390-72D5BB3EC59F}"/>
-    <hyperlink ref="H58" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5EF32F46-F67E-42FC-8F23-64E2DFC818BE}"/>
-    <hyperlink ref="H59" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{47BD76DB-B7EE-4AA8-AE0A-70B28E660954}"/>
-    <hyperlink ref="H60" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CDC78262-2229-4847-B303-813B574F8EE5}"/>
-    <hyperlink ref="H61" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5B97DFF-6CC1-4A69-A9FE-DD1C99DACF50}"/>
-    <hyperlink ref="H62" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5E77F0A-3557-40D8-B8A3-577FACDE056B}"/>
-    <hyperlink ref="H63" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{70FBCE56-656D-477A-83F4-0AFA04A808FC}"/>
-    <hyperlink ref="H64" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{93731BA7-B2A0-4776-965E-17A7B1BAB201}"/>
-    <hyperlink ref="H65" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C410A9FA-539C-4E83-B463-FA90104A0A39}"/>
-    <hyperlink ref="H66" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{610F377F-834E-4CF4-8B3C-F0A4DC0498C2}"/>
-    <hyperlink ref="H67" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C14AED96-01F8-47A5-B7FE-D6B1A3B3EC3B}"/>
-    <hyperlink ref="H68" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8FABA8B0-3CD1-4546-95C2-BAF0FADE3597}"/>
-    <hyperlink ref="H69" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A74CDF5A-0BDB-43A0-976C-6361A1904602}"/>
-    <hyperlink ref="H70" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B1D3426F-0142-45CE-939B-8C055B9F229C}"/>
-    <hyperlink ref="H71" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E411C4D5-8F83-437F-8C4D-B86654CB559D}"/>
-    <hyperlink ref="H72" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0F119914-F3E1-4824-9792-A0A357F0C69B}"/>
-    <hyperlink ref="H73" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D32D0D21-2612-4845-8CAC-6D25352EF5D3}"/>
-    <hyperlink ref="H74" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CA051FA0-0A47-4B67-81A9-16F2D79D0081}"/>
-    <hyperlink ref="H75" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B7F56C90-456C-440F-BDFA-45F01F1AF565}"/>
-    <hyperlink ref="H76" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{93C00ACA-C3D2-460C-B9DA-117BDA833187}"/>
-    <hyperlink ref="H77" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8F3479D-3681-4B1E-BCE5-4E0133B2E36D}"/>
-    <hyperlink ref="H78" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DFEB60E2-96C4-4BA7-AF58-EF7581E3E37A}"/>
-    <hyperlink ref="H79" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5CF0FB32-CDC9-4C8D-89C7-A6FF4095C4F9}"/>
-    <hyperlink ref="H80" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3A85C454-9ABF-4536-A3BD-675C7034DE1C}"/>
-    <hyperlink ref="H81" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{91B4B64E-1B8A-4483-A731-0EE302C8EEC7}"/>
-    <hyperlink ref="H82" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5B6B187F-6E1C-4D7D-A171-76E12F010408}"/>
-    <hyperlink ref="H83" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FAA64865-36F1-41F1-BB4D-5F9E691EF208}"/>
-    <hyperlink ref="H84" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C544D59B-4E38-447B-88DE-6C9AE6A8284F}"/>
-    <hyperlink ref="H85" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DC777E21-D4B6-4035-8E42-23DA33C9C087}"/>
-    <hyperlink ref="H86" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2A2E1A6D-86FE-4987-9AB4-54B7C971DFAA}"/>
-    <hyperlink ref="H87" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B827DB21-242B-410B-9591-CBE07C83FDFD}"/>
-    <hyperlink ref="H88" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F57C9182-5D3B-4E46-BC40-46A3D8E627D3}"/>
-    <hyperlink ref="H89" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2554A8C1-62DA-44DF-BC74-A27CE8F7BFBC}"/>
-    <hyperlink ref="H90" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D640E482-9F19-4D2A-B812-FBB54A9504A1}"/>
-    <hyperlink ref="H91" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C457E0D7-1278-44E9-932C-B24EF3343FC3}"/>
-    <hyperlink ref="H92" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{696D2CB9-2D96-486D-9F75-7376DE1F0AEB}"/>
-    <hyperlink ref="H93" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{383E64D0-D9EC-437F-A3B7-DA69FBA1E00E}"/>
-    <hyperlink ref="H94" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{615FC7F9-F46E-45A6-BBA2-B72742CA4B41}"/>
-    <hyperlink ref="H95" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9838F64C-F593-4678-9DEC-7CCAF67151FA}"/>
-    <hyperlink ref="H96" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A596E95E-9814-454A-B1E7-DEF21E58E6CF}"/>
-    <hyperlink ref="H97" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A193D687-4899-45DD-88BB-7DBAA2A9C895}"/>
-    <hyperlink ref="H98" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C585F8E2-8893-49F5-BEC8-9ABD3B0B5208}"/>
-    <hyperlink ref="H99" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CD864CC2-420B-4384-B326-3C50D3018E3E}"/>
-    <hyperlink ref="H100" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C523094A-D799-4C05-BCB7-37B0F52ACFEB}"/>
-    <hyperlink ref="H101" r:id="rId100" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9B2544B7-2F90-4077-8BE4-351C81B91E6D}"/>
+    <hyperlink ref="I2" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0FCBDF7F-DBCD-449D-AA2E-06185888F985}"/>
+    <hyperlink ref="I3" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FF73F192-9590-488D-A75A-2E0B31E9222F}"/>
+    <hyperlink ref="I4" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2DB990CC-FAC5-45FF-945E-3759CDA1E0A2}"/>
+    <hyperlink ref="I5" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{25973EA4-5900-4AC9-8D4F-CA1C33271EB7}"/>
+    <hyperlink ref="I6" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF1DEE4C-DA5A-4C09-B41B-009247983E60}"/>
+    <hyperlink ref="I7" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5F752DEE-B49F-4390-ABF1-6BB2F79E5304}"/>
+    <hyperlink ref="I8" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5469E140-AFE5-46EC-9612-45B45C6161A9}"/>
+    <hyperlink ref="I9" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DE74E478-E6A1-4292-9E54-DAF048A34D02}"/>
+    <hyperlink ref="I10" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4487A71F-4709-4920-ACB1-91E07B9D18B8}"/>
+    <hyperlink ref="I11" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FFFA4705-F484-4B3E-93A1-A9E47BB54CB9}"/>
+    <hyperlink ref="I12" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{88612F3B-E50E-4D82-B45F-A793DDF84A37}"/>
+    <hyperlink ref="I13" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CAE279EC-B962-42D3-9529-7851F75A61F8}"/>
+    <hyperlink ref="I14" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{ADF08FAB-2C1D-440D-BBBD-83F01ADFD5AA}"/>
+    <hyperlink ref="I15" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DBF2AF88-58FD-4DBE-B8E9-75831EE171CD}"/>
+    <hyperlink ref="I16" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0C6E3BF0-AC54-4B80-90F8-33D9B305172B}"/>
+    <hyperlink ref="I17" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8F0CB904-1B5D-437D-BF55-F9F69DD30167}"/>
+    <hyperlink ref="I18" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C238411D-AA75-4757-8DB0-7FFF69DDFB8A}"/>
+    <hyperlink ref="I19" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2CF67AD9-AC37-4A2C-9F0C-B88919CE0F0B}"/>
+    <hyperlink ref="I20" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2365DA53-A1B6-4663-84F1-81578502F133}"/>
+    <hyperlink ref="I21" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{27C7D044-2183-4716-89B4-C8035A5BDACD}"/>
+    <hyperlink ref="I22" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9E80976F-467A-4B3F-BCF7-5FEF9BF0C8AE}"/>
+    <hyperlink ref="I23" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF8104DA-29E5-48F8-AFED-A25C0810F9F1}"/>
+    <hyperlink ref="I24" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B3E70961-470C-4C29-85A5-D74EDE38D151}"/>
+    <hyperlink ref="I25" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{38E86826-A211-494A-B6B9-1B69DDA2EFF7}"/>
+    <hyperlink ref="I26" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1F20F8DA-CB16-474B-A4B9-E1DE8EF7B09B}"/>
+    <hyperlink ref="I27" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2FD70308-BDB7-4249-A039-5D067660BFD6}"/>
+    <hyperlink ref="I28" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EA7880BB-4407-4622-9350-159221423B3B}"/>
+    <hyperlink ref="I29" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DB53A627-9823-4A01-A33A-A9D5FE8B2AAC}"/>
+    <hyperlink ref="I30" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F0F55E47-3169-4DEA-8A5D-DAE098E7AA0E}"/>
+    <hyperlink ref="I31" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{73A5B96C-ED9A-4AD1-9E59-E94722FC6C4A}"/>
+    <hyperlink ref="I32" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{69FD3ECA-E6CA-451D-B9DC-3E388750B256}"/>
+    <hyperlink ref="I33" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{334F12FE-5699-40ED-A7EF-B9FDF8878812}"/>
+    <hyperlink ref="I34" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{696173DE-241C-4BEF-8A3A-85997AEEDB99}"/>
+    <hyperlink ref="I35" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{55928F6D-FAA5-45BC-B738-422AD9F475DF}"/>
+    <hyperlink ref="I36" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A1DF03D6-97B6-4086-B93A-954D2A825E10}"/>
+    <hyperlink ref="I37" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4D5F3AF4-2725-43BD-AA9B-9523987533AC}"/>
+    <hyperlink ref="I38" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8A208B5A-1C1B-43DD-B2B2-FE5CBAD35495}"/>
+    <hyperlink ref="I39" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C529394C-3620-4427-A2BF-4292E38557FC}"/>
+    <hyperlink ref="I40" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BDDECC2B-E9AE-47C6-A23C-2DA7B59E7077}"/>
+    <hyperlink ref="I41" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FD5C0161-5CEB-4F94-82B3-E067DE66ED04}"/>
+    <hyperlink ref="I42" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{143ECA98-C8BA-4897-B755-588898AC192E}"/>
+    <hyperlink ref="I43" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8F88F95-8B05-4AB3-9866-9C70E9B2A4E4}"/>
+    <hyperlink ref="I44" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F124A78A-547A-48A0-B7F2-BCD018B97195}"/>
+    <hyperlink ref="I45" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{62A5BAA4-50D8-4BF4-AE64-6D2CC7E9DE07}"/>
+    <hyperlink ref="I46" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{84982593-6A7A-48C4-929C-73648C3B107A}"/>
+    <hyperlink ref="I47" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E607F40D-AB62-490A-9B14-A32A120E28A5}"/>
+    <hyperlink ref="I48" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{71AFF0FF-4AFD-4274-9B0C-B518AE9D4FBB}"/>
+    <hyperlink ref="I49" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{22943615-22F6-43D7-8D6B-D83D57A9668E}"/>
+    <hyperlink ref="I50" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{513EACCF-D581-414C-9FE6-7D531B61A162}"/>
+    <hyperlink ref="I51" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C6ECBB6-FF10-4B7E-9D81-A42EF84AA8E1}"/>
+    <hyperlink ref="I52" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A44F4C23-317F-411D-97DE-90D8A4FB33E9}"/>
+    <hyperlink ref="I53" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F680E46D-8C1F-4821-8B8A-DDB1C60E2649}"/>
+    <hyperlink ref="I54" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B47BF1C6-4B29-4841-BC81-7A9F9167CEA0}"/>
+    <hyperlink ref="I55" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F15A7166-2A15-4E22-976C-5C9DEEE00387}"/>
+    <hyperlink ref="I56" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{03311C28-542E-4A06-8A69-E0753F94342C}"/>
+    <hyperlink ref="I57" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B89816E6-2DB1-4559-8390-72D5BB3EC59F}"/>
+    <hyperlink ref="I58" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5EF32F46-F67E-42FC-8F23-64E2DFC818BE}"/>
+    <hyperlink ref="I59" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{47BD76DB-B7EE-4AA8-AE0A-70B28E660954}"/>
+    <hyperlink ref="I60" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CDC78262-2229-4847-B303-813B574F8EE5}"/>
+    <hyperlink ref="I61" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5B97DFF-6CC1-4A69-A9FE-DD1C99DACF50}"/>
+    <hyperlink ref="I62" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5E77F0A-3557-40D8-B8A3-577FACDE056B}"/>
+    <hyperlink ref="I63" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{70FBCE56-656D-477A-83F4-0AFA04A808FC}"/>
+    <hyperlink ref="I64" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{93731BA7-B2A0-4776-965E-17A7B1BAB201}"/>
+    <hyperlink ref="I65" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C410A9FA-539C-4E83-B463-FA90104A0A39}"/>
+    <hyperlink ref="I66" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{610F377F-834E-4CF4-8B3C-F0A4DC0498C2}"/>
+    <hyperlink ref="I67" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C14AED96-01F8-47A5-B7FE-D6B1A3B3EC3B}"/>
+    <hyperlink ref="I68" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8FABA8B0-3CD1-4546-95C2-BAF0FADE3597}"/>
+    <hyperlink ref="I69" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A74CDF5A-0BDB-43A0-976C-6361A1904602}"/>
+    <hyperlink ref="I70" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B1D3426F-0142-45CE-939B-8C055B9F229C}"/>
+    <hyperlink ref="I71" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E411C4D5-8F83-437F-8C4D-B86654CB559D}"/>
+    <hyperlink ref="I72" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0F119914-F3E1-4824-9792-A0A357F0C69B}"/>
+    <hyperlink ref="I73" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D32D0D21-2612-4845-8CAC-6D25352EF5D3}"/>
+    <hyperlink ref="I74" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CA051FA0-0A47-4B67-81A9-16F2D79D0081}"/>
+    <hyperlink ref="I75" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B7F56C90-456C-440F-BDFA-45F01F1AF565}"/>
+    <hyperlink ref="I76" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{93C00ACA-C3D2-460C-B9DA-117BDA833187}"/>
+    <hyperlink ref="I77" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8F3479D-3681-4B1E-BCE5-4E0133B2E36D}"/>
+    <hyperlink ref="I78" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DFEB60E2-96C4-4BA7-AF58-EF7581E3E37A}"/>
+    <hyperlink ref="I79" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5CF0FB32-CDC9-4C8D-89C7-A6FF4095C4F9}"/>
+    <hyperlink ref="I80" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3A85C454-9ABF-4536-A3BD-675C7034DE1C}"/>
+    <hyperlink ref="I81" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{91B4B64E-1B8A-4483-A731-0EE302C8EEC7}"/>
+    <hyperlink ref="I82" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5B6B187F-6E1C-4D7D-A171-76E12F010408}"/>
+    <hyperlink ref="I83" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FAA64865-36F1-41F1-BB4D-5F9E691EF208}"/>
+    <hyperlink ref="I84" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C544D59B-4E38-447B-88DE-6C9AE6A8284F}"/>
+    <hyperlink ref="I85" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DC777E21-D4B6-4035-8E42-23DA33C9C087}"/>
+    <hyperlink ref="I86" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2A2E1A6D-86FE-4987-9AB4-54B7C971DFAA}"/>
+    <hyperlink ref="I87" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B827DB21-242B-410B-9591-CBE07C83FDFD}"/>
+    <hyperlink ref="I88" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F57C9182-5D3B-4E46-BC40-46A3D8E627D3}"/>
+    <hyperlink ref="I89" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2554A8C1-62DA-44DF-BC74-A27CE8F7BFBC}"/>
+    <hyperlink ref="I90" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D640E482-9F19-4D2A-B812-FBB54A9504A1}"/>
+    <hyperlink ref="I91" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C457E0D7-1278-44E9-932C-B24EF3343FC3}"/>
+    <hyperlink ref="I92" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{696D2CB9-2D96-486D-9F75-7376DE1F0AEB}"/>
+    <hyperlink ref="I93" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{383E64D0-D9EC-437F-A3B7-DA69FBA1E00E}"/>
+    <hyperlink ref="I94" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{615FC7F9-F46E-45A6-BBA2-B72742CA4B41}"/>
+    <hyperlink ref="I95" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9838F64C-F593-4678-9DEC-7CCAF67151FA}"/>
+    <hyperlink ref="I96" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A596E95E-9814-454A-B1E7-DEF21E58E6CF}"/>
+    <hyperlink ref="I97" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A193D687-4899-45DD-88BB-7DBAA2A9C895}"/>
+    <hyperlink ref="I98" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C585F8E2-8893-49F5-BEC8-9ABD3B0B5208}"/>
+    <hyperlink ref="I99" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CD864CC2-420B-4384-B326-3C50D3018E3E}"/>
+    <hyperlink ref="I100" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C523094A-D799-4C05-BCB7-37B0F52ACFEB}"/>
+    <hyperlink ref="I101" r:id="rId100" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9B2544B7-2F90-4077-8BE4-351C81B91E6D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -32928,7 +33045,7 @@
       <c r="G6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="25" t="s">
         <v>256</v>
       </c>
     </row>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7945384-786B-4823-BB04-B02BDA59EEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6125F57C-E4AF-4425-9F82-72384BB1E799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,30 +34,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="258">
   <si>
     <t>BIN</t>
   </si>
@@ -812,9 +790,6 @@
     <t>data_num</t>
   </si>
   <si>
-    <t>TCB - 449</t>
-  </si>
-  <si>
     <t>Templa</t>
   </si>
   <si>
@@ -843,7 +818,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ [$đ-42A]"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,12 +890,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1032,7 +1001,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1074,16 +1043,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1095,6 +1061,45 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1125,42 +1130,6 @@
         <outline val="0"/>
         <shadow val="0"/>
         <u/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
@@ -1357,109 +1326,32 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-  <types>
-    <type name="_webimage">
-      <keyFlags>
-        <key name="WebImageIdentifier">
-          <flag name="ShowInCardView" value="0"/>
-        </key>
-      </keyFlags>
-    </type>
-  </types>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdRichValueWebImage.xml><?xml version="1.0" encoding="utf-8"?>
-<webImagesSrd xmlns="http://schemas.microsoft.com/office/spreadsheetml/2020/richdatawebimage" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <webImageSrd>
-    <address r:id="rId1"/>
-  </webImageSrd>
-</webImagesSrd>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_webimage">
-    <k n="WebImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-    <k n="ComputedImage" t="b"/>
-    <k n="ImageSizing" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7F0749FA-984C-46C9-AAB8-7ABB595D4FB8}" name="Table1" displayName="Table1" ref="A1:J101" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:J101" xr:uid="{7F0749FA-984C-46C9-AAB8-7ABB595D4FB8}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F8D53C57-7078-4EF6-9C73-35B4D8C4988B}" name="data__id" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{390DCB3F-4D6D-4198-B590-711049680796}" name="list_name" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{576DFB3C-BE82-459C-804A-245AC638C8B8}" name="data_num" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{A98793EC-C017-48A1-96BE-B60CD452DAC7}" name="name_ac" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{2B86B3E1-90A9-4410-87A1-76EA940DC021}" name="data__name" dataDxfId="6">
-      <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,2,0)),"-")</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{390DCB3F-4D6D-4198-B590-711049680796}" name="list_name" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D4B6D36E-F5B4-4050-84DA-B62E678E55BF}" name="data__code" dataDxfId="5">
-      <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,3,0)),"-")</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{576DFB3C-BE82-459C-804A-245AC638C8B8}" name="data_num" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{A98793EC-C017-48A1-96BE-B60CD452DAC7}" name="name_ac" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{2B86B3E1-90A9-4410-87A1-76EA940DC021}" name="data__name" dataDxfId="2">
+      <calculatedColumnFormula>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F102E323-9AC5-4420-B847-1C14F7757293}" name="data__bin" dataDxfId="4">
+    <tableColumn id="4" xr3:uid="{D4B6D36E-F5B4-4050-84DA-B62E678E55BF}" name="data__code" dataDxfId="1">
+      <calculatedColumnFormula>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{F102E323-9AC5-4420-B847-1C14F7757293}" name="data__bin" dataDxfId="6">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DB8F4E18-D2FD-4EA2-B28D-DA53D8A12D89}" name="data__shortName" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{DB8F4E18-D2FD-4EA2-B28D-DA53D8A12D89}" name="data__shortName" dataDxfId="5">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{EA429D0C-4231-435B-91FE-DAD0B13369DF}" name="data__logo" dataDxfId="2">
+    <tableColumn id="7" xr3:uid="{EA429D0C-4231-435B-91FE-DAD0B13369DF}" name="data__logo" dataDxfId="4">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BD47F35F-8B5D-4304-BED9-AA9B06C54ACA}" name="data__short_name" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{BD47F35F-8B5D-4304-BED9-AA9B06C54ACA}" name="data__short_name" dataDxfId="3">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1699,7 +1591,7 @@
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="23">
+      <c r="B1" s="22">
         <v>25000</v>
       </c>
       <c r="C1" s="2"/>
@@ -1730,9 +1622,9 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="5" t="e">
         <f>+VLOOKUP($A$1,List_bank!$B:$G,5,0)</f>
-        <v>ACB</v>
+        <v>#N/A</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1761,9 +1653,9 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="5" t="e">
         <f>+VLOOKUP($A$1,List_bank!$B:$G,2,0)</f>
-        <v>81051</v>
+        <v>#N/A</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1792,7 +1684,7 @@
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="2"/>
@@ -1819,13 +1711,13 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="6" t="str">
+      <c r="A5" s="6" t="e">
         <f>HYPERLINK(B5, "🔗 Link_qr")</f>
-        <v>🔗 Link_qr</v>
-      </c>
-      <c r="B5" s="7" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B5" s="7" t="e">
         <f>"https://img.vietqr.io/image/"&amp;B2&amp;"-"&amp;B3&amp;"-"&amp;B4&amp;".png?amount="&amp;B1&amp;""</f>
-        <v>https://img.vietqr.io/image/ACB-81051-BdT8CDO.png?amount=25000</v>
+        <v>#N/A</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1888,9 +1780,9 @@
         <f>HYPERLINK("https://my.payos.vn/", "🔗 Pay_os")</f>
         <v>🔗 Pay_os</v>
       </c>
-      <c r="B7" s="26" t="e" vm="1">
-        <f ca="1">_xlfn.IMAGE(B5)</f>
-        <v>#VALUE!</v>
+      <c r="B7" s="25" t="e">
+        <f>_xlfn.IMAGE(B5)</f>
+        <v>#N/A</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1922,7 +1814,7 @@
         <f>HYPERLINK("https://my.vietqr.io/", "🔗 Template")</f>
         <v>🔗 Template</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1950,7 +1842,7 @@
     </row>
     <row r="9" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="11"/>
-      <c r="B9" s="27"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1978,7 +1870,7 @@
     </row>
     <row r="10" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2"/>
-      <c r="B10" s="27"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2006,7 +1898,7 @@
     </row>
     <row r="11" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2"/>
-      <c r="B11" s="27"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2034,7 +1926,7 @@
     </row>
     <row r="12" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2"/>
-      <c r="B12" s="27"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -2062,7 +1954,7 @@
     </row>
     <row r="13" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2"/>
-      <c r="B13" s="27"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -2090,7 +1982,7 @@
     </row>
     <row r="14" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2"/>
-      <c r="B14" s="27"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -2118,7 +2010,7 @@
     </row>
     <row r="15" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2"/>
-      <c r="B15" s="27"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -2146,7 +2038,7 @@
     </row>
     <row r="16" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2"/>
-      <c r="B16" s="27"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -2174,7 +2066,7 @@
     </row>
     <row r="17" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2"/>
-      <c r="B17" s="27"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -2202,7 +2094,7 @@
     </row>
     <row r="18" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2"/>
-      <c r="B18" s="27"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -2230,7 +2122,7 @@
     </row>
     <row r="19" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="2"/>
-      <c r="B19" s="27"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -2258,7 +2150,7 @@
     </row>
     <row r="20" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="2"/>
-      <c r="B20" s="27"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -29705,7 +29597,7 @@
     <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="72" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" customWidth="1"/>
@@ -29724,7 +29616,7 @@
         <v>250</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E1" s="16" t="s">
         <v>4</v>
@@ -29745,93 +29637,98 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19">
-        <v>2</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="19">
-        <v>81051</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>258</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="21">
+        <v>38</v>
+      </c>
+      <c r="B2" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>TCB</v>
+      </c>
+      <c r="C2" s="21">
+        <v>44699999999</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>257</v>
       </c>
       <c r="E2" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,2,0)),"-")</f>
-        <v>Ngân hàng TMCP Á Châu</v>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <v>Techcombank</v>
       </c>
       <c r="F2" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,3,0)),"-")</f>
-        <v>ACB</v>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>TCB</v>
       </c>
       <c r="G2" s="19">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970416</v>
+        <v>970407</v>
       </c>
       <c r="H2" s="19" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>ACB</v>
+        <v>Techcombank</v>
       </c>
       <c r="I2" s="20" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/ACB.png</v>
+        <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J2" s="19" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>ACB</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19">
-        <v>38</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>251</v>
+        <v>Techcombank</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="21">
+        <v>43</v>
+      </c>
+      <c r="B3" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>VCB</v>
       </c>
       <c r="C3" s="21">
-        <v>44699999999</v>
+        <v>1031451081</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E3" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,2,0)),"-")</f>
-        <v>Ngân hàng TMCP Kỹ thương Việt Nam</v>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <v>Vietcombank</v>
       </c>
       <c r="F3" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,3,0)),"-")</f>
-        <v>TCB</v>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>VCB</v>
       </c>
       <c r="G3" s="19">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970407</v>
+        <v>970436</v>
       </c>
       <c r="H3" s="19" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="I3" s="20" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/TCB.png</v>
+        <v>https://cdn.vietqr.io/img/VCB.png</v>
       </c>
       <c r="J3" s="19" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Techcombank</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
+        <v>Vietcombank</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="21"/>
+      <c r="B4" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F4" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G4" s="19" t="str">
@@ -29851,17 +29748,20 @@
         <v>-</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F5" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G5" s="19" t="str">
@@ -29881,17 +29781,20 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F6" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G6" s="19" t="str">
@@ -29913,15 +29816,18 @@
     </row>
     <row r="7" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
+      <c r="B7" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
       <c r="E7" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F7" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G7" s="19" t="str">
@@ -29943,15 +29849,18 @@
     </row>
     <row r="8" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
+      <c r="B8" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" s="19" t="str">
@@ -29973,15 +29882,18 @@
     </row>
     <row r="9" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
+      <c r="B9" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F9" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G9" s="19" t="str">
@@ -30003,15 +29915,18 @@
     </row>
     <row r="10" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
+      <c r="B10" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F10" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G10" s="19" t="str">
@@ -30033,15 +29948,18 @@
     </row>
     <row r="11" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
+      <c r="B11" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F11" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G11" s="19" t="str">
@@ -30063,15 +29981,18 @@
     </row>
     <row r="12" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
+      <c r="B12" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F12" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G12" s="19" t="str">
@@ -30093,15 +30014,18 @@
     </row>
     <row r="13" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
+      <c r="B13" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F13" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G13" s="19" t="str">
@@ -30123,15 +30047,18 @@
     </row>
     <row r="14" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
+      <c r="B14" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F14" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G14" s="19" t="str">
@@ -30153,15 +30080,18 @@
     </row>
     <row r="15" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
+      <c r="B15" s="19" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F15" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G15" s="19" t="str">
@@ -30182,16 +30112,19 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F16" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G16" s="19" t="str">
@@ -30212,16 +30145,19 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F17" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G17" s="19" t="str">
@@ -30242,16 +30178,19 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F18" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G18" s="19" t="str">
@@ -30272,16 +30211,19 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F19" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G19" s="19" t="str">
@@ -30302,16 +30244,19 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F20" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G20" s="19" t="str">
@@ -30332,16 +30277,19 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F21" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G21" s="19" t="str">
@@ -30362,16 +30310,19 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F22" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G22" s="19" t="str">
@@ -30392,16 +30343,19 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F23" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G23" s="19" t="str">
@@ -30422,16 +30376,19 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F24" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G24" s="19" t="str">
@@ -30452,16 +30409,19 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F25" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G25" s="19" t="str">
@@ -30482,16 +30442,19 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F26" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G26" s="19" t="str">
@@ -30512,16 +30475,19 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F27" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G27" s="19" t="str">
@@ -30542,16 +30508,19 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F28" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G28" s="19" t="str">
@@ -30572,16 +30541,19 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F29" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G29" s="19" t="str">
@@ -30602,16 +30574,19 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F30" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G30" s="19" t="str">
@@ -30632,16 +30607,19 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F31" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G31" s="19" t="str">
@@ -30662,16 +30640,19 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F32" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G32" s="19" t="str">
@@ -30692,16 +30673,19 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F33" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G33" s="19" t="str">
@@ -30722,16 +30706,19 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F34" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G34" s="19" t="str">
@@ -30752,16 +30739,19 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F35" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G35" s="19" t="str">
@@ -30782,16 +30772,19 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F36" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G36" s="19" t="str">
@@ -30812,16 +30805,19 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F37" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G37" s="19" t="str">
@@ -30842,16 +30838,19 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F38" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G38" s="19" t="str">
@@ -30872,16 +30871,19 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F39" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G39" s="19" t="str">
@@ -30902,16 +30904,19 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F40" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G40" s="19" t="str">
@@ -30932,16 +30937,19 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F41" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G41" s="19" t="str">
@@ -30962,16 +30970,19 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F42" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G42" s="19" t="str">
@@ -30992,16 +31003,19 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F43" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G43" s="19" t="str">
@@ -31022,16 +31036,19 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F44" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G44" s="19" t="str">
@@ -31052,16 +31069,19 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
+      <c r="A45" s="21"/>
+      <c r="B45" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F45" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G45" s="19" t="str">
@@ -31082,16 +31102,19 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
+      <c r="A46" s="21"/>
+      <c r="B46" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F46" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G46" s="19" t="str">
@@ -31112,16 +31135,19 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F47" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G47" s="19" t="str">
@@ -31142,16 +31168,19 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F48" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G48" s="19" t="str">
@@ -31172,16 +31201,19 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F49" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G49" s="19" t="str">
@@ -31202,16 +31234,19 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F50" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G50" s="19" t="str">
@@ -31232,16 +31267,19 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="22"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F51" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G51" s="19" t="str">
@@ -31262,16 +31300,19 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="22"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F52" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G52" s="19" t="str">
@@ -31292,16 +31333,19 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F53" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G53" s="19" t="str">
@@ -31322,16 +31366,19 @@
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F54" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G54" s="19" t="str">
@@ -31352,16 +31399,19 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
+      <c r="A55" s="21"/>
+      <c r="B55" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F55" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G55" s="19" t="str">
@@ -31382,16 +31432,19 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
+      <c r="A56" s="21"/>
+      <c r="B56" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F56" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G56" s="19" t="str">
@@ -31412,16 +31465,19 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
+      <c r="A57" s="21"/>
+      <c r="B57" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F57" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G57" s="19" t="str">
@@ -31442,16 +31498,19 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="22"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
+      <c r="A58" s="21"/>
+      <c r="B58" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
       <c r="E58" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F58" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G58" s="19" t="str">
@@ -31472,16 +31531,19 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
+      <c r="A59" s="21"/>
+      <c r="B59" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
       <c r="E59" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F59" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G59" s="19" t="str">
@@ -31502,16 +31564,19 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="22"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
+      <c r="A60" s="21"/>
+      <c r="B60" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
       <c r="E60" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F60" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G60" s="19" t="str">
@@ -31532,16 +31597,19 @@
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
+      <c r="A61" s="21"/>
+      <c r="B61" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
       <c r="E61" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F61" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G61" s="19" t="str">
@@ -31562,16 +31630,19 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
+      <c r="A62" s="21"/>
+      <c r="B62" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
       <c r="E62" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F62" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G62" s="19" t="str">
@@ -31592,16 +31663,19 @@
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
+      <c r="A63" s="21"/>
+      <c r="B63" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
       <c r="E63" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F63" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G63" s="19" t="str">
@@ -31622,16 +31696,19 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
+      <c r="A64" s="21"/>
+      <c r="B64" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
       <c r="E64" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F64" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G64" s="19" t="str">
@@ -31652,16 +31729,19 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="22"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
+      <c r="A65" s="21"/>
+      <c r="B65" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
       <c r="E65" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F65" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G65" s="19" t="str">
@@ -31682,16 +31762,19 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="22"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
+      <c r="A66" s="21"/>
+      <c r="B66" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
       <c r="E66" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F66" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G66" s="19" t="str">
@@ -31712,16 +31795,19 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="22"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
+      <c r="A67" s="21"/>
+      <c r="B67" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
       <c r="E67" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F67" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G67" s="19" t="str">
@@ -31742,16 +31828,19 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
+      <c r="A68" s="21"/>
+      <c r="B68" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
       <c r="E68" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F68" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G68" s="19" t="str">
@@ -31772,16 +31861,19 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="22"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
+      <c r="A69" s="21"/>
+      <c r="B69" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
       <c r="E69" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F69" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G69" s="19" t="str">
@@ -31802,16 +31894,19 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="22"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
+      <c r="A70" s="21"/>
+      <c r="B70" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
       <c r="E70" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F70" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G70" s="19" t="str">
@@ -31832,16 +31927,19 @@
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="22"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
+      <c r="A71" s="21"/>
+      <c r="B71" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
       <c r="E71" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F71" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G71" s="19" t="str">
@@ -31862,16 +31960,19 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="22"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
+      <c r="A72" s="21"/>
+      <c r="B72" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
       <c r="E72" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F72" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G72" s="19" t="str">
@@ -31892,16 +31993,19 @@
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="22"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
+      <c r="A73" s="21"/>
+      <c r="B73" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
       <c r="E73" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F73" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G73" s="19" t="str">
@@ -31922,16 +32026,19 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="22"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
+      <c r="A74" s="21"/>
+      <c r="B74" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
       <c r="E74" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F74" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G74" s="19" t="str">
@@ -31952,16 +32059,19 @@
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="22"/>
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
+      <c r="A75" s="21"/>
+      <c r="B75" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
       <c r="E75" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F75" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G75" s="19" t="str">
@@ -31982,16 +32092,19 @@
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="22"/>
-      <c r="B76" s="22"/>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
+      <c r="A76" s="21"/>
+      <c r="B76" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
       <c r="E76" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F76" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G76" s="19" t="str">
@@ -32012,16 +32125,19 @@
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="22"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
+      <c r="A77" s="21"/>
+      <c r="B77" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
       <c r="E77" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F77" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G77" s="19" t="str">
@@ -32042,16 +32158,19 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="22"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
+      <c r="A78" s="21"/>
+      <c r="B78" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
       <c r="E78" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F78" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G78" s="19" t="str">
@@ -32072,16 +32191,19 @@
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="22"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22"/>
+      <c r="A79" s="21"/>
+      <c r="B79" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
       <c r="E79" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F79" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G79" s="19" t="str">
@@ -32102,16 +32224,19 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="22"/>
-      <c r="B80" s="22"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
+      <c r="A80" s="21"/>
+      <c r="B80" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
       <c r="E80" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F80" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G80" s="19" t="str">
@@ -32132,16 +32257,19 @@
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="22"/>
-      <c r="B81" s="22"/>
-      <c r="C81" s="22"/>
-      <c r="D81" s="22"/>
+      <c r="A81" s="21"/>
+      <c r="B81" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C81" s="21"/>
+      <c r="D81" s="21"/>
       <c r="E81" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F81" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G81" s="19" t="str">
@@ -32162,16 +32290,19 @@
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="22"/>
-      <c r="B82" s="22"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
+      <c r="A82" s="21"/>
+      <c r="B82" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
       <c r="E82" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F82" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G82" s="19" t="str">
@@ -32192,16 +32323,19 @@
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="22"/>
-      <c r="B83" s="22"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
+      <c r="A83" s="21"/>
+      <c r="B83" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
       <c r="E83" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F83" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G83" s="19" t="str">
@@ -32222,16 +32356,19 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="22"/>
-      <c r="B84" s="22"/>
-      <c r="C84" s="22"/>
-      <c r="D84" s="22"/>
+      <c r="A84" s="21"/>
+      <c r="B84" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C84" s="21"/>
+      <c r="D84" s="21"/>
       <c r="E84" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F84" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G84" s="19" t="str">
@@ -32252,16 +32389,19 @@
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="22"/>
-      <c r="B85" s="22"/>
-      <c r="C85" s="22"/>
-      <c r="D85" s="22"/>
+      <c r="A85" s="21"/>
+      <c r="B85" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
       <c r="E85" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F85" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G85" s="19" t="str">
@@ -32282,16 +32422,19 @@
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="22"/>
-      <c r="B86" s="22"/>
-      <c r="C86" s="22"/>
-      <c r="D86" s="22"/>
+      <c r="A86" s="21"/>
+      <c r="B86" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
       <c r="E86" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F86" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G86" s="19" t="str">
@@ -32312,16 +32455,19 @@
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="22"/>
-      <c r="B87" s="22"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="22"/>
+      <c r="A87" s="21"/>
+      <c r="B87" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
       <c r="E87" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F87" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G87" s="19" t="str">
@@ -32342,16 +32488,19 @@
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="22"/>
-      <c r="B88" s="22"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22"/>
+      <c r="A88" s="21"/>
+      <c r="B88" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
       <c r="E88" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F88" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G88" s="19" t="str">
@@ -32372,16 +32521,19 @@
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="22"/>
-      <c r="B89" s="22"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22"/>
+      <c r="A89" s="21"/>
+      <c r="B89" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
       <c r="E89" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F89" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G89" s="19" t="str">
@@ -32402,16 +32554,19 @@
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="22"/>
-      <c r="B90" s="22"/>
-      <c r="C90" s="22"/>
-      <c r="D90" s="22"/>
+      <c r="A90" s="21"/>
+      <c r="B90" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
       <c r="E90" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F90" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G90" s="19" t="str">
@@ -32432,16 +32587,19 @@
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="22"/>
-      <c r="B91" s="22"/>
-      <c r="C91" s="22"/>
-      <c r="D91" s="22"/>
+      <c r="A91" s="21"/>
+      <c r="B91" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
       <c r="E91" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F91" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G91" s="19" t="str">
@@ -32462,16 +32620,19 @@
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="22"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
+      <c r="A92" s="21"/>
+      <c r="B92" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
       <c r="E92" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F92" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G92" s="19" t="str">
@@ -32492,16 +32653,19 @@
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="22"/>
-      <c r="B93" s="22"/>
-      <c r="C93" s="22"/>
-      <c r="D93" s="22"/>
+      <c r="A93" s="21"/>
+      <c r="B93" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C93" s="21"/>
+      <c r="D93" s="21"/>
       <c r="E93" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F93" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G93" s="19" t="str">
@@ -32522,16 +32686,19 @@
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="22"/>
-      <c r="B94" s="22"/>
-      <c r="C94" s="22"/>
-      <c r="D94" s="22"/>
+      <c r="A94" s="21"/>
+      <c r="B94" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
       <c r="E94" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F94" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G94" s="19" t="str">
@@ -32552,16 +32719,19 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="22"/>
-      <c r="B95" s="22"/>
-      <c r="C95" s="22"/>
-      <c r="D95" s="22"/>
+      <c r="A95" s="21"/>
+      <c r="B95" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
       <c r="E95" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F95" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G95" s="19" t="str">
@@ -32582,16 +32752,19 @@
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="22"/>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22"/>
+      <c r="A96" s="21"/>
+      <c r="B96" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C96" s="21"/>
+      <c r="D96" s="21"/>
       <c r="E96" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F96" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G96" s="19" t="str">
@@ -32612,16 +32785,19 @@
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="22"/>
-      <c r="B97" s="22"/>
-      <c r="C97" s="22"/>
-      <c r="D97" s="22"/>
+      <c r="A97" s="21"/>
+      <c r="B97" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
       <c r="E97" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F97" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G97" s="19" t="str">
@@ -32642,16 +32818,19 @@
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="22"/>
-      <c r="B98" s="22"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="22"/>
+      <c r="A98" s="21"/>
+      <c r="B98" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C98" s="21"/>
+      <c r="D98" s="21"/>
       <c r="E98" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F98" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G98" s="19" t="str">
@@ -32672,16 +32851,19 @@
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="22"/>
-      <c r="B99" s="22"/>
-      <c r="C99" s="22"/>
-      <c r="D99" s="22"/>
+      <c r="A99" s="21"/>
+      <c r="B99" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
       <c r="E99" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F99" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G99" s="19" t="str">
@@ -32702,16 +32884,19 @@
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A100" s="22"/>
-      <c r="B100" s="22"/>
-      <c r="C100" s="22"/>
-      <c r="D100" s="22"/>
+      <c r="A100" s="21"/>
+      <c r="B100" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
       <c r="E100" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F100" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G100" s="19" t="str">
@@ -32732,16 +32917,19 @@
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" s="22"/>
-      <c r="B101" s="22"/>
-      <c r="C101" s="22"/>
-      <c r="D101" s="22"/>
+      <c r="A101" s="21"/>
+      <c r="B101" s="21" t="str">
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
       <c r="E101" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,2,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F101" s="19" t="str">
-        <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G101" s="19" t="str">
@@ -32763,111 +32951,111 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G101 A4 A2:D3 A5:D15" xr:uid="{A89C4704-896A-47DC-A7B5-29F469ADEA0A}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A7:D15 G2:G101" xr:uid="{A89C4704-896A-47DC-A7B5-29F469ADEA0A}">
       <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0FCBDF7F-DBCD-449D-AA2E-06185888F985}"/>
-    <hyperlink ref="I3" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FF73F192-9590-488D-A75A-2E0B31E9222F}"/>
-    <hyperlink ref="I4" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2DB990CC-FAC5-45FF-945E-3759CDA1E0A2}"/>
-    <hyperlink ref="I5" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{25973EA4-5900-4AC9-8D4F-CA1C33271EB7}"/>
-    <hyperlink ref="I6" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF1DEE4C-DA5A-4C09-B41B-009247983E60}"/>
-    <hyperlink ref="I7" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5F752DEE-B49F-4390-ABF1-6BB2F79E5304}"/>
-    <hyperlink ref="I8" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5469E140-AFE5-46EC-9612-45B45C6161A9}"/>
-    <hyperlink ref="I9" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DE74E478-E6A1-4292-9E54-DAF048A34D02}"/>
-    <hyperlink ref="I10" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4487A71F-4709-4920-ACB1-91E07B9D18B8}"/>
-    <hyperlink ref="I11" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FFFA4705-F484-4B3E-93A1-A9E47BB54CB9}"/>
-    <hyperlink ref="I12" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{88612F3B-E50E-4D82-B45F-A793DDF84A37}"/>
-    <hyperlink ref="I13" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CAE279EC-B962-42D3-9529-7851F75A61F8}"/>
-    <hyperlink ref="I14" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{ADF08FAB-2C1D-440D-BBBD-83F01ADFD5AA}"/>
-    <hyperlink ref="I15" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DBF2AF88-58FD-4DBE-B8E9-75831EE171CD}"/>
-    <hyperlink ref="I16" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0C6E3BF0-AC54-4B80-90F8-33D9B305172B}"/>
-    <hyperlink ref="I17" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8F0CB904-1B5D-437D-BF55-F9F69DD30167}"/>
-    <hyperlink ref="I18" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C238411D-AA75-4757-8DB0-7FFF69DDFB8A}"/>
-    <hyperlink ref="I19" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2CF67AD9-AC37-4A2C-9F0C-B88919CE0F0B}"/>
-    <hyperlink ref="I20" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2365DA53-A1B6-4663-84F1-81578502F133}"/>
-    <hyperlink ref="I21" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{27C7D044-2183-4716-89B4-C8035A5BDACD}"/>
-    <hyperlink ref="I22" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9E80976F-467A-4B3F-BCF7-5FEF9BF0C8AE}"/>
-    <hyperlink ref="I23" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF8104DA-29E5-48F8-AFED-A25C0810F9F1}"/>
-    <hyperlink ref="I24" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B3E70961-470C-4C29-85A5-D74EDE38D151}"/>
-    <hyperlink ref="I25" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{38E86826-A211-494A-B6B9-1B69DDA2EFF7}"/>
-    <hyperlink ref="I26" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1F20F8DA-CB16-474B-A4B9-E1DE8EF7B09B}"/>
-    <hyperlink ref="I27" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2FD70308-BDB7-4249-A039-5D067660BFD6}"/>
-    <hyperlink ref="I28" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EA7880BB-4407-4622-9350-159221423B3B}"/>
-    <hyperlink ref="I29" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DB53A627-9823-4A01-A33A-A9D5FE8B2AAC}"/>
-    <hyperlink ref="I30" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F0F55E47-3169-4DEA-8A5D-DAE098E7AA0E}"/>
-    <hyperlink ref="I31" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{73A5B96C-ED9A-4AD1-9E59-E94722FC6C4A}"/>
-    <hyperlink ref="I32" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{69FD3ECA-E6CA-451D-B9DC-3E388750B256}"/>
-    <hyperlink ref="I33" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{334F12FE-5699-40ED-A7EF-B9FDF8878812}"/>
-    <hyperlink ref="I34" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{696173DE-241C-4BEF-8A3A-85997AEEDB99}"/>
-    <hyperlink ref="I35" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{55928F6D-FAA5-45BC-B738-422AD9F475DF}"/>
-    <hyperlink ref="I36" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A1DF03D6-97B6-4086-B93A-954D2A825E10}"/>
-    <hyperlink ref="I37" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4D5F3AF4-2725-43BD-AA9B-9523987533AC}"/>
-    <hyperlink ref="I38" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8A208B5A-1C1B-43DD-B2B2-FE5CBAD35495}"/>
-    <hyperlink ref="I39" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C529394C-3620-4427-A2BF-4292E38557FC}"/>
-    <hyperlink ref="I40" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BDDECC2B-E9AE-47C6-A23C-2DA7B59E7077}"/>
-    <hyperlink ref="I41" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FD5C0161-5CEB-4F94-82B3-E067DE66ED04}"/>
-    <hyperlink ref="I42" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{143ECA98-C8BA-4897-B755-588898AC192E}"/>
-    <hyperlink ref="I43" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8F88F95-8B05-4AB3-9866-9C70E9B2A4E4}"/>
-    <hyperlink ref="I44" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F124A78A-547A-48A0-B7F2-BCD018B97195}"/>
-    <hyperlink ref="I45" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{62A5BAA4-50D8-4BF4-AE64-6D2CC7E9DE07}"/>
-    <hyperlink ref="I46" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{84982593-6A7A-48C4-929C-73648C3B107A}"/>
-    <hyperlink ref="I47" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E607F40D-AB62-490A-9B14-A32A120E28A5}"/>
-    <hyperlink ref="I48" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{71AFF0FF-4AFD-4274-9B0C-B518AE9D4FBB}"/>
-    <hyperlink ref="I49" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{22943615-22F6-43D7-8D6B-D83D57A9668E}"/>
-    <hyperlink ref="I50" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{513EACCF-D581-414C-9FE6-7D531B61A162}"/>
-    <hyperlink ref="I51" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C6ECBB6-FF10-4B7E-9D81-A42EF84AA8E1}"/>
-    <hyperlink ref="I52" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A44F4C23-317F-411D-97DE-90D8A4FB33E9}"/>
-    <hyperlink ref="I53" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F680E46D-8C1F-4821-8B8A-DDB1C60E2649}"/>
-    <hyperlink ref="I54" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B47BF1C6-4B29-4841-BC81-7A9F9167CEA0}"/>
-    <hyperlink ref="I55" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F15A7166-2A15-4E22-976C-5C9DEEE00387}"/>
-    <hyperlink ref="I56" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{03311C28-542E-4A06-8A69-E0753F94342C}"/>
-    <hyperlink ref="I57" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B89816E6-2DB1-4559-8390-72D5BB3EC59F}"/>
-    <hyperlink ref="I58" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5EF32F46-F67E-42FC-8F23-64E2DFC818BE}"/>
-    <hyperlink ref="I59" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{47BD76DB-B7EE-4AA8-AE0A-70B28E660954}"/>
-    <hyperlink ref="I60" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CDC78262-2229-4847-B303-813B574F8EE5}"/>
-    <hyperlink ref="I61" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5B97DFF-6CC1-4A69-A9FE-DD1C99DACF50}"/>
-    <hyperlink ref="I62" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5E77F0A-3557-40D8-B8A3-577FACDE056B}"/>
-    <hyperlink ref="I63" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{70FBCE56-656D-477A-83F4-0AFA04A808FC}"/>
-    <hyperlink ref="I64" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{93731BA7-B2A0-4776-965E-17A7B1BAB201}"/>
-    <hyperlink ref="I65" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C410A9FA-539C-4E83-B463-FA90104A0A39}"/>
-    <hyperlink ref="I66" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{610F377F-834E-4CF4-8B3C-F0A4DC0498C2}"/>
-    <hyperlink ref="I67" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C14AED96-01F8-47A5-B7FE-D6B1A3B3EC3B}"/>
-    <hyperlink ref="I68" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8FABA8B0-3CD1-4546-95C2-BAF0FADE3597}"/>
-    <hyperlink ref="I69" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A74CDF5A-0BDB-43A0-976C-6361A1904602}"/>
-    <hyperlink ref="I70" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B1D3426F-0142-45CE-939B-8C055B9F229C}"/>
-    <hyperlink ref="I71" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E411C4D5-8F83-437F-8C4D-B86654CB559D}"/>
-    <hyperlink ref="I72" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0F119914-F3E1-4824-9792-A0A357F0C69B}"/>
-    <hyperlink ref="I73" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D32D0D21-2612-4845-8CAC-6D25352EF5D3}"/>
-    <hyperlink ref="I74" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CA051FA0-0A47-4B67-81A9-16F2D79D0081}"/>
-    <hyperlink ref="I75" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B7F56C90-456C-440F-BDFA-45F01F1AF565}"/>
-    <hyperlink ref="I76" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{93C00ACA-C3D2-460C-B9DA-117BDA833187}"/>
-    <hyperlink ref="I77" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8F3479D-3681-4B1E-BCE5-4E0133B2E36D}"/>
-    <hyperlink ref="I78" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DFEB60E2-96C4-4BA7-AF58-EF7581E3E37A}"/>
-    <hyperlink ref="I79" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5CF0FB32-CDC9-4C8D-89C7-A6FF4095C4F9}"/>
-    <hyperlink ref="I80" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3A85C454-9ABF-4536-A3BD-675C7034DE1C}"/>
-    <hyperlink ref="I81" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{91B4B64E-1B8A-4483-A731-0EE302C8EEC7}"/>
-    <hyperlink ref="I82" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5B6B187F-6E1C-4D7D-A171-76E12F010408}"/>
-    <hyperlink ref="I83" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FAA64865-36F1-41F1-BB4D-5F9E691EF208}"/>
-    <hyperlink ref="I84" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C544D59B-4E38-447B-88DE-6C9AE6A8284F}"/>
-    <hyperlink ref="I85" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DC777E21-D4B6-4035-8E42-23DA33C9C087}"/>
-    <hyperlink ref="I86" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2A2E1A6D-86FE-4987-9AB4-54B7C971DFAA}"/>
-    <hyperlink ref="I87" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B827DB21-242B-410B-9591-CBE07C83FDFD}"/>
-    <hyperlink ref="I88" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F57C9182-5D3B-4E46-BC40-46A3D8E627D3}"/>
-    <hyperlink ref="I89" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2554A8C1-62DA-44DF-BC74-A27CE8F7BFBC}"/>
-    <hyperlink ref="I90" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D640E482-9F19-4D2A-B812-FBB54A9504A1}"/>
-    <hyperlink ref="I91" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C457E0D7-1278-44E9-932C-B24EF3343FC3}"/>
-    <hyperlink ref="I92" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{696D2CB9-2D96-486D-9F75-7376DE1F0AEB}"/>
-    <hyperlink ref="I93" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{383E64D0-D9EC-437F-A3B7-DA69FBA1E00E}"/>
-    <hyperlink ref="I94" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{615FC7F9-F46E-45A6-BBA2-B72742CA4B41}"/>
-    <hyperlink ref="I95" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9838F64C-F593-4678-9DEC-7CCAF67151FA}"/>
-    <hyperlink ref="I96" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A596E95E-9814-454A-B1E7-DEF21E58E6CF}"/>
-    <hyperlink ref="I97" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A193D687-4899-45DD-88BB-7DBAA2A9C895}"/>
-    <hyperlink ref="I98" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C585F8E2-8893-49F5-BEC8-9ABD3B0B5208}"/>
-    <hyperlink ref="I99" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CD864CC2-420B-4384-B326-3C50D3018E3E}"/>
-    <hyperlink ref="I100" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C523094A-D799-4C05-BCB7-37B0F52ACFEB}"/>
-    <hyperlink ref="I101" r:id="rId100" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9B2544B7-2F90-4077-8BE4-351C81B91E6D}"/>
+    <hyperlink ref="I7" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5F752DEE-B49F-4390-ABF1-6BB2F79E5304}"/>
+    <hyperlink ref="I8" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5469E140-AFE5-46EC-9612-45B45C6161A9}"/>
+    <hyperlink ref="I9" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DE74E478-E6A1-4292-9E54-DAF048A34D02}"/>
+    <hyperlink ref="I10" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4487A71F-4709-4920-ACB1-91E07B9D18B8}"/>
+    <hyperlink ref="I11" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FFFA4705-F484-4B3E-93A1-A9E47BB54CB9}"/>
+    <hyperlink ref="I12" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{88612F3B-E50E-4D82-B45F-A793DDF84A37}"/>
+    <hyperlink ref="I13" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CAE279EC-B962-42D3-9529-7851F75A61F8}"/>
+    <hyperlink ref="I14" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{ADF08FAB-2C1D-440D-BBBD-83F01ADFD5AA}"/>
+    <hyperlink ref="I15" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DBF2AF88-58FD-4DBE-B8E9-75831EE171CD}"/>
+    <hyperlink ref="I16" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0C6E3BF0-AC54-4B80-90F8-33D9B305172B}"/>
+    <hyperlink ref="I17" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8F0CB904-1B5D-437D-BF55-F9F69DD30167}"/>
+    <hyperlink ref="I18" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C238411D-AA75-4757-8DB0-7FFF69DDFB8A}"/>
+    <hyperlink ref="I19" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2CF67AD9-AC37-4A2C-9F0C-B88919CE0F0B}"/>
+    <hyperlink ref="I20" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2365DA53-A1B6-4663-84F1-81578502F133}"/>
+    <hyperlink ref="I21" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{27C7D044-2183-4716-89B4-C8035A5BDACD}"/>
+    <hyperlink ref="I22" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9E80976F-467A-4B3F-BCF7-5FEF9BF0C8AE}"/>
+    <hyperlink ref="I23" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF8104DA-29E5-48F8-AFED-A25C0810F9F1}"/>
+    <hyperlink ref="I24" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B3E70961-470C-4C29-85A5-D74EDE38D151}"/>
+    <hyperlink ref="I25" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{38E86826-A211-494A-B6B9-1B69DDA2EFF7}"/>
+    <hyperlink ref="I26" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1F20F8DA-CB16-474B-A4B9-E1DE8EF7B09B}"/>
+    <hyperlink ref="I27" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2FD70308-BDB7-4249-A039-5D067660BFD6}"/>
+    <hyperlink ref="I28" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EA7880BB-4407-4622-9350-159221423B3B}"/>
+    <hyperlink ref="I29" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DB53A627-9823-4A01-A33A-A9D5FE8B2AAC}"/>
+    <hyperlink ref="I30" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F0F55E47-3169-4DEA-8A5D-DAE098E7AA0E}"/>
+    <hyperlink ref="I31" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{73A5B96C-ED9A-4AD1-9E59-E94722FC6C4A}"/>
+    <hyperlink ref="I32" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{69FD3ECA-E6CA-451D-B9DC-3E388750B256}"/>
+    <hyperlink ref="I33" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{334F12FE-5699-40ED-A7EF-B9FDF8878812}"/>
+    <hyperlink ref="I34" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{696173DE-241C-4BEF-8A3A-85997AEEDB99}"/>
+    <hyperlink ref="I35" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{55928F6D-FAA5-45BC-B738-422AD9F475DF}"/>
+    <hyperlink ref="I36" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A1DF03D6-97B6-4086-B93A-954D2A825E10}"/>
+    <hyperlink ref="I37" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4D5F3AF4-2725-43BD-AA9B-9523987533AC}"/>
+    <hyperlink ref="I38" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8A208B5A-1C1B-43DD-B2B2-FE5CBAD35495}"/>
+    <hyperlink ref="I39" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C529394C-3620-4427-A2BF-4292E38557FC}"/>
+    <hyperlink ref="I40" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BDDECC2B-E9AE-47C6-A23C-2DA7B59E7077}"/>
+    <hyperlink ref="I41" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FD5C0161-5CEB-4F94-82B3-E067DE66ED04}"/>
+    <hyperlink ref="I42" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{143ECA98-C8BA-4897-B755-588898AC192E}"/>
+    <hyperlink ref="I43" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8F88F95-8B05-4AB3-9866-9C70E9B2A4E4}"/>
+    <hyperlink ref="I44" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F124A78A-547A-48A0-B7F2-BCD018B97195}"/>
+    <hyperlink ref="I45" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{62A5BAA4-50D8-4BF4-AE64-6D2CC7E9DE07}"/>
+    <hyperlink ref="I46" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{84982593-6A7A-48C4-929C-73648C3B107A}"/>
+    <hyperlink ref="I47" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E607F40D-AB62-490A-9B14-A32A120E28A5}"/>
+    <hyperlink ref="I48" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{71AFF0FF-4AFD-4274-9B0C-B518AE9D4FBB}"/>
+    <hyperlink ref="I49" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{22943615-22F6-43D7-8D6B-D83D57A9668E}"/>
+    <hyperlink ref="I50" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{513EACCF-D581-414C-9FE6-7D531B61A162}"/>
+    <hyperlink ref="I51" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C6ECBB6-FF10-4B7E-9D81-A42EF84AA8E1}"/>
+    <hyperlink ref="I52" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A44F4C23-317F-411D-97DE-90D8A4FB33E9}"/>
+    <hyperlink ref="I53" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F680E46D-8C1F-4821-8B8A-DDB1C60E2649}"/>
+    <hyperlink ref="I54" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B47BF1C6-4B29-4841-BC81-7A9F9167CEA0}"/>
+    <hyperlink ref="I55" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F15A7166-2A15-4E22-976C-5C9DEEE00387}"/>
+    <hyperlink ref="I56" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{03311C28-542E-4A06-8A69-E0753F94342C}"/>
+    <hyperlink ref="I57" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B89816E6-2DB1-4559-8390-72D5BB3EC59F}"/>
+    <hyperlink ref="I58" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5EF32F46-F67E-42FC-8F23-64E2DFC818BE}"/>
+    <hyperlink ref="I59" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{47BD76DB-B7EE-4AA8-AE0A-70B28E660954}"/>
+    <hyperlink ref="I60" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CDC78262-2229-4847-B303-813B574F8EE5}"/>
+    <hyperlink ref="I61" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5B97DFF-6CC1-4A69-A9FE-DD1C99DACF50}"/>
+    <hyperlink ref="I62" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5E77F0A-3557-40D8-B8A3-577FACDE056B}"/>
+    <hyperlink ref="I63" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{70FBCE56-656D-477A-83F4-0AFA04A808FC}"/>
+    <hyperlink ref="I64" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{93731BA7-B2A0-4776-965E-17A7B1BAB201}"/>
+    <hyperlink ref="I65" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C410A9FA-539C-4E83-B463-FA90104A0A39}"/>
+    <hyperlink ref="I66" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{610F377F-834E-4CF4-8B3C-F0A4DC0498C2}"/>
+    <hyperlink ref="I67" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C14AED96-01F8-47A5-B7FE-D6B1A3B3EC3B}"/>
+    <hyperlink ref="I68" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8FABA8B0-3CD1-4546-95C2-BAF0FADE3597}"/>
+    <hyperlink ref="I69" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A74CDF5A-0BDB-43A0-976C-6361A1904602}"/>
+    <hyperlink ref="I70" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B1D3426F-0142-45CE-939B-8C055B9F229C}"/>
+    <hyperlink ref="I71" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E411C4D5-8F83-437F-8C4D-B86654CB559D}"/>
+    <hyperlink ref="I72" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0F119914-F3E1-4824-9792-A0A357F0C69B}"/>
+    <hyperlink ref="I73" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D32D0D21-2612-4845-8CAC-6D25352EF5D3}"/>
+    <hyperlink ref="I74" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CA051FA0-0A47-4B67-81A9-16F2D79D0081}"/>
+    <hyperlink ref="I75" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B7F56C90-456C-440F-BDFA-45F01F1AF565}"/>
+    <hyperlink ref="I76" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{93C00ACA-C3D2-460C-B9DA-117BDA833187}"/>
+    <hyperlink ref="I77" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8F3479D-3681-4B1E-BCE5-4E0133B2E36D}"/>
+    <hyperlink ref="I78" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DFEB60E2-96C4-4BA7-AF58-EF7581E3E37A}"/>
+    <hyperlink ref="I79" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5CF0FB32-CDC9-4C8D-89C7-A6FF4095C4F9}"/>
+    <hyperlink ref="I80" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3A85C454-9ABF-4536-A3BD-675C7034DE1C}"/>
+    <hyperlink ref="I81" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{91B4B64E-1B8A-4483-A731-0EE302C8EEC7}"/>
+    <hyperlink ref="I82" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5B6B187F-6E1C-4D7D-A171-76E12F010408}"/>
+    <hyperlink ref="I83" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FAA64865-36F1-41F1-BB4D-5F9E691EF208}"/>
+    <hyperlink ref="I84" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C544D59B-4E38-447B-88DE-6C9AE6A8284F}"/>
+    <hyperlink ref="I85" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DC777E21-D4B6-4035-8E42-23DA33C9C087}"/>
+    <hyperlink ref="I86" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2A2E1A6D-86FE-4987-9AB4-54B7C971DFAA}"/>
+    <hyperlink ref="I87" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B827DB21-242B-410B-9591-CBE07C83FDFD}"/>
+    <hyperlink ref="I88" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F57C9182-5D3B-4E46-BC40-46A3D8E627D3}"/>
+    <hyperlink ref="I89" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2554A8C1-62DA-44DF-BC74-A27CE8F7BFBC}"/>
+    <hyperlink ref="I90" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D640E482-9F19-4D2A-B812-FBB54A9504A1}"/>
+    <hyperlink ref="I91" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C457E0D7-1278-44E9-932C-B24EF3343FC3}"/>
+    <hyperlink ref="I92" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{696D2CB9-2D96-486D-9F75-7376DE1F0AEB}"/>
+    <hyperlink ref="I93" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{383E64D0-D9EC-437F-A3B7-DA69FBA1E00E}"/>
+    <hyperlink ref="I94" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{615FC7F9-F46E-45A6-BBA2-B72742CA4B41}"/>
+    <hyperlink ref="I95" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9838F64C-F593-4678-9DEC-7CCAF67151FA}"/>
+    <hyperlink ref="I96" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A596E95E-9814-454A-B1E7-DEF21E58E6CF}"/>
+    <hyperlink ref="I97" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A193D687-4899-45DD-88BB-7DBAA2A9C895}"/>
+    <hyperlink ref="I98" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C585F8E2-8893-49F5-BEC8-9ABD3B0B5208}"/>
+    <hyperlink ref="I99" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CD864CC2-420B-4384-B326-3C50D3018E3E}"/>
+    <hyperlink ref="I100" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C523094A-D799-4C05-BCB7-37B0F52ACFEB}"/>
+    <hyperlink ref="I101" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9B2544B7-2F90-4077-8BE4-351C81B91E6D}"/>
+    <hyperlink ref="I2" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B3BB877E-7AA1-4D5A-B804-775C32BFCBFB}"/>
+    <hyperlink ref="I3" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1DC533D2-9FA6-4B3A-BB10-D969F6B9CBF7}"/>
+    <hyperlink ref="I4" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DFA07BE1-56E8-444F-B982-7038C2ACD65A}"/>
+    <hyperlink ref="I5" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{821702AF-8E85-4D48-BFBD-B11817203B03}"/>
+    <hyperlink ref="I6" r:id="rId100" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A054A60E-9915-4BFE-8D0B-3B480892BBEB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -32916,7 +33104,7 @@
         <v>8</v>
       </c>
       <c r="H1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -32942,7 +33130,7 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -32968,7 +33156,7 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -32994,7 +33182,7 @@
         <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -33045,8 +33233,8 @@
       <c r="G6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="25" t="s">
-        <v>256</v>
+      <c r="H6" s="24" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -1061,48 +1061,6 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1175,9 +1133,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1331,27 +1331,27 @@
   <autoFilter ref="A1:J101" xr:uid="{7F0749FA-984C-46C9-AAB8-7ABB595D4FB8}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F8D53C57-7078-4EF6-9C73-35B4D8C4988B}" name="data__id" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{390DCB3F-4D6D-4198-B590-711049680796}" name="list_name" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{390DCB3F-4D6D-4198-B590-711049680796}" name="list_name" dataDxfId="8">
       <calculatedColumnFormula>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{576DFB3C-BE82-459C-804A-245AC638C8B8}" name="data_num" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{A98793EC-C017-48A1-96BE-B60CD452DAC7}" name="name_ac" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{2B86B3E1-90A9-4410-87A1-76EA940DC021}" name="data__name" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{576DFB3C-BE82-459C-804A-245AC638C8B8}" name="data_num" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{A98793EC-C017-48A1-96BE-B60CD452DAC7}" name="name_ac" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{2B86B3E1-90A9-4410-87A1-76EA940DC021}" name="data__name" dataDxfId="5">
       <calculatedColumnFormula>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D4B6D36E-F5B4-4050-84DA-B62E678E55BF}" name="data__code" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{D4B6D36E-F5B4-4050-84DA-B62E678E55BF}" name="data__code" dataDxfId="4">
       <calculatedColumnFormula>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F102E323-9AC5-4420-B847-1C14F7757293}" name="data__bin" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{F102E323-9AC5-4420-B847-1C14F7757293}" name="data__bin" dataDxfId="3">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DB8F4E18-D2FD-4EA2-B28D-DA53D8A12D89}" name="data__shortName" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{DB8F4E18-D2FD-4EA2-B28D-DA53D8A12D89}" name="data__shortName" dataDxfId="2">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{EA429D0C-4231-435B-91FE-DAD0B13369DF}" name="data__logo" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{EA429D0C-4231-435B-91FE-DAD0B13369DF}" name="data__logo" dataDxfId="1">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BD47F35F-8B5D-4304-BED9-AA9B06C54ACA}" name="data__short_name" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{BD47F35F-8B5D-4304-BED9-AA9B06C54ACA}" name="data__short_name" dataDxfId="0">
       <calculatedColumnFormula>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6125F57C-E4AF-4425-9F82-72384BB1E799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDAF692-E3A5-473E-B3E5-426C9440817B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -1,42 +1,814 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9387026-A75E-43E3-A1C6-668129E5258B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
     <sheet name="API - io" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="256">
+  <si>
+    <t>data__id</t>
+  </si>
+  <si>
+    <t>list_name</t>
+  </si>
+  <si>
+    <t>data_num</t>
+  </si>
+  <si>
+    <t>name_ac</t>
+  </si>
+  <si>
+    <t>data__name</t>
+  </si>
+  <si>
+    <t>data__code</t>
+  </si>
+  <si>
+    <t>data__bin</t>
+  </si>
+  <si>
+    <t>data__shortName</t>
+  </si>
+  <si>
+    <t>data__logo</t>
+  </si>
+  <si>
+    <t>data__short_name</t>
+  </si>
+  <si>
+    <t>Huynh Tran Tuan Kiet</t>
+  </si>
+  <si>
+    <t>Templa</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP An Bình</t>
+  </si>
+  <si>
+    <t>ABB</t>
+  </si>
+  <si>
+    <t>ABBANK</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/ABB.png</t>
+  </si>
+  <si>
+    <t>compact2</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Á Châu</t>
+  </si>
+  <si>
+    <t>ACB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/ACB.png</t>
+  </si>
+  <si>
+    <t>compact</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Bắc Á</t>
+  </si>
+  <si>
+    <t>BAB</t>
+  </si>
+  <si>
+    <t>BacABank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/BAB.png</t>
+  </si>
+  <si>
+    <t>print</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Đầu tư và Phát triển Việt Nam</t>
+  </si>
+  <si>
+    <t>BIDV</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/BIDV.png</t>
+  </si>
+  <si>
+    <t>BdT8CDO</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Bảo Việt</t>
+  </si>
+  <si>
+    <t>BVB</t>
+  </si>
+  <si>
+    <t>BaoVietBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/BVB.png</t>
+  </si>
+  <si>
+    <t>qr_only</t>
+  </si>
+  <si>
+    <t>Ngân hàng Thương mại TNHH MTV Xây dựng Việt Nam</t>
+  </si>
+  <si>
+    <t>CBB</t>
+  </si>
+  <si>
+    <t>CBBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/CBB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV CIMB Việt Nam</t>
+  </si>
+  <si>
+    <t>CIMB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/CIMB.png</t>
+  </si>
+  <si>
+    <t>DBS Bank Ltd - Chi nhánh Thành phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>DBS</t>
+  </si>
+  <si>
+    <t>DBSBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/DBS.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV Số Vikki</t>
+  </si>
+  <si>
+    <t>Vikki</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/Vikki.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Xuất Nhập khẩu Việt Nam</t>
+  </si>
+  <si>
+    <t>EIB</t>
+  </si>
+  <si>
+    <t>Eximbank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/EIB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Thương mại TNHH MTV Dầu Khí Toàn Cầu</t>
+  </si>
+  <si>
+    <t>GPB</t>
+  </si>
+  <si>
+    <t>GPBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/GPB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Phát triển Thành phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>HDB</t>
+  </si>
+  <si>
+    <t>HDBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/HDB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV Hong Leong Việt Nam</t>
+  </si>
+  <si>
+    <t>HLBVN</t>
+  </si>
+  <si>
+    <t>HongLeong</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/HLBVN.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV HSBC (Việt Nam)</t>
+  </si>
+  <si>
+    <t>HSBC</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/HSBC.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Công nghiệp Hàn Quốc - Chi nhánh Hà Nội</t>
+  </si>
+  <si>
+    <t>IBK - HN</t>
+  </si>
+  <si>
+    <t>IBKHN</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/IBK.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Công nghiệp Hàn Quốc - Chi nhánh TP. Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>IBK - HCM</t>
+  </si>
+  <si>
+    <t>IBKHCM</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Công thương Việt Nam</t>
+  </si>
+  <si>
+    <t>ICB</t>
+  </si>
+  <si>
+    <t>VietinBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/ICB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH Indovina</t>
+  </si>
+  <si>
+    <t>IVB</t>
+  </si>
+  <si>
+    <t>IndovinaBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/IVB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Kiên Long</t>
+  </si>
+  <si>
+    <t>KLB</t>
+  </si>
+  <si>
+    <t>KienLongBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/KLB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+  </si>
+  <si>
+    <t>LPB</t>
+  </si>
+  <si>
+    <t>LPBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/LPB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Quân đội</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>MBBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/MB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Hàng Hải Việt Nam</t>
+  </si>
+  <si>
+    <t>MSB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/MSB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Nam Á</t>
+  </si>
+  <si>
+    <t>NAB</t>
+  </si>
+  <si>
+    <t>NamABank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/NAB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Quốc Dân</t>
+  </si>
+  <si>
+    <t>NCB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/NCB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Nonghyup - Chi nhánh Hà Nội</t>
+  </si>
+  <si>
+    <t>NHB HN</t>
+  </si>
+  <si>
+    <t>Nonghyup</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/NHB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Phương Đông</t>
+  </si>
+  <si>
+    <t>OCB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/OCB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV Việt Nam Hiện Đại</t>
+  </si>
+  <si>
+    <t>MBV</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/MBV.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV Public Việt Nam</t>
+  </si>
+  <si>
+    <t>PBVN</t>
+  </si>
+  <si>
+    <t>PublicBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/PBVN.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Thịnh vượng và Phát triển</t>
+  </si>
+  <si>
+    <t>PGB</t>
+  </si>
+  <si>
+    <t>PGBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/PGB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Đại Chúng Việt Nam</t>
+  </si>
+  <si>
+    <t>PVCB</t>
+  </si>
+  <si>
+    <t>PVcomBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/PVCB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Sài Gòn</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/SCB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV Standard Chartered Bank Việt Nam</t>
+  </si>
+  <si>
+    <t>SCVN</t>
+  </si>
+  <si>
+    <t>StandardChartered</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/SCVN.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Đông Nam Á</t>
+  </si>
+  <si>
+    <t>SEAB</t>
+  </si>
+  <si>
+    <t>SeABank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/SEAB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Sài Gòn Công Thương</t>
+  </si>
+  <si>
+    <t>SGICB</t>
+  </si>
+  <si>
+    <t>SaigonBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/SGICB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Sài Gòn - Hà Nội</t>
+  </si>
+  <si>
+    <t>SHB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/SHB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Sài Gòn Thương Tín</t>
+  </si>
+  <si>
+    <t>STB</t>
+  </si>
+  <si>
+    <t>Sacombank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/STB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV Shinhan Việt Nam</t>
+  </si>
+  <si>
+    <t>SHBVN</t>
+  </si>
+  <si>
+    <t>ShinhanBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/SHBVN.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Kỹ thương Việt Nam</t>
+  </si>
+  <si>
+    <t>TCB</t>
+  </si>
+  <si>
+    <t>Techcombank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/TCB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Tiên Phong</t>
+  </si>
+  <si>
+    <t>TPB</t>
+  </si>
+  <si>
+    <t>TPBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/TPB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng United Overseas - Chi nhánh TP. Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>UOB</t>
+  </si>
+  <si>
+    <t>UnitedOverseas</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/UOB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Việt Á</t>
+  </si>
+  <si>
+    <t>VAB</t>
+  </si>
+  <si>
+    <t>VietABank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VAB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Nông nghiệp và Phát triển Nông thôn Việt Nam</t>
+  </si>
+  <si>
+    <t>VBA</t>
+  </si>
+  <si>
+    <t>Agribank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VBA.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Ngoại Thương Việt Nam</t>
+  </si>
+  <si>
+    <t>VCB</t>
+  </si>
+  <si>
+    <t>Vietcombank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VCB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Bản Việt</t>
+  </si>
+  <si>
+    <t>VCCB</t>
+  </si>
+  <si>
+    <t>VietCapitalBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VCCB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Quốc tế Việt Nam</t>
+  </si>
+  <si>
+    <t>VIB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VIB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Việt Nam Thương Tín</t>
+  </si>
+  <si>
+    <t>VIETBANK</t>
+  </si>
+  <si>
+    <t>VietBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VIETBANK.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Việt Nam Thịnh Vượng</t>
+  </si>
+  <si>
+    <t>VPB</t>
+  </si>
+  <si>
+    <t>VPBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VPB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Liên doanh Việt - Nga</t>
+  </si>
+  <si>
+    <t>VRB</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VRB.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TNHH MTV Woori Việt Nam</t>
+  </si>
+  <si>
+    <t>WVN</t>
+  </si>
+  <si>
+    <t>Woori</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/WVN.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Kookmin - Chi nhánh Hà Nội</t>
+  </si>
+  <si>
+    <t>KBHN</t>
+  </si>
+  <si>
+    <t>KookminHN</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/KBHN.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Kookmin - Chi nhánh Thành phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>KBHCM</t>
+  </si>
+  <si>
+    <t>KookminHCM</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/KBHCM.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Hợp tác xã Việt Nam</t>
+  </si>
+  <si>
+    <t>COOPBANK</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/COOPBANK.png</t>
+  </si>
+  <si>
+    <t>TMCP Việt Nam Thịnh Vượng - Ngân hàng số CAKE by VPBank</t>
+  </si>
+  <si>
+    <t>CAKE</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/CAKE.png</t>
+  </si>
+  <si>
+    <t>TMCP Việt Nam Thịnh Vượng - Ngân hàng số Ubank by VPBank</t>
+  </si>
+  <si>
+    <t>Ubank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/UBANK.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Đại chúng TNHH Kasikornbank</t>
+  </si>
+  <si>
+    <t>KBank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/KBANK.png</t>
+  </si>
+  <si>
+    <t>VNPT Money</t>
+  </si>
+  <si>
+    <t>VNPTMONEY</t>
+  </si>
+  <si>
+    <t>VNPTMoney</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VNPTMONEY.png</t>
+  </si>
+  <si>
+    <t>Tổng Công ty Dịch vụ số Viettel - Chi nhánh tập đoàn công nghiệp viễn thông Quân Đội</t>
+  </si>
+  <si>
+    <t>VTLMONEY</t>
+  </si>
+  <si>
+    <t>ViettelMoney</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VIETTELMONEY.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng số Timo by Ban Viet Bank (Timo by Ban Viet Bank)</t>
+  </si>
+  <si>
+    <t>TIMO</t>
+  </si>
+  <si>
+    <t>Timo</t>
+  </si>
+  <si>
+    <t>https://vietqr.net/portal-service/resources/icons/TIMO.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Citibank, N.A. - Chi nhánh Hà Nội</t>
+  </si>
+  <si>
+    <t>CITIBANK</t>
+  </si>
+  <si>
+    <t>Citibank</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/CITIBANK.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng KEB Hana – Chi nhánh Thành phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>KEBHANAHCM</t>
+  </si>
+  <si>
+    <t>KEBHanaHCM</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/KEBHANAHCM.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng KEB Hana – Chi nhánh Hà Nội</t>
+  </si>
+  <si>
+    <t>KEBHANAHN</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/KEBHANAHN.png</t>
+  </si>
+  <si>
+    <t>Công ty Tài chính TNHH MTV Mirae Asset (Việt Nam)</t>
+  </si>
+  <si>
+    <t>MAFC</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/MAFC.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng Chính sách Xã hội</t>
+  </si>
+  <si>
+    <t>VBSP</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/VBSP.png</t>
+  </si>
+  <si>
+    <t>Ngân hàng TMCP Đại Chúng Việt Nam Ngân hàng số</t>
+  </si>
+  <si>
+    <t>PVDB</t>
+  </si>
+  <si>
+    <t>PVcomBank Pay</t>
+  </si>
+  <si>
+    <t>CTCP Dịch Vụ Di Động Trực Tuyến</t>
+  </si>
+  <si>
+    <t>momo</t>
+  </si>
+  <si>
+    <t>MoMo</t>
+  </si>
+  <si>
+    <t>https://cdn.vietqr.io/img/momo.png</t>
+  </si>
+  <si>
+    <t>0582118210</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,14 +837,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,62 +1178,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J101"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>data__id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>list_name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>data_num</v>
-      </c>
-      <c r="D1" t="str">
-        <v>name_ac</v>
-      </c>
-      <c r="E1" t="str">
-        <v>data__name</v>
-      </c>
-      <c r="F1" t="str">
-        <v>data__code</v>
-      </c>
-      <c r="G1" t="str">
-        <v>data__bin</v>
-      </c>
-      <c r="H1" t="str">
-        <v>data__shortName</v>
-      </c>
-      <c r="I1" t="str">
-        <v>data__logo</v>
-      </c>
-      <c r="J1" t="str">
-        <v>data__short_name</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>38</v>
       </c>
       <c r="B2" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
-        <v>TCB</v>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
       </c>
       <c r="C2">
         <v>44699999999</v>
       </c>
-      <c r="D2" t="str">
-        <v>Huynh Tran Tuan Kiet</v>
+      <c r="D2" t="s">
+        <v>10</v>
       </c>
       <c r="E2" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <v>-</v>
       </c>
       <c r="F2" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
-        <v>TCB</v>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
       </c>
       <c r="G2">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
@@ -471,27 +1258,27 @@
         <v>Techcombank</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>43</v>
       </c>
       <c r="B3" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VCB</v>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
       </c>
       <c r="C3">
         <v>1031451081</v>
       </c>
-      <c r="D3" t="str">
-        <v>Huynh Tran Tuan Kiet</v>
+      <c r="D3" t="s">
+        <v>10</v>
       </c>
       <c r="E3" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <v>-</v>
       </c>
       <c r="F3" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VCB</v>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
       </c>
       <c r="G3">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
@@ -510,47 +1297,56 @@
         <v>Vietcombank</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>26</v>
+      </c>
       <c r="B4" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
       </c>
       <c r="E4" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F4" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G4" t="str">
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G4">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970448</v>
       </c>
       <c r="H4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>OCB</v>
       </c>
       <c r="I4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/OCB.png</v>
       </c>
       <c r="J4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>OCB</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E5" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F5" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G5" t="str">
@@ -570,17 +1366,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E6" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F6" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G6" t="str">
@@ -600,17 +1396,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E7" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F7" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G7" t="str">
@@ -630,17 +1426,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E8" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" t="str">
@@ -660,17 +1456,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E9" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F9" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G9" t="str">
@@ -690,17 +1486,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E10" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F10" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G10" t="str">
@@ -720,17 +1516,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E11" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F11" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G11" t="str">
@@ -750,17 +1546,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E12" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F12" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G12" t="str">
@@ -780,17 +1576,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E13" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F13" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G13" t="str">
@@ -810,17 +1606,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E14" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F14" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G14" t="str">
@@ -840,17 +1636,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E15" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F15" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G15" t="str">
@@ -870,17 +1666,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E16" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F16" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G16" t="str">
@@ -900,17 +1696,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B17" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E17" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F17" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G17" t="str">
@@ -930,17 +1726,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E18" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F18" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G18" t="str">
@@ -960,17 +1756,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B19" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E19" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F19" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G19" t="str">
@@ -990,17 +1786,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E20" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F20" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G20" t="str">
@@ -1020,17 +1816,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E21" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F21" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G21" t="str">
@@ -1050,17 +1846,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B22" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E22" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F22" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G22" t="str">
@@ -1080,17 +1876,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B23" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E23" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F23" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G23" t="str">
@@ -1110,17 +1906,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B24" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E24" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F24" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G24" t="str">
@@ -1140,17 +1936,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B25" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E25" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F25" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G25" t="str">
@@ -1170,17 +1966,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B26" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E26" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F26" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G26" t="str">
@@ -1200,17 +1996,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B27" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E27" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F27" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G27" t="str">
@@ -1230,17 +2026,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B28" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E28" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F28" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G28" t="str">
@@ -1260,17 +2056,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B29" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E29" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F29" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G29" t="str">
@@ -1290,17 +2086,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B30" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E30" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F30" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G30" t="str">
@@ -1320,17 +2116,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B31" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E31" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F31" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G31" t="str">
@@ -1350,17 +2146,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B32" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E32" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F32" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G32" t="str">
@@ -1380,17 +2176,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E33" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F33" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G33" t="str">
@@ -1410,17 +2206,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B34" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E34" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F34" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G34" t="str">
@@ -1440,17 +2236,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B35" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E35" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F35" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G35" t="str">
@@ -1470,17 +2266,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B36" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E36" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F36" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G36" t="str">
@@ -1500,17 +2296,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B37" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E37" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F37" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G37" t="str">
@@ -1530,17 +2326,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E38" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F38" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G38" t="str">
@@ -1560,17 +2356,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B39" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E39" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F39" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G39" t="str">
@@ -1590,17 +2386,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B40" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E40" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F40" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G40" t="str">
@@ -1620,17 +2416,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B41" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E41" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F41" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G41" t="str">
@@ -1650,17 +2446,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B42" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E42" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F42" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G42" t="str">
@@ -1680,17 +2476,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B43" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E43" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F43" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G43" t="str">
@@ -1710,17 +2506,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B44" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E44" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F44" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G44" t="str">
@@ -1740,17 +2536,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B45" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E45" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F45" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G45" t="str">
@@ -1770,17 +2566,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B46" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E46" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F46" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G46" t="str">
@@ -1800,17 +2596,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B47" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E47" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F47" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G47" t="str">
@@ -1830,17 +2626,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E48" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F48" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G48" t="str">
@@ -1860,17 +2656,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B49" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E49" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F49" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G49" t="str">
@@ -1890,17 +2686,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B50" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E50" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F50" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G50" t="str">
@@ -1920,17 +2716,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B51" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E51" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F51" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G51" t="str">
@@ -1950,17 +2746,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B52" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E52" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F52" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G52" t="str">
@@ -1980,17 +2776,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B53" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E53" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F53" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G53" t="str">
@@ -2010,17 +2806,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B54" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E54" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F54" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G54" t="str">
@@ -2040,17 +2836,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B55" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E55" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F55" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G55" t="str">
@@ -2070,17 +2866,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B56" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E56" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F56" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G56" t="str">
@@ -2100,17 +2896,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B57" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E57" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F57" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G57" t="str">
@@ -2130,17 +2926,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B58" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E58" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F58" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G58" t="str">
@@ -2160,17 +2956,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B59" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E59" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F59" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G59" t="str">
@@ -2190,17 +2986,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B60" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E60" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F60" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G60" t="str">
@@ -2220,17 +3016,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B61" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E61" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F61" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G61" t="str">
@@ -2250,17 +3046,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B62" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E62" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F62" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G62" t="str">
@@ -2280,17 +3076,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B63" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E63" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F63" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G63" t="str">
@@ -2310,17 +3106,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B64" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E64" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F64" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G64" t="str">
@@ -2340,17 +3136,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B65" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E65" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F65" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G65" t="str">
@@ -2370,17 +3166,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B66" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E66" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F66" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G66" t="str">
@@ -2400,17 +3196,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B67" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E67" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F67" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G67" t="str">
@@ -2430,17 +3226,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B68" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E68" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F68" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G68" t="str">
@@ -2460,17 +3256,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B69" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E69" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F69" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G69" t="str">
@@ -2490,17 +3286,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B70" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E70" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F70" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G70" t="str">
@@ -2520,17 +3316,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B71" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E71" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F71" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G71" t="str">
@@ -2550,17 +3346,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B72" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E72" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F72" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G72" t="str">
@@ -2580,17 +3376,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B73" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E73" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F73" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G73" t="str">
@@ -2610,17 +3406,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B74" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E74" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F74" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G74" t="str">
@@ -2640,17 +3436,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B75" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E75" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F75" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G75" t="str">
@@ -2670,17 +3466,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B76" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E76" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F76" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G76" t="str">
@@ -2700,17 +3496,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B77" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E77" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F77" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G77" t="str">
@@ -2730,17 +3526,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B78" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E78" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F78" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G78" t="str">
@@ -2760,17 +3556,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B79" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E79" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F79" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G79" t="str">
@@ -2790,17 +3586,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B80" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E80" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F80" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G80" t="str">
@@ -2820,17 +3616,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B81" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E81" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F81" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G81" t="str">
@@ -2850,17 +3646,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B82" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E82" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F82" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G82" t="str">
@@ -2880,17 +3676,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B83" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E83" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F83" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G83" t="str">
@@ -2910,17 +3706,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B84" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E84" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F84" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G84" t="str">
@@ -2940,17 +3736,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B85" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E85" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F85" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G85" t="str">
@@ -2970,17 +3766,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B86" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E86" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F86" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G86" t="str">
@@ -3000,17 +3796,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B87" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E87" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F87" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G87" t="str">
@@ -3030,17 +3826,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B88" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E88" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F88" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G88" t="str">
@@ -3060,17 +3856,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B89" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E89" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F89" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G89" t="str">
@@ -3090,17 +3886,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B90" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E90" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F90" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G90" t="str">
@@ -3120,17 +3916,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B91" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E91" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F91" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G91" t="str">
@@ -3150,17 +3946,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B92" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E92" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F92" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G92" t="str">
@@ -3180,17 +3976,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B93" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E93" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F93" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G93" t="str">
@@ -3210,17 +4006,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E94" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F94" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G94" t="str">
@@ -3240,17 +4036,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B95" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E95" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F95" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G95" t="str">
@@ -3270,17 +4066,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B96" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E96" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F96" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G96" t="str">
@@ -3300,17 +4096,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B97" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E97" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F97" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G97" t="str">
@@ -3330,17 +4126,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B98" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E98" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F98" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G98" t="str">
@@ -3360,17 +4156,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B99" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E99" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F99" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G99" t="str">
@@ -3390,17 +4186,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B100" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E100" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F100" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G100" t="str">
@@ -3420,17 +4216,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B101" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="E101" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F101" t="str">
-        <f>IFERROR((VLOOKUP(Table1[[#This Row],[data__id]],'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G101" t="str">
@@ -3452,1725 +4248,1736 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1"/>
-    <hyperlink ref="I3" r:id="rId2"/>
-    <hyperlink ref="I4" r:id="rId3"/>
-    <hyperlink ref="I5" r:id="rId4"/>
-    <hyperlink ref="I6" r:id="rId5"/>
-    <hyperlink ref="I7" r:id="rId6"/>
-    <hyperlink ref="I8" r:id="rId7"/>
-    <hyperlink ref="I9" r:id="rId8"/>
-    <hyperlink ref="I10" r:id="rId9"/>
-    <hyperlink ref="I11" r:id="rId10"/>
-    <hyperlink ref="I12" r:id="rId11"/>
-    <hyperlink ref="I13" r:id="rId12"/>
-    <hyperlink ref="I14" r:id="rId13"/>
-    <hyperlink ref="I15" r:id="rId14"/>
-    <hyperlink ref="I16" r:id="rId15"/>
-    <hyperlink ref="I17" r:id="rId16"/>
-    <hyperlink ref="I18" r:id="rId17"/>
-    <hyperlink ref="I19" r:id="rId18"/>
-    <hyperlink ref="I20" r:id="rId19"/>
-    <hyperlink ref="I21" r:id="rId20"/>
-    <hyperlink ref="I22" r:id="rId21"/>
-    <hyperlink ref="I23" r:id="rId22"/>
-    <hyperlink ref="I24" r:id="rId23"/>
-    <hyperlink ref="I25" r:id="rId24"/>
-    <hyperlink ref="I26" r:id="rId25"/>
-    <hyperlink ref="I27" r:id="rId26"/>
-    <hyperlink ref="I28" r:id="rId27"/>
-    <hyperlink ref="I29" r:id="rId28"/>
-    <hyperlink ref="I30" r:id="rId29"/>
-    <hyperlink ref="I31" r:id="rId30"/>
-    <hyperlink ref="I32" r:id="rId31"/>
-    <hyperlink ref="I33" r:id="rId32"/>
-    <hyperlink ref="I34" r:id="rId33"/>
-    <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
-    <hyperlink ref="I38" r:id="rId37"/>
-    <hyperlink ref="I39" r:id="rId38"/>
-    <hyperlink ref="I40" r:id="rId39"/>
-    <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
-    <hyperlink ref="I44" r:id="rId43"/>
-    <hyperlink ref="I45" r:id="rId44"/>
-    <hyperlink ref="I46" r:id="rId45"/>
-    <hyperlink ref="I47" r:id="rId46"/>
-    <hyperlink ref="I48" r:id="rId47"/>
-    <hyperlink ref="I49" r:id="rId48"/>
-    <hyperlink ref="I50" r:id="rId49"/>
-    <hyperlink ref="I51" r:id="rId50"/>
-    <hyperlink ref="I52" r:id="rId51"/>
-    <hyperlink ref="I53" r:id="rId52"/>
-    <hyperlink ref="I54" r:id="rId53"/>
-    <hyperlink ref="I55" r:id="rId54"/>
-    <hyperlink ref="I56" r:id="rId55"/>
-    <hyperlink ref="I57" r:id="rId56"/>
-    <hyperlink ref="I58" r:id="rId57"/>
-    <hyperlink ref="I59" r:id="rId58"/>
-    <hyperlink ref="I60" r:id="rId59"/>
-    <hyperlink ref="I61" r:id="rId60"/>
-    <hyperlink ref="I62" r:id="rId61"/>
-    <hyperlink ref="I63" r:id="rId62"/>
-    <hyperlink ref="I64" r:id="rId63"/>
-    <hyperlink ref="I65" r:id="rId64"/>
-    <hyperlink ref="I66" r:id="rId65"/>
-    <hyperlink ref="I67" r:id="rId66"/>
-    <hyperlink ref="I68" r:id="rId67"/>
-    <hyperlink ref="I69" r:id="rId68"/>
-    <hyperlink ref="I70" r:id="rId69"/>
-    <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
-    <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
-    <hyperlink ref="I77" r:id="rId76"/>
-    <hyperlink ref="I78" r:id="rId77"/>
-    <hyperlink ref="I79" r:id="rId78"/>
-    <hyperlink ref="I80" r:id="rId79"/>
-    <hyperlink ref="I81" r:id="rId80"/>
-    <hyperlink ref="I82" r:id="rId81"/>
-    <hyperlink ref="I83" r:id="rId82"/>
-    <hyperlink ref="I84" r:id="rId83"/>
-    <hyperlink ref="I85" r:id="rId84"/>
-    <hyperlink ref="I86" r:id="rId85"/>
-    <hyperlink ref="I87" r:id="rId86"/>
-    <hyperlink ref="I88" r:id="rId87"/>
-    <hyperlink ref="I89" r:id="rId88"/>
-    <hyperlink ref="I90" r:id="rId89"/>
-    <hyperlink ref="I91" r:id="rId90"/>
-    <hyperlink ref="I92" r:id="rId91"/>
-    <hyperlink ref="I93" r:id="rId92"/>
-    <hyperlink ref="I94" r:id="rId93"/>
-    <hyperlink ref="I95" r:id="rId94"/>
-    <hyperlink ref="I96" r:id="rId95"/>
-    <hyperlink ref="I97" r:id="rId96"/>
-    <hyperlink ref="I98" r:id="rId97"/>
-    <hyperlink ref="I99" r:id="rId98"/>
-    <hyperlink ref="I100" r:id="rId99"/>
-    <hyperlink ref="I101" r:id="rId100"/>
+    <hyperlink ref="I2" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="I3" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I4" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I5" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I6" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I7" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I8" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I9" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I10" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I11" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I12" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="I13" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I14" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="I15" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I16" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="I17" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I18" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="I19" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="I20" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I21" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I22" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="I23" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="I24" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="I25" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="I26" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="I27" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="I28" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="I29" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="I30" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="I31" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="I32" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="I33" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="I34" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="I35" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="I36" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="I37" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="I38" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="I39" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="I40" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="I41" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="I42" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="I43" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="I44" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="I45" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="I46" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="I47" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="I48" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="I49" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="I50" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="I51" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="I52" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="I53" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="I54" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="I55" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="I56" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="I57" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="I58" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="I59" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="I60" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="I61" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="I62" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="I63" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="I64" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="I65" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="I66" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="I67" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="I68" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="I69" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="I70" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="I71" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="I72" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="I73" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="I74" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="I75" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="I76" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="I77" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="I78" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="I79" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="I80" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="I81" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="I82" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="I83" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="I84" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="I85" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="I86" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="I87" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="I88" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="I89" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="I90" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="I91" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="I92" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="I93" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="I94" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="I95" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="I96" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="I97" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="I98" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="I99" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="I100" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="I101" r:id="rId100" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J101"/>
+    <ignoredError sqref="A1:J3 A5:J101 B4 E4:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H66"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>data__id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>data__name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>data__code</v>
-      </c>
-      <c r="D1" t="str">
-        <v>data__bin</v>
-      </c>
-      <c r="E1" t="str">
-        <v>data__shortName</v>
-      </c>
-      <c r="F1" t="str">
-        <v>data__logo</v>
-      </c>
-      <c r="G1" t="str">
-        <v>data__short_name</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Templa</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Ngân hàng TMCP An Bình</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ABB</v>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
       </c>
       <c r="D2">
         <v>970425</v>
       </c>
-      <c r="E2" t="str">
-        <v>ABBANK</v>
-      </c>
-      <c r="F2" t="str">
-        <v>https://cdn.vietqr.io/img/ABB.png</v>
-      </c>
-      <c r="G2" t="str">
-        <v>ABBANK</v>
-      </c>
-      <c r="H2" t="str">
-        <v>compact2</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Ngân hàng TMCP Á Châu</v>
-      </c>
-      <c r="C3" t="str">
-        <v>ACB</v>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
       </c>
       <c r="D3">
         <v>970416</v>
       </c>
-      <c r="E3" t="str">
-        <v>ACB</v>
-      </c>
-      <c r="F3" t="str">
-        <v>https://cdn.vietqr.io/img/ACB.png</v>
-      </c>
-      <c r="G3" t="str">
-        <v>ACB</v>
-      </c>
-      <c r="H3" t="str">
-        <v>compact</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Ngân hàng TMCP Bắc Á</v>
-      </c>
-      <c r="C4" t="str">
-        <v>BAB</v>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
       </c>
       <c r="D4">
         <v>970409</v>
       </c>
-      <c r="E4" t="str">
-        <v>BacABank</v>
-      </c>
-      <c r="F4" t="str">
-        <v>https://cdn.vietqr.io/img/BAB.png</v>
-      </c>
-      <c r="G4" t="str">
-        <v>BacABank</v>
-      </c>
-      <c r="H4" t="str">
-        <v>print</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Ngân hàng TMCP Đầu tư và Phát triển Việt Nam</v>
-      </c>
-      <c r="C5" t="str">
-        <v>BIDV</v>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
       </c>
       <c r="D5">
         <v>970418</v>
       </c>
-      <c r="E5" t="str">
-        <v>BIDV</v>
-      </c>
-      <c r="F5" t="str">
-        <v>https://cdn.vietqr.io/img/BIDV.png</v>
-      </c>
-      <c r="G5" t="str">
-        <v>BIDV</v>
-      </c>
-      <c r="H5" t="str">
-        <v>BdT8CDO</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Ngân hàng TMCP Bảo Việt</v>
-      </c>
-      <c r="C6" t="str">
-        <v>BVB</v>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
       </c>
       <c r="D6">
         <v>970438</v>
       </c>
-      <c r="E6" t="str">
-        <v>BaoVietBank</v>
-      </c>
-      <c r="F6" t="str">
-        <v>https://cdn.vietqr.io/img/BVB.png</v>
-      </c>
-      <c r="G6" t="str">
-        <v>BaoVietBank</v>
-      </c>
-      <c r="H6" t="str">
-        <v>qr_only</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>Ngân hàng Thương mại TNHH MTV Xây dựng Việt Nam</v>
-      </c>
-      <c r="C7" t="str">
-        <v>CBB</v>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
       </c>
       <c r="D7">
         <v>970444</v>
       </c>
-      <c r="E7" t="str">
-        <v>CBBank</v>
-      </c>
-      <c r="F7" t="str">
-        <v>https://cdn.vietqr.io/img/CBB.png</v>
-      </c>
-      <c r="G7" t="str">
-        <v>CBBank</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>Ngân hàng TNHH MTV CIMB Việt Nam</v>
-      </c>
-      <c r="C8" t="str">
-        <v>CIMB</v>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
       </c>
       <c r="D8">
         <v>422589</v>
       </c>
-      <c r="E8" t="str">
-        <v>CIMB</v>
-      </c>
-      <c r="F8" t="str">
-        <v>https://cdn.vietqr.io/img/CIMB.png</v>
-      </c>
-      <c r="G8" t="str">
-        <v>CIMB</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>DBS Bank Ltd - Chi nhánh Thành phố Hồ Chí Minh</v>
-      </c>
-      <c r="C9" t="str">
-        <v>DBS</v>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
       </c>
       <c r="D9">
         <v>796500</v>
       </c>
-      <c r="E9" t="str">
-        <v>DBSBank</v>
-      </c>
-      <c r="F9" t="str">
-        <v>https://cdn.vietqr.io/img/DBS.png</v>
-      </c>
-      <c r="G9" t="str">
-        <v>DBSBank</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>Ngân hàng TNHH MTV Số Vikki</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Vikki</v>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
       </c>
       <c r="D10">
         <v>970406</v>
       </c>
-      <c r="E10" t="str">
-        <v>Vikki</v>
-      </c>
-      <c r="F10" t="str">
-        <v>https://cdn.vietqr.io/img/Vikki.png</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Vikki</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>Ngân hàng TMCP Xuất Nhập khẩu Việt Nam</v>
-      </c>
-      <c r="C11" t="str">
-        <v>EIB</v>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
       </c>
       <c r="D11">
         <v>970431</v>
       </c>
-      <c r="E11" t="str">
-        <v>Eximbank</v>
-      </c>
-      <c r="F11" t="str">
-        <v>https://cdn.vietqr.io/img/EIB.png</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Eximbank</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>Ngân hàng Thương mại TNHH MTV Dầu Khí Toàn Cầu</v>
-      </c>
-      <c r="C12" t="str">
-        <v>GPB</v>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
       </c>
       <c r="D12">
         <v>970408</v>
       </c>
-      <c r="E12" t="str">
-        <v>GPBank</v>
-      </c>
-      <c r="F12" t="str">
-        <v>https://cdn.vietqr.io/img/GPB.png</v>
-      </c>
-      <c r="G12" t="str">
-        <v>GPBank</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>Ngân hàng TMCP Phát triển Thành phố Hồ Chí Minh</v>
-      </c>
-      <c r="C13" t="str">
-        <v>HDB</v>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
       </c>
       <c r="D13">
         <v>970437</v>
       </c>
-      <c r="E13" t="str">
-        <v>HDBank</v>
-      </c>
-      <c r="F13" t="str">
-        <v>https://cdn.vietqr.io/img/HDB.png</v>
-      </c>
-      <c r="G13" t="str">
-        <v>HDBank</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>Ngân hàng TNHH MTV Hong Leong Việt Nam</v>
-      </c>
-      <c r="C14" t="str">
-        <v>HLBVN</v>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
       </c>
       <c r="D14">
         <v>970442</v>
       </c>
-      <c r="E14" t="str">
-        <v>HongLeong</v>
-      </c>
-      <c r="F14" t="str">
-        <v>https://cdn.vietqr.io/img/HLBVN.png</v>
-      </c>
-      <c r="G14" t="str">
-        <v>HongLeong</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>Ngân hàng TNHH MTV HSBC (Việt Nam)</v>
-      </c>
-      <c r="C15" t="str">
-        <v>HSBC</v>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
       </c>
       <c r="D15">
         <v>458761</v>
       </c>
-      <c r="E15" t="str">
-        <v>HSBC</v>
-      </c>
-      <c r="F15" t="str">
-        <v>https://cdn.vietqr.io/img/HSBC.png</v>
-      </c>
-      <c r="G15" t="str">
-        <v>HSBC</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>Ngân hàng Công nghiệp Hàn Quốc - Chi nhánh Hà Nội</v>
-      </c>
-      <c r="C16" t="str">
-        <v>IBK - HN</v>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
       </c>
       <c r="D16">
         <v>970455</v>
       </c>
-      <c r="E16" t="str">
-        <v>IBKHN</v>
-      </c>
-      <c r="F16" t="str">
-        <v>https://cdn.vietqr.io/img/IBK.png</v>
-      </c>
-      <c r="G16" t="str">
-        <v>IBKHN</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>Ngân hàng Công nghiệp Hàn Quốc - Chi nhánh TP. Hồ Chí Minh</v>
-      </c>
-      <c r="C17" t="str">
-        <v>IBK - HCM</v>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
       </c>
       <c r="D17">
         <v>970456</v>
       </c>
-      <c r="E17" t="str">
-        <v>IBKHCM</v>
-      </c>
-      <c r="F17" t="str">
-        <v>https://cdn.vietqr.io/img/IBK.png</v>
-      </c>
-      <c r="G17" t="str">
-        <v>IBKHCM</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>Ngân hàng TMCP Công thương Việt Nam</v>
-      </c>
-      <c r="C18" t="str">
-        <v>ICB</v>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
       </c>
       <c r="D18">
         <v>970415</v>
       </c>
-      <c r="E18" t="str">
-        <v>VietinBank</v>
-      </c>
-      <c r="F18" t="str">
-        <v>https://cdn.vietqr.io/img/ICB.png</v>
-      </c>
-      <c r="G18" t="str">
-        <v>VietinBank</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>Ngân hàng TNHH Indovina</v>
-      </c>
-      <c r="C19" t="str">
-        <v>IVB</v>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
       </c>
       <c r="D19">
         <v>970434</v>
       </c>
-      <c r="E19" t="str">
-        <v>IndovinaBank</v>
-      </c>
-      <c r="F19" t="str">
-        <v>https://cdn.vietqr.io/img/IVB.png</v>
-      </c>
-      <c r="G19" t="str">
-        <v>IndovinaBank</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>Ngân hàng TMCP Kiên Long</v>
-      </c>
-      <c r="C20" t="str">
-        <v>KLB</v>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
       </c>
       <c r="D20">
         <v>970452</v>
       </c>
-      <c r="E20" t="str">
-        <v>KienLongBank</v>
-      </c>
-      <c r="F20" t="str">
-        <v>https://cdn.vietqr.io/img/KLB.png</v>
-      </c>
-      <c r="G20" t="str">
-        <v>KienLongBank</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="E20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>Ngân hàng TMCP Lộc Phát Việt Nam</v>
-      </c>
-      <c r="C21" t="str">
-        <v>LPB</v>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
       </c>
       <c r="D21">
         <v>970449</v>
       </c>
-      <c r="E21" t="str">
-        <v>LPBank</v>
-      </c>
-      <c r="F21" t="str">
-        <v>https://cdn.vietqr.io/img/LPB.png</v>
-      </c>
-      <c r="G21" t="str">
-        <v>LPBank</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="E21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>Ngân hàng TMCP Quân đội</v>
-      </c>
-      <c r="C22" t="str">
-        <v>MB</v>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>92</v>
       </c>
       <c r="D22">
         <v>970422</v>
       </c>
-      <c r="E22" t="str">
-        <v>MBBank</v>
-      </c>
-      <c r="F22" t="str">
-        <v>https://cdn.vietqr.io/img/MB.png</v>
-      </c>
-      <c r="G22" t="str">
-        <v>MBBank</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="E22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>Ngân hàng TMCP Hàng Hải Việt Nam</v>
-      </c>
-      <c r="C23" t="str">
-        <v>MSB</v>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
       </c>
       <c r="D23">
         <v>970426</v>
       </c>
-      <c r="E23" t="str">
-        <v>MSB</v>
-      </c>
-      <c r="F23" t="str">
-        <v>https://cdn.vietqr.io/img/MSB.png</v>
-      </c>
-      <c r="G23" t="str">
-        <v>MSB</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="E23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v>Ngân hàng TMCP Nam Á</v>
-      </c>
-      <c r="C24" t="str">
-        <v>NAB</v>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
       </c>
       <c r="D24">
         <v>970428</v>
       </c>
-      <c r="E24" t="str">
-        <v>NamABank</v>
-      </c>
-      <c r="F24" t="str">
-        <v>https://cdn.vietqr.io/img/NAB.png</v>
-      </c>
-      <c r="G24" t="str">
-        <v>NamABank</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="E24" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v>Ngân hàng TMCP Quốc Dân</v>
-      </c>
-      <c r="C25" t="str">
-        <v>NCB</v>
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
       </c>
       <c r="D25">
         <v>970419</v>
       </c>
-      <c r="E25" t="str">
-        <v>NCB</v>
-      </c>
-      <c r="F25" t="str">
-        <v>https://cdn.vietqr.io/img/NCB.png</v>
-      </c>
-      <c r="G25" t="str">
-        <v>NCB</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="E25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>Ngân hàng Nonghyup - Chi nhánh Hà Nội</v>
-      </c>
-      <c r="C26" t="str">
-        <v>NHB HN</v>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
       </c>
       <c r="D26">
         <v>801011</v>
       </c>
-      <c r="E26" t="str">
-        <v>Nonghyup</v>
-      </c>
-      <c r="F26" t="str">
-        <v>https://cdn.vietqr.io/img/NHB.png</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Nonghyup</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="E26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v>Ngân hàng TMCP Phương Đông</v>
-      </c>
-      <c r="C27" t="str">
-        <v>OCB</v>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
       </c>
       <c r="D27">
         <v>970448</v>
       </c>
-      <c r="E27" t="str">
-        <v>OCB</v>
-      </c>
-      <c r="F27" t="str">
-        <v>https://cdn.vietqr.io/img/OCB.png</v>
-      </c>
-      <c r="G27" t="str">
-        <v>OCB</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="E27" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v>Ngân hàng TNHH MTV Việt Nam Hiện Đại</v>
-      </c>
-      <c r="C28" t="str">
-        <v>MBV</v>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
       </c>
       <c r="D28">
         <v>970414</v>
       </c>
-      <c r="E28" t="str">
-        <v>MBV</v>
-      </c>
-      <c r="F28" t="str">
-        <v>https://cdn.vietqr.io/img/MBV.png</v>
-      </c>
-      <c r="G28" t="str">
-        <v>MBV</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="E28" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>Ngân hàng TNHH MTV Public Việt Nam</v>
-      </c>
-      <c r="C29" t="str">
-        <v>PBVN</v>
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
       </c>
       <c r="D29">
         <v>970439</v>
       </c>
-      <c r="E29" t="str">
-        <v>PublicBank</v>
-      </c>
-      <c r="F29" t="str">
-        <v>https://cdn.vietqr.io/img/PBVN.png</v>
-      </c>
-      <c r="G29" t="str">
-        <v>PublicBank</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="E29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>Ngân hàng TMCP Thịnh vượng và Phát triển</v>
-      </c>
-      <c r="C30" t="str">
-        <v>PGB</v>
+      <c r="B30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
       </c>
       <c r="D30">
         <v>970430</v>
       </c>
-      <c r="E30" t="str">
-        <v>PGBank</v>
-      </c>
-      <c r="F30" t="str">
-        <v>https://cdn.vietqr.io/img/PGB.png</v>
-      </c>
-      <c r="G30" t="str">
-        <v>PGBank</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="E30" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" t="s">
+        <v>122</v>
+      </c>
+      <c r="G30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>Ngân hàng TMCP Đại Chúng Việt Nam</v>
-      </c>
-      <c r="C31" t="str">
-        <v>PVCB</v>
+      <c r="B31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" t="s">
+        <v>124</v>
       </c>
       <c r="D31">
         <v>970412</v>
       </c>
-      <c r="E31" t="str">
-        <v>PVcomBank</v>
-      </c>
-      <c r="F31" t="str">
-        <v>https://cdn.vietqr.io/img/PVCB.png</v>
-      </c>
-      <c r="G31" t="str">
-        <v>PVcomBank</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="E31" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>Ngân hàng TMCP Sài Gòn</v>
-      </c>
-      <c r="C32" t="str">
-        <v>SCB</v>
+      <c r="B32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
       </c>
       <c r="D32">
         <v>970429</v>
       </c>
-      <c r="E32" t="str">
-        <v>SCB</v>
-      </c>
-      <c r="F32" t="str">
-        <v>https://cdn.vietqr.io/img/SCB.png</v>
-      </c>
-      <c r="G32" t="str">
-        <v>SCB</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>Ngân hàng TNHH MTV Standard Chartered Bank Việt Nam</v>
-      </c>
-      <c r="C33" t="str">
-        <v>SCVN</v>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" t="s">
+        <v>131</v>
       </c>
       <c r="D33">
         <v>970410</v>
       </c>
-      <c r="E33" t="str">
-        <v>StandardChartered</v>
-      </c>
-      <c r="F33" t="str">
-        <v>https://cdn.vietqr.io/img/SCVN.png</v>
-      </c>
-      <c r="G33" t="str">
-        <v>StandardChartered</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="E33" t="s">
+        <v>132</v>
+      </c>
+      <c r="F33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v>Ngân hàng TMCP Đông Nam Á</v>
-      </c>
-      <c r="C34" t="str">
-        <v>SEAB</v>
+      <c r="B34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" t="s">
+        <v>135</v>
       </c>
       <c r="D34">
         <v>970440</v>
       </c>
-      <c r="E34" t="str">
-        <v>SeABank</v>
-      </c>
-      <c r="F34" t="str">
-        <v>https://cdn.vietqr.io/img/SEAB.png</v>
-      </c>
-      <c r="G34" t="str">
-        <v>SeABank</v>
-      </c>
-    </row>
-    <row r="35">
+      <c r="E34" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v>Ngân hàng TMCP Sài Gòn Công Thương</v>
-      </c>
-      <c r="C35" t="str">
-        <v>SGICB</v>
+      <c r="B35" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" t="s">
+        <v>139</v>
       </c>
       <c r="D35">
         <v>970400</v>
       </c>
-      <c r="E35" t="str">
-        <v>SaigonBank</v>
-      </c>
-      <c r="F35" t="str">
-        <v>https://cdn.vietqr.io/img/SGICB.png</v>
-      </c>
-      <c r="G35" t="str">
-        <v>SaigonBank</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="E35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" t="s">
+        <v>141</v>
+      </c>
+      <c r="G35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>Ngân hàng TMCP Sài Gòn - Hà Nội</v>
-      </c>
-      <c r="C36" t="str">
-        <v>SHB</v>
+      <c r="B36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" t="s">
+        <v>143</v>
       </c>
       <c r="D36">
         <v>970443</v>
       </c>
-      <c r="E36" t="str">
-        <v>SHB</v>
-      </c>
-      <c r="F36" t="str">
-        <v>https://cdn.vietqr.io/img/SHB.png</v>
-      </c>
-      <c r="G36" t="str">
-        <v>SHB</v>
-      </c>
-    </row>
-    <row r="37">
+      <c r="E36" t="s">
+        <v>143</v>
+      </c>
+      <c r="F36" t="s">
+        <v>144</v>
+      </c>
+      <c r="G36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <v>Ngân hàng TMCP Sài Gòn Thương Tín</v>
-      </c>
-      <c r="C37" t="str">
-        <v>STB</v>
+      <c r="B37" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
       </c>
       <c r="D37">
         <v>970403</v>
       </c>
-      <c r="E37" t="str">
-        <v>Sacombank</v>
-      </c>
-      <c r="F37" t="str">
-        <v>https://cdn.vietqr.io/img/STB.png</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Sacombank</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="E37" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" t="s">
+        <v>148</v>
+      </c>
+      <c r="G37" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="str">
-        <v>Ngân hàng TNHH MTV Shinhan Việt Nam</v>
-      </c>
-      <c r="C38" t="str">
-        <v>SHBVN</v>
+      <c r="B38" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" t="s">
+        <v>150</v>
       </c>
       <c r="D38">
         <v>970424</v>
       </c>
-      <c r="E38" t="str">
-        <v>ShinhanBank</v>
-      </c>
-      <c r="F38" t="str">
-        <v>https://cdn.vietqr.io/img/SHBVN.png</v>
-      </c>
-      <c r="G38" t="str">
-        <v>ShinhanBank</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="E38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>Ngân hàng TMCP Kỹ thương Việt Nam</v>
-      </c>
-      <c r="C39" t="str">
-        <v>TCB</v>
+      <c r="B39" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" t="s">
+        <v>154</v>
       </c>
       <c r="D39">
         <v>970407</v>
       </c>
-      <c r="E39" t="str">
-        <v>Techcombank</v>
-      </c>
-      <c r="F39" t="str">
-        <v>https://cdn.vietqr.io/img/TCB.png</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Techcombank</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="E39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>Ngân hàng TMCP Tiên Phong</v>
-      </c>
-      <c r="C40" t="str">
-        <v>TPB</v>
+      <c r="B40" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" t="s">
+        <v>158</v>
       </c>
       <c r="D40">
         <v>970423</v>
       </c>
-      <c r="E40" t="str">
-        <v>TPBank</v>
-      </c>
-      <c r="F40" t="str">
-        <v>https://cdn.vietqr.io/img/TPB.png</v>
-      </c>
-      <c r="G40" t="str">
-        <v>TPBank</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="E40" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" t="s">
+        <v>160</v>
+      </c>
+      <c r="G40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="str">
-        <v>Ngân hàng United Overseas - Chi nhánh TP. Hồ Chí Minh</v>
-      </c>
-      <c r="C41" t="str">
-        <v>UOB</v>
+      <c r="B41" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" t="s">
+        <v>162</v>
       </c>
       <c r="D41">
         <v>970458</v>
       </c>
-      <c r="E41" t="str">
-        <v>UnitedOverseas</v>
-      </c>
-      <c r="F41" t="str">
-        <v>https://cdn.vietqr.io/img/UOB.png</v>
-      </c>
-      <c r="G41" t="str">
-        <v>UnitedOverseas</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="E41" t="s">
+        <v>163</v>
+      </c>
+      <c r="F41" t="s">
+        <v>164</v>
+      </c>
+      <c r="G41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="str">
-        <v>Ngân hàng TMCP Việt Á</v>
-      </c>
-      <c r="C42" t="str">
-        <v>VAB</v>
+      <c r="B42" t="s">
+        <v>165</v>
+      </c>
+      <c r="C42" t="s">
+        <v>166</v>
       </c>
       <c r="D42">
         <v>970427</v>
       </c>
-      <c r="E42" t="str">
-        <v>VietABank</v>
-      </c>
-      <c r="F42" t="str">
-        <v>https://cdn.vietqr.io/img/VAB.png</v>
-      </c>
-      <c r="G42" t="str">
-        <v>VietABank</v>
-      </c>
-    </row>
-    <row r="43">
+      <c r="E42" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42" t="s">
+        <v>168</v>
+      </c>
+      <c r="G42" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>Ngân hàng Nông nghiệp và Phát triển Nông thôn Việt Nam</v>
-      </c>
-      <c r="C43" t="str">
-        <v>VBA</v>
+      <c r="B43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" t="s">
+        <v>170</v>
       </c>
       <c r="D43">
         <v>970405</v>
       </c>
-      <c r="E43" t="str">
-        <v>Agribank</v>
-      </c>
-      <c r="F43" t="str">
-        <v>https://cdn.vietqr.io/img/VBA.png</v>
-      </c>
-      <c r="G43" t="str">
-        <v>Agribank</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="E43" t="s">
+        <v>171</v>
+      </c>
+      <c r="F43" t="s">
+        <v>172</v>
+      </c>
+      <c r="G43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="str">
-        <v>Ngân hàng TMCP Ngoại Thương Việt Nam</v>
-      </c>
-      <c r="C44" t="str">
-        <v>VCB</v>
+      <c r="B44" t="s">
+        <v>173</v>
+      </c>
+      <c r="C44" t="s">
+        <v>174</v>
       </c>
       <c r="D44">
         <v>970436</v>
       </c>
-      <c r="E44" t="str">
-        <v>Vietcombank</v>
-      </c>
-      <c r="F44" t="str">
-        <v>https://cdn.vietqr.io/img/VCB.png</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Vietcombank</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="E44" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" t="s">
+        <v>176</v>
+      </c>
+      <c r="G44" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="str">
-        <v>Ngân hàng TMCP Bản Việt</v>
-      </c>
-      <c r="C45" t="str">
-        <v>VCCB</v>
+      <c r="B45" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" t="s">
+        <v>178</v>
       </c>
       <c r="D45">
         <v>970454</v>
       </c>
-      <c r="E45" t="str">
-        <v>VietCapitalBank</v>
-      </c>
-      <c r="F45" t="str">
-        <v>https://cdn.vietqr.io/img/VCCB.png</v>
-      </c>
-      <c r="G45" t="str">
-        <v>VietCapitalBank</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="E45" t="s">
+        <v>179</v>
+      </c>
+      <c r="F45" t="s">
+        <v>180</v>
+      </c>
+      <c r="G45" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="str">
-        <v>Ngân hàng TMCP Quốc tế Việt Nam</v>
-      </c>
-      <c r="C46" t="str">
-        <v>VIB</v>
+      <c r="B46" t="s">
+        <v>181</v>
+      </c>
+      <c r="C46" t="s">
+        <v>182</v>
       </c>
       <c r="D46">
         <v>970441</v>
       </c>
-      <c r="E46" t="str">
-        <v>VIB</v>
-      </c>
-      <c r="F46" t="str">
-        <v>https://cdn.vietqr.io/img/VIB.png</v>
-      </c>
-      <c r="G46" t="str">
-        <v>VIB</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="E46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F46" t="s">
+        <v>183</v>
+      </c>
+      <c r="G46" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="str">
-        <v>Ngân hàng TMCP Việt Nam Thương Tín</v>
-      </c>
-      <c r="C47" t="str">
-        <v>VIETBANK</v>
+      <c r="B47" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" t="s">
+        <v>185</v>
       </c>
       <c r="D47">
         <v>970433</v>
       </c>
-      <c r="E47" t="str">
-        <v>VietBank</v>
-      </c>
-      <c r="F47" t="str">
-        <v>https://cdn.vietqr.io/img/VIETBANK.png</v>
-      </c>
-      <c r="G47" t="str">
-        <v>VietBank</v>
-      </c>
-    </row>
-    <row r="48">
+      <c r="E47" t="s">
+        <v>186</v>
+      </c>
+      <c r="F47" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="str">
-        <v>Ngân hàng TMCP Việt Nam Thịnh Vượng</v>
-      </c>
-      <c r="C48" t="str">
-        <v>VPB</v>
+      <c r="B48" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" t="s">
+        <v>189</v>
       </c>
       <c r="D48">
         <v>970432</v>
       </c>
-      <c r="E48" t="str">
-        <v>VPBank</v>
-      </c>
-      <c r="F48" t="str">
-        <v>https://cdn.vietqr.io/img/VPB.png</v>
-      </c>
-      <c r="G48" t="str">
-        <v>VPBank</v>
-      </c>
-    </row>
-    <row r="49">
+      <c r="E48" t="s">
+        <v>190</v>
+      </c>
+      <c r="F48" t="s">
+        <v>191</v>
+      </c>
+      <c r="G48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="str">
-        <v>Ngân hàng Liên doanh Việt - Nga</v>
-      </c>
-      <c r="C49" t="str">
-        <v>VRB</v>
+      <c r="B49" t="s">
+        <v>192</v>
+      </c>
+      <c r="C49" t="s">
+        <v>193</v>
       </c>
       <c r="D49">
         <v>970421</v>
       </c>
-      <c r="E49" t="str">
-        <v>VRB</v>
-      </c>
-      <c r="F49" t="str">
-        <v>https://cdn.vietqr.io/img/VRB.png</v>
-      </c>
-      <c r="G49" t="str">
-        <v>VRB</v>
-      </c>
-    </row>
-    <row r="50">
+      <c r="E49" t="s">
+        <v>193</v>
+      </c>
+      <c r="F49" t="s">
+        <v>194</v>
+      </c>
+      <c r="G49" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="str">
-        <v>Ngân hàng TNHH MTV Woori Việt Nam</v>
-      </c>
-      <c r="C50" t="str">
-        <v>WVN</v>
+      <c r="B50" t="s">
+        <v>195</v>
+      </c>
+      <c r="C50" t="s">
+        <v>196</v>
       </c>
       <c r="D50">
         <v>970457</v>
       </c>
-      <c r="E50" t="str">
-        <v>Woori</v>
-      </c>
-      <c r="F50" t="str">
-        <v>https://cdn.vietqr.io/img/WVN.png</v>
-      </c>
-      <c r="G50" t="str">
-        <v>Woori</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="E50" t="s">
+        <v>197</v>
+      </c>
+      <c r="F50" t="s">
+        <v>198</v>
+      </c>
+      <c r="G50" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="str">
-        <v>Ngân hàng Kookmin - Chi nhánh Hà Nội</v>
-      </c>
-      <c r="C51" t="str">
-        <v>KBHN</v>
+      <c r="B51" t="s">
+        <v>199</v>
+      </c>
+      <c r="C51" t="s">
+        <v>200</v>
       </c>
       <c r="D51">
         <v>970462</v>
       </c>
-      <c r="E51" t="str">
-        <v>KookminHN</v>
-      </c>
-      <c r="F51" t="str">
-        <v>https://cdn.vietqr.io/img/KBHN.png</v>
-      </c>
-      <c r="G51" t="str">
-        <v>KookminHN</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="E51" t="s">
+        <v>201</v>
+      </c>
+      <c r="F51" t="s">
+        <v>202</v>
+      </c>
+      <c r="G51" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="str">
-        <v>Ngân hàng Kookmin - Chi nhánh Thành phố Hồ Chí Minh</v>
-      </c>
-      <c r="C52" t="str">
-        <v>KBHCM</v>
+      <c r="B52" t="s">
+        <v>203</v>
+      </c>
+      <c r="C52" t="s">
+        <v>204</v>
       </c>
       <c r="D52">
         <v>970463</v>
       </c>
-      <c r="E52" t="str">
-        <v>KookminHCM</v>
-      </c>
-      <c r="F52" t="str">
-        <v>https://cdn.vietqr.io/img/KBHCM.png</v>
-      </c>
-      <c r="G52" t="str">
-        <v>KookminHCM</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="E52" t="s">
+        <v>205</v>
+      </c>
+      <c r="F52" t="s">
+        <v>206</v>
+      </c>
+      <c r="G52" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="str">
-        <v>Ngân hàng Hợp tác xã Việt Nam</v>
-      </c>
-      <c r="C53" t="str">
-        <v>COOPBANK</v>
+      <c r="B53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C53" t="s">
+        <v>208</v>
       </c>
       <c r="D53">
         <v>970446</v>
       </c>
-      <c r="E53" t="str">
-        <v>COOPBANK</v>
-      </c>
-      <c r="F53" t="str">
-        <v>https://cdn.vietqr.io/img/COOPBANK.png</v>
-      </c>
-      <c r="G53" t="str">
-        <v>COOPBANK</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="E53" t="s">
+        <v>208</v>
+      </c>
+      <c r="F53" t="s">
+        <v>209</v>
+      </c>
+      <c r="G53" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="str">
-        <v>TMCP Việt Nam Thịnh Vượng - Ngân hàng số CAKE by VPBank</v>
-      </c>
-      <c r="C54" t="str">
-        <v>CAKE</v>
+      <c r="B54" t="s">
+        <v>210</v>
+      </c>
+      <c r="C54" t="s">
+        <v>211</v>
       </c>
       <c r="D54">
         <v>546034</v>
       </c>
-      <c r="E54" t="str">
-        <v>CAKE</v>
-      </c>
-      <c r="F54" t="str">
-        <v>https://cdn.vietqr.io/img/CAKE.png</v>
-      </c>
-      <c r="G54" t="str">
-        <v>CAKE</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="E54" t="s">
+        <v>211</v>
+      </c>
+      <c r="F54" t="s">
+        <v>212</v>
+      </c>
+      <c r="G54" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="str">
-        <v>TMCP Việt Nam Thịnh Vượng - Ngân hàng số Ubank by VPBank</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Ubank</v>
+      <c r="B55" t="s">
+        <v>213</v>
+      </c>
+      <c r="C55" t="s">
+        <v>214</v>
       </c>
       <c r="D55">
         <v>546035</v>
       </c>
-      <c r="E55" t="str">
-        <v>Ubank</v>
-      </c>
-      <c r="F55" t="str">
-        <v>https://cdn.vietqr.io/img/UBANK.png</v>
-      </c>
-      <c r="G55" t="str">
-        <v>Ubank</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="E55" t="s">
+        <v>214</v>
+      </c>
+      <c r="F55" t="s">
+        <v>215</v>
+      </c>
+      <c r="G55" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="str">
-        <v>Ngân hàng Đại chúng TNHH Kasikornbank</v>
-      </c>
-      <c r="C56" t="str">
-        <v>KBank</v>
+      <c r="B56" t="s">
+        <v>216</v>
+      </c>
+      <c r="C56" t="s">
+        <v>217</v>
       </c>
       <c r="D56">
         <v>668888</v>
       </c>
-      <c r="E56" t="str">
-        <v>KBank</v>
-      </c>
-      <c r="F56" t="str">
-        <v>https://cdn.vietqr.io/img/KBANK.png</v>
-      </c>
-      <c r="G56" t="str">
-        <v>KBank</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="E56" t="s">
+        <v>217</v>
+      </c>
+      <c r="F56" t="s">
+        <v>218</v>
+      </c>
+      <c r="G56" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="str">
-        <v>VNPT Money</v>
-      </c>
-      <c r="C57" t="str">
-        <v>VNPTMONEY</v>
+      <c r="B57" t="s">
+        <v>219</v>
+      </c>
+      <c r="C57" t="s">
+        <v>220</v>
       </c>
       <c r="D57">
         <v>971011</v>
       </c>
-      <c r="E57" t="str">
-        <v>VNPTMoney</v>
-      </c>
-      <c r="F57" t="str">
-        <v>https://cdn.vietqr.io/img/VNPTMONEY.png</v>
-      </c>
-      <c r="G57" t="str">
-        <v>VNPTMoney</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="E57" t="s">
+        <v>221</v>
+      </c>
+      <c r="F57" t="s">
+        <v>222</v>
+      </c>
+      <c r="G57" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="str">
-        <v>Tổng Công ty Dịch vụ số Viettel - Chi nhánh tập đoàn công nghiệp viễn thông Quân Đội</v>
-      </c>
-      <c r="C58" t="str">
-        <v>VTLMONEY</v>
+      <c r="B58" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" t="s">
+        <v>224</v>
       </c>
       <c r="D58">
         <v>971005</v>
       </c>
-      <c r="E58" t="str">
-        <v>ViettelMoney</v>
-      </c>
-      <c r="F58" t="str">
-        <v>https://cdn.vietqr.io/img/VIETTELMONEY.png</v>
-      </c>
-      <c r="G58" t="str">
-        <v>ViettelMoney</v>
-      </c>
-    </row>
-    <row r="59">
+      <c r="E58" t="s">
+        <v>225</v>
+      </c>
+      <c r="F58" t="s">
+        <v>226</v>
+      </c>
+      <c r="G58" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="str">
-        <v>Ngân hàng số Timo by Ban Viet Bank (Timo by Ban Viet Bank)</v>
-      </c>
-      <c r="C59" t="str">
-        <v>TIMO</v>
+      <c r="B59" t="s">
+        <v>227</v>
+      </c>
+      <c r="C59" t="s">
+        <v>228</v>
       </c>
       <c r="D59">
         <v>963388</v>
       </c>
-      <c r="E59" t="str">
-        <v>Timo</v>
-      </c>
-      <c r="F59" t="str">
-        <v>https://vietqr.net/portal-service/resources/icons/TIMO.png</v>
-      </c>
-      <c r="G59" t="str">
-        <v>Timo</v>
-      </c>
-    </row>
-    <row r="60">
+      <c r="E59" t="s">
+        <v>229</v>
+      </c>
+      <c r="F59" t="s">
+        <v>230</v>
+      </c>
+      <c r="G59" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="str">
-        <v>Ngân hàng Citibank, N.A. - Chi nhánh Hà Nội</v>
-      </c>
-      <c r="C60" t="str">
-        <v>CITIBANK</v>
+      <c r="B60" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" t="s">
+        <v>232</v>
       </c>
       <c r="D60">
         <v>533948</v>
       </c>
-      <c r="E60" t="str">
-        <v>Citibank</v>
-      </c>
-      <c r="F60" t="str">
-        <v>https://cdn.vietqr.io/img/CITIBANK.png</v>
-      </c>
-      <c r="G60" t="str">
-        <v>Citibank</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="E60" t="s">
+        <v>233</v>
+      </c>
+      <c r="F60" t="s">
+        <v>234</v>
+      </c>
+      <c r="G60" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="str">
-        <v>Ngân hàng KEB Hana – Chi nhánh Thành phố Hồ Chí Minh</v>
-      </c>
-      <c r="C61" t="str">
-        <v>KEBHANAHCM</v>
+      <c r="B61" t="s">
+        <v>235</v>
+      </c>
+      <c r="C61" t="s">
+        <v>236</v>
       </c>
       <c r="D61">
         <v>970466</v>
       </c>
-      <c r="E61" t="str">
-        <v>KEBHanaHCM</v>
-      </c>
-      <c r="F61" t="str">
-        <v>https://cdn.vietqr.io/img/KEBHANAHCM.png</v>
-      </c>
-      <c r="G61" t="str">
-        <v>KEBHanaHCM</v>
-      </c>
-    </row>
-    <row r="62">
+      <c r="E61" t="s">
+        <v>237</v>
+      </c>
+      <c r="F61" t="s">
+        <v>238</v>
+      </c>
+      <c r="G61" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="str">
-        <v>Ngân hàng KEB Hana – Chi nhánh Hà Nội</v>
-      </c>
-      <c r="C62" t="str">
-        <v>KEBHANAHN</v>
+      <c r="B62" t="s">
+        <v>239</v>
+      </c>
+      <c r="C62" t="s">
+        <v>240</v>
       </c>
       <c r="D62">
         <v>970467</v>
       </c>
-      <c r="E62" t="str">
-        <v>KEBHANAHN</v>
-      </c>
-      <c r="F62" t="str">
-        <v>https://cdn.vietqr.io/img/KEBHANAHN.png</v>
-      </c>
-      <c r="G62" t="str">
-        <v>KEBHANAHN</v>
-      </c>
-    </row>
-    <row r="63">
+      <c r="E62" t="s">
+        <v>240</v>
+      </c>
+      <c r="F62" t="s">
+        <v>241</v>
+      </c>
+      <c r="G62" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="str">
-        <v>Công ty Tài chính TNHH MTV Mirae Asset (Việt Nam)</v>
-      </c>
-      <c r="C63" t="str">
-        <v>MAFC</v>
+      <c r="B63" t="s">
+        <v>242</v>
+      </c>
+      <c r="C63" t="s">
+        <v>243</v>
       </c>
       <c r="D63">
         <v>977777</v>
       </c>
-      <c r="E63" t="str">
-        <v>MAFC</v>
-      </c>
-      <c r="F63" t="str">
-        <v>https://cdn.vietqr.io/img/MAFC.png</v>
-      </c>
-      <c r="G63" t="str">
-        <v>MAFC</v>
-      </c>
-    </row>
-    <row r="64">
+      <c r="E63" t="s">
+        <v>243</v>
+      </c>
+      <c r="F63" t="s">
+        <v>244</v>
+      </c>
+      <c r="G63" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="str">
-        <v>Ngân hàng Chính sách Xã hội</v>
-      </c>
-      <c r="C64" t="str">
-        <v>VBSP</v>
+      <c r="B64" t="s">
+        <v>245</v>
+      </c>
+      <c r="C64" t="s">
+        <v>246</v>
       </c>
       <c r="D64">
         <v>999888</v>
       </c>
-      <c r="E64" t="str">
-        <v>VBSP</v>
-      </c>
-      <c r="F64" t="str">
-        <v>https://cdn.vietqr.io/img/VBSP.png</v>
-      </c>
-      <c r="G64" t="str">
-        <v>VBSP</v>
-      </c>
-    </row>
-    <row r="65">
+      <c r="E64" t="s">
+        <v>246</v>
+      </c>
+      <c r="F64" t="s">
+        <v>247</v>
+      </c>
+      <c r="G64" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="str">
-        <v>Ngân hàng TMCP Đại Chúng Việt Nam Ngân hàng số</v>
-      </c>
-      <c r="C65" t="str">
-        <v>PVDB</v>
+      <c r="B65" t="s">
+        <v>248</v>
+      </c>
+      <c r="C65" t="s">
+        <v>249</v>
       </c>
       <c r="D65">
         <v>971133</v>
       </c>
-      <c r="E65" t="str">
-        <v>PVcomBank Pay</v>
-      </c>
-      <c r="F65" t="str">
-        <v>https://cdn.vietqr.io/img/PVCB.png</v>
-      </c>
-      <c r="G65" t="str">
-        <v>PVcomBank Pay</v>
-      </c>
-    </row>
-    <row r="66">
+      <c r="E65" t="s">
+        <v>250</v>
+      </c>
+      <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="str">
-        <v>CTCP Dịch Vụ Di Động Trực Tuyến</v>
-      </c>
-      <c r="C66" t="str">
-        <v>momo</v>
+      <c r="B66" t="s">
+        <v>251</v>
+      </c>
+      <c r="C66" t="s">
+        <v>252</v>
       </c>
       <c r="D66">
         <v>971025</v>
       </c>
-      <c r="E66" t="str">
-        <v>MoMo</v>
-      </c>
-      <c r="F66" t="str">
-        <v>https://cdn.vietqr.io/img/momo.png</v>
-      </c>
-      <c r="G66" t="str">
-        <v>MoMo</v>
+      <c r="E66" t="s">
+        <v>253</v>
+      </c>
+      <c r="F66" t="s">
+        <v>254</v>
+      </c>
+      <c r="G66" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
-    <hyperlink ref="F13" r:id="rId12"/>
-    <hyperlink ref="F14" r:id="rId13"/>
-    <hyperlink ref="F15" r:id="rId14"/>
-    <hyperlink ref="F16" r:id="rId15"/>
-    <hyperlink ref="F17" r:id="rId16"/>
-    <hyperlink ref="F18" r:id="rId17"/>
-    <hyperlink ref="F19" r:id="rId18"/>
-    <hyperlink ref="F20" r:id="rId19"/>
-    <hyperlink ref="F21" r:id="rId20"/>
-    <hyperlink ref="F22" r:id="rId21"/>
-    <hyperlink ref="F23" r:id="rId22"/>
-    <hyperlink ref="F24" r:id="rId23"/>
-    <hyperlink ref="F25" r:id="rId24"/>
-    <hyperlink ref="F26" r:id="rId25"/>
-    <hyperlink ref="F27" r:id="rId26"/>
-    <hyperlink ref="F28" r:id="rId27"/>
-    <hyperlink ref="F29" r:id="rId28"/>
-    <hyperlink ref="F30" r:id="rId29"/>
-    <hyperlink ref="F31" r:id="rId30"/>
-    <hyperlink ref="F32" r:id="rId31"/>
-    <hyperlink ref="F33" r:id="rId32"/>
-    <hyperlink ref="F34" r:id="rId33"/>
-    <hyperlink ref="F35" r:id="rId34"/>
-    <hyperlink ref="F36" r:id="rId35"/>
-    <hyperlink ref="F37" r:id="rId36"/>
-    <hyperlink ref="F38" r:id="rId37"/>
-    <hyperlink ref="F39" r:id="rId38"/>
-    <hyperlink ref="F40" r:id="rId39"/>
-    <hyperlink ref="F41" r:id="rId40"/>
-    <hyperlink ref="F42" r:id="rId41"/>
-    <hyperlink ref="F43" r:id="rId42"/>
-    <hyperlink ref="F44" r:id="rId43"/>
-    <hyperlink ref="F45" r:id="rId44"/>
-    <hyperlink ref="F46" r:id="rId45"/>
-    <hyperlink ref="F47" r:id="rId46"/>
-    <hyperlink ref="F48" r:id="rId47"/>
-    <hyperlink ref="F49" r:id="rId48"/>
-    <hyperlink ref="F50" r:id="rId49"/>
-    <hyperlink ref="F51" r:id="rId50"/>
-    <hyperlink ref="F52" r:id="rId51"/>
-    <hyperlink ref="F53" r:id="rId52"/>
-    <hyperlink ref="F54" r:id="rId53"/>
-    <hyperlink ref="F55" r:id="rId54"/>
-    <hyperlink ref="F56" r:id="rId55"/>
-    <hyperlink ref="F57" r:id="rId56"/>
-    <hyperlink ref="F58" r:id="rId57"/>
-    <hyperlink ref="F59" r:id="rId58"/>
-    <hyperlink ref="F60" r:id="rId59"/>
-    <hyperlink ref="F61" r:id="rId60"/>
-    <hyperlink ref="F62" r:id="rId61"/>
-    <hyperlink ref="F63" r:id="rId62"/>
-    <hyperlink ref="F64" r:id="rId63"/>
-    <hyperlink ref="F65" r:id="rId64"/>
-    <hyperlink ref="F66" r:id="rId65"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="F13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="F14" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="F15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="F16" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="F17" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="F18" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="F19" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="F20" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="F21" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="F24" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="F25" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="F26" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="F27" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="F29" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="F30" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="F31" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="F32" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="F33" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="F34" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="F35" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="F36" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="F37" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="F38" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="F39" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="F40" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="F41" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="F43" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="F44" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="F45" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="F46" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="F48" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="F49" r:id="rId48" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="F50" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="F51" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="F52" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="F53" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="F54" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="F55" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="F56" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="F57" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="F58" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
+    <hyperlink ref="F59" r:id="rId58" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="F60" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="F61" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="F62" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
+    <hyperlink ref="F63" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="F64" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="F65" r:id="rId64" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="F66" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H66"/>
+    <ignoredError sqref="A1:H66" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9387026-A75E-43E3-A1C6-668129E5258B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18EE9FA-F004-4C76-92B3-7DC50494CF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="261">
   <si>
     <t>data__id</t>
   </si>
@@ -802,6 +802,21 @@
   </si>
   <si>
     <t>0582118210</t>
+  </si>
+  <si>
+    <t>0396105538</t>
+  </si>
+  <si>
+    <t>0396105653</t>
+  </si>
+  <si>
+    <t>TCB_446</t>
+  </si>
+  <si>
+    <t>MOMO _ 538</t>
+  </si>
+  <si>
+    <t>MOMO _ 635</t>
   </si>
 </sst>
 </file>
@@ -1180,14 +1195,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1219,13 +1234,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>38</v>
       </c>
-      <c r="B2" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+      <c r="B2" t="s">
+        <v>258</v>
       </c>
       <c r="C2">
         <v>44699999999</v>
@@ -1258,13 +1272,12 @@
         <v>Techcombank</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>43</v>
       </c>
-      <c r="B3" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+      <c r="B3" t="s">
+        <v>174</v>
       </c>
       <c r="C3">
         <v>1031451081</v>
@@ -1297,13 +1310,12 @@
         <v>Vietcombank</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26</v>
       </c>
-      <c r="B4" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+      <c r="B4" t="s">
+        <v>110</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>255</v>
@@ -1336,10 +1348,18 @@
         <v>OCB</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
       </c>
       <c r="E5" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1349,27 +1369,35 @@
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G5">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>971025</v>
       </c>
       <c r="H5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
       <c r="I5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/momo.png</v>
       </c>
       <c r="J5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
       </c>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1379,24 +1407,24 @@
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G6">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>971025</v>
       </c>
       <c r="H6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
       <c r="I6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/momo.png</v>
       </c>
       <c r="J6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>MoMo</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1426,7 +1454,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1456,7 +1484,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1486,7 +1514,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1516,7 +1544,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1546,7 +1574,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1576,7 +1604,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1606,7 +1634,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1636,7 +1664,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1666,7 +1694,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1696,7 +1724,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1726,7 +1754,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1756,7 +1784,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1786,7 +1814,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1816,7 +1844,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1846,7 +1874,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1876,7 +1904,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1906,7 +1934,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1936,7 +1964,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1966,7 +1994,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1996,7 +2024,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2026,7 +2054,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2056,7 +2084,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2086,7 +2114,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2116,7 +2144,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="31" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2146,7 +2174,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2176,7 +2204,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2206,7 +2234,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2236,7 +2264,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2266,7 +2294,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2296,7 +2324,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2326,7 +2354,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="38" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2356,7 +2384,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2386,7 +2414,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2416,7 +2444,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2446,7 +2474,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="42" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2476,7 +2504,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2506,7 +2534,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2536,7 +2564,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2566,7 +2594,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="46" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2596,7 +2624,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2626,7 +2654,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="48" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2656,7 +2684,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2686,7 +2714,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2716,7 +2744,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="51" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2746,7 +2774,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2776,7 +2804,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="53" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2806,7 +2834,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2836,7 +2864,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="55" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2866,7 +2894,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2896,7 +2924,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="57" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2926,7 +2954,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="58" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2956,7 +2984,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="59" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2986,7 +3014,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="60" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3016,7 +3044,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="61" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3046,7 +3074,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="62" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3076,7 +3104,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="63" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3106,7 +3134,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="64" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3136,7 +3164,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="65" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3166,7 +3194,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="66" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3196,7 +3224,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="67" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3226,7 +3254,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="68" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3256,7 +3284,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="69" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3286,7 +3314,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="70" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3316,7 +3344,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="71" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3346,7 +3374,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="72" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3376,7 +3404,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="73" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3406,7 +3434,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="74" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3436,7 +3464,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="75" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3466,7 +3494,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="76" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3496,7 +3524,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="77" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3526,7 +3554,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="78" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3556,7 +3584,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="79" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3586,7 +3614,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="80" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3616,7 +3644,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="81" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3646,7 +3674,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="82" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3676,7 +3704,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="83" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3706,7 +3734,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="84" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3736,7 +3764,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="85" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3766,7 +3794,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="86" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3796,7 +3824,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="87" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3826,7 +3854,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="88" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3856,7 +3884,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="89" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3886,7 +3914,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="90" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3916,7 +3944,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="91" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3946,7 +3974,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="92" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3976,7 +4004,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="93" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4006,7 +4034,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="94" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4036,7 +4064,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="95" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4066,7 +4094,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="96" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4096,7 +4124,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="97" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4126,7 +4154,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="98" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4156,7 +4184,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="99" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4186,7 +4214,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="100" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4216,7 +4244,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="101" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4351,7 +4379,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J3 A5:J101 B4 E4:J4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A7:J101 E4:J4 E5:J5 E6:J6 A3 A2 C2:J2 C3:J3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4359,7 +4387,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H66"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="75" bestFit="1" customWidth="1"/>
@@ -4371,7 +4399,7 @@
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4397,7 +4425,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4423,7 +4451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4449,7 +4477,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4475,7 +4503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4501,7 +4529,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4527,7 +4555,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4550,7 +4578,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4573,7 +4601,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4596,7 +4624,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4619,7 +4647,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4642,7 +4670,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4665,7 +4693,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4688,7 +4716,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4711,7 +4739,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4734,7 +4762,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4757,7 +4785,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4780,7 +4808,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4803,7 +4831,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4826,7 +4854,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4849,7 +4877,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4872,7 +4900,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4895,7 +4923,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4918,7 +4946,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4941,7 +4969,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4964,7 +4992,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4987,7 +5015,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5010,7 +5038,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5033,7 +5061,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5056,7 +5084,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5079,7 +5107,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5102,7 +5130,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5125,7 +5153,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5148,7 +5176,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5171,7 +5199,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5194,7 +5222,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5217,7 +5245,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5240,7 +5268,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5263,7 +5291,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5286,7 +5314,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5309,7 +5337,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5332,7 +5360,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5355,7 +5383,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5378,7 +5406,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5401,7 +5429,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5424,7 +5452,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5447,7 +5475,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5470,7 +5498,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5493,7 +5521,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5516,7 +5544,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5539,7 +5567,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5562,7 +5590,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5585,7 +5613,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5608,7 +5636,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5631,7 +5659,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5654,7 +5682,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5677,7 +5705,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5700,7 +5728,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5723,7 +5751,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5746,7 +5774,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5769,7 +5797,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5792,7 +5820,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5815,7 +5843,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5838,7 +5866,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5861,7 +5889,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5884,7 +5912,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18EE9FA-F004-4C76-92B3-7DC50494CF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CD9FC9-D12D-4B92-A952-9C10267CCB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="261">
   <si>
     <t>data__id</t>
   </si>
@@ -1198,7 +1198,7 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1455,10 +1455,19 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>12</v>
+      </c>
       <c r="B8" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
       <c r="E8" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1467,21 +1476,21 @@
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G8">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970437</v>
       </c>
       <c r="H8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>HDBank</v>
       </c>
       <c r="I8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/HDB.png</v>
       </c>
       <c r="J8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>HDBank</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -4379,7 +4388,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 A7:J101 E4:J4 E5:J5 E6:J6 A3 A2 C2:J2 C3:J3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A7:J7 E4:J4 E5:J5 E6:J6 A3 A2 C2:J2 C3:J3 A9:J101 B8 E8:J8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CD9FC9-D12D-4B92-A952-9C10267CCB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF1AD3A-3C74-4E3B-8610-DE555864D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1198,8 +1198,14 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1311,9 +1317,6 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>26</v>
-      </c>
       <c r="B4" t="s">
         <v>110</v>
       </c>
@@ -1331,27 +1334,24 @@
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970448</v>
+        <v>-</v>
       </c>
       <c r="H4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>OCB</v>
+        <v>-</v>
       </c>
       <c r="I4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/OCB.png</v>
+        <v>-</v>
       </c>
       <c r="J4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>OCB</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>65</v>
-      </c>
       <c r="B5" t="s">
         <v>259</v>
       </c>
@@ -1369,27 +1369,24 @@
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>971025</v>
+        <v>-</v>
       </c>
       <c r="H5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>MoMo</v>
+        <v>-</v>
       </c>
       <c r="I5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/momo.png</v>
+        <v>-</v>
       </c>
       <c r="J5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>MoMo</v>
+        <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>65</v>
-      </c>
       <c r="B6" t="s">
         <v>260</v>
       </c>
@@ -1407,21 +1404,21 @@
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>971025</v>
+        <v>-</v>
       </c>
       <c r="H6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>MoMo</v>
+        <v>-</v>
       </c>
       <c r="I6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/momo.png</v>
+        <v>-</v>
       </c>
       <c r="J6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>MoMo</v>
+        <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1455,9 +1452,6 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>12</v>
-      </c>
       <c r="B8" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1476,21 +1470,21 @@
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970437</v>
+        <v>-</v>
       </c>
       <c r="H8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>HDBank</v>
+        <v>-</v>
       </c>
       <c r="I8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/HDB.png</v>
+        <v>-</v>
       </c>
       <c r="J8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>HDBank</v>
+        <v>-</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -4388,7 +4382,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 A7:J7 E4:J4 E5:J5 E6:J6 A3 A2 C2:J2 C3:J3 A9:J101 B8 E8:J8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 B7:J7 E4:J4 E5:J5 E6:J6 A3 A2 C2:J2 C3:J3 A10:J101 B8 E8:J8 B9:J9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF1AD3A-3C74-4E3B-8610-DE555864D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D970E974-4F83-45ED-95A4-0CDD0B345132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="256">
   <si>
     <t>data__id</t>
   </si>
@@ -801,22 +801,7 @@
     <t>https://cdn.vietqr.io/img/momo.png</t>
   </si>
   <si>
-    <t>0582118210</t>
-  </si>
-  <si>
-    <t>0396105538</t>
-  </si>
-  <si>
-    <t>0396105653</t>
-  </si>
-  <si>
     <t>TCB_446</t>
-  </si>
-  <si>
-    <t>MOMO _ 538</t>
-  </si>
-  <si>
-    <t>MOMO _ 635</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1230,7 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C2">
         <v>44699999999</v>
@@ -1317,15 +1302,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="E4" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1352,15 +1329,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="1"/>
       <c r="E5" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1387,15 +1356,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
+      <c r="C6" s="1"/>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1422,10 +1383,6 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B7" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1452,16 +1409,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B8" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
+      <c r="C8" s="1"/>
       <c r="E8" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4382,7 +4330,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 B7:J7 E4:J4 E5:J5 E6:J6 A3 A2 C2:J2 C3:J3 A10:J101 B8 E8:J8 B9:J9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 E7:J7 E4:J4 E5:J5 E6:J6 A3 A2 C2:J2 C3:J3 A10:J101 E8:J8 B9:J9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10529"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -16,7 +16,7 @@
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
     <sheet name="API - io" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="258">
   <si>
     <t>data__id</t>
   </si>
@@ -802,6 +802,12 @@
   </si>
   <si>
     <t>TCB_446</t>
+  </si>
+  <si>
+    <t>TCB -iPanDa</t>
+  </si>
+  <si>
+    <t>MS00T09548691713297</t>
   </si>
 </sst>
 </file>
@@ -812,7 +818,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -842,7 +848,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -1180,20 +1186,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J101"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.3125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.91015625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.21484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.34765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.67578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.06640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.02734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>38</v>
       </c>
@@ -1263,7 +1269,7 @@
         <v>Techcombank</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>43</v>
       </c>
@@ -1301,8 +1307,19 @@
         <v>Vietcombank</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="1"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
       <c r="E4" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1311,24 +1328,24 @@
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970407</v>
       </c>
       <c r="H4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>Techcombank</v>
       </c>
       <c r="I4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>Techcombank</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="C5" s="1"/>
       <c r="E5" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1355,7 +1372,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="C6" s="1"/>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1382,7 +1399,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1408,7 +1425,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="C8" s="1"/>
       <c r="E8" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1435,7 +1452,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B9" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1465,7 +1482,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1495,7 +1512,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1525,7 +1542,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1555,7 +1572,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1585,7 +1602,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1615,7 +1632,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1645,7 +1662,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1675,7 +1692,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B17" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1705,7 +1722,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B18" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1735,7 +1752,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B19" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1765,7 +1782,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B20" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1795,7 +1812,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B21" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1825,7 +1842,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B22" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1855,7 +1872,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B23" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1885,7 +1902,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B24" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1915,7 +1932,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B25" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1945,7 +1962,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B26" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1975,7 +1992,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B27" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2005,7 +2022,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B28" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2035,7 +2052,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B29" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2065,7 +2082,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B30" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2095,7 +2112,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B31" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2125,7 +2142,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B32" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2155,7 +2172,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B33" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2185,7 +2202,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B34" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2215,7 +2232,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B35" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2245,7 +2262,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B36" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2275,7 +2292,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B37" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2305,7 +2322,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B38" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2335,7 +2352,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B39" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2365,7 +2382,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B40" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2395,7 +2412,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B41" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2425,7 +2442,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B42" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2455,7 +2472,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B43" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2485,7 +2502,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B44" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2515,7 +2532,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B45" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2545,7 +2562,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B46" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2575,7 +2592,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B47" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2605,7 +2622,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B48" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2635,7 +2652,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B49" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2665,7 +2682,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B50" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2695,7 +2712,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B51" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2725,7 +2742,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B52" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2755,7 +2772,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B53" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2785,7 +2802,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B54" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2815,7 +2832,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B55" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2845,7 +2862,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B56" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2875,7 +2892,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B57" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2905,7 +2922,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B58" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2935,7 +2952,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B59" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2965,7 +2982,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B60" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2995,7 +3012,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B61" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3025,7 +3042,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B62" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3055,7 +3072,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B63" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3085,7 +3102,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B64" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3115,7 +3132,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B65" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3145,7 +3162,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B66" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3175,7 +3192,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B67" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3205,7 +3222,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B68" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3235,7 +3252,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B69" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3265,7 +3282,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B70" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3295,7 +3312,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B71" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3325,7 +3342,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B72" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3355,7 +3372,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3385,7 +3402,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3415,7 +3432,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B75" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3445,7 +3462,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B76" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3475,7 +3492,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B77" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3505,7 +3522,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B78" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3535,7 +3552,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B79" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3565,7 +3582,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B80" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3595,7 +3612,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B81" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3625,7 +3642,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B82" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3655,7 +3672,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B83" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3685,7 +3702,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B84" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3715,7 +3732,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B85" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3745,7 +3762,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B86" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3775,7 +3792,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B87" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3805,7 +3822,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B88" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3835,7 +3852,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B89" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3865,7 +3882,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B90" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3895,7 +3912,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B91" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3925,7 +3942,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B92" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3955,7 +3972,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B93" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3985,7 +4002,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B94" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4015,7 +4032,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B95" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4045,7 +4062,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B96" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4075,7 +4092,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B97" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4105,7 +4122,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B98" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4135,7 +4152,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B99" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4165,7 +4182,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B100" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4195,7 +4212,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B101" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4338,19 +4355,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H66"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.3125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.03515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.078125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.98828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4376,7 +4393,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4402,7 +4419,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4428,7 +4445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4454,7 +4471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4480,7 +4497,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4506,7 +4523,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4529,7 +4546,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4552,7 +4569,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4575,7 +4592,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4598,7 +4615,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4621,7 +4638,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4644,7 +4661,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4667,7 +4684,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4690,7 +4707,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4713,7 +4730,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4736,7 +4753,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4759,7 +4776,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4782,7 +4799,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4805,7 +4822,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4828,7 +4845,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4851,7 +4868,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4874,7 +4891,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4897,7 +4914,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4920,7 +4937,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4943,7 +4960,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4966,7 +4983,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4989,7 +5006,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5012,7 +5029,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5035,7 +5052,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5058,7 +5075,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5081,7 +5098,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5104,7 +5121,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5127,7 +5144,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5150,7 +5167,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5173,7 +5190,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5196,7 +5213,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5219,7 +5236,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5242,7 +5259,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5265,7 +5282,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5288,7 +5305,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5311,7 +5328,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5334,7 +5351,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5357,7 +5374,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5380,7 +5397,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5403,7 +5420,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5426,7 +5443,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5449,7 +5466,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5472,7 +5489,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5495,7 +5512,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5518,7 +5535,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5541,7 +5558,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5564,7 +5581,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5587,7 +5604,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5610,7 +5627,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5633,7 +5650,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5656,7 +5673,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5679,7 +5696,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5702,7 +5719,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5725,7 +5742,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5748,7 +5765,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5771,7 +5788,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5794,7 +5811,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5817,7 +5834,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5840,7 +5857,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5863,7 +5880,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>65</v>
       </c>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D970E974-4F83-45ED-95A4-0CDD0B345132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F892DD6E-BF63-4698-942B-CE64D4A55FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="258">
   <si>
     <t>data__id</t>
   </si>
@@ -818,7 +818,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -848,7 +848,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -1186,20 +1186,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J101"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.3125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.91015625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.21484375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.34765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.67578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.4375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.06640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.02734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1231,15 +1231,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C2">
-        <v>44699999999</v>
+        <v>256</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1269,15 +1269,15 @@
         <v>Techcombank</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="C3">
-        <v>1031451081</v>
+        <v>44699999999</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1292,34 +1292,22 @@
       </c>
       <c r="G3">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970436</v>
+        <v>970407</v>
       </c>
       <c r="H3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="I3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/VCB.png</v>
+        <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Vietcombank</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
+        <v>Techcombank</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E4" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1329,23 +1317,23 @@
         <v>-</v>
       </c>
       <c r="G4">
-        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
         <v>970407</v>
       </c>
       <c r="H4" t="str">
-        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</f>
         <v>Techcombank</v>
       </c>
       <c r="I4" t="str">
-        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</f>
         <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J4" t="str">
-        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</f>
         <v>Techcombank</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
       <c r="E5" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1372,7 +1360,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1399,7 +1387,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1425,7 +1413,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="E8" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1452,7 +1440,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1482,7 +1470,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1512,7 +1500,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1542,7 +1530,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1572,7 +1560,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1602,7 +1590,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1632,7 +1620,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1662,7 +1650,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1692,7 +1680,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1722,7 +1710,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1752,7 +1740,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1782,7 +1770,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1812,7 +1800,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1842,7 +1830,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1872,7 +1860,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1902,7 +1890,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1932,7 +1920,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1962,7 +1950,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -1992,7 +1980,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2022,7 +2010,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2052,7 +2040,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2082,7 +2070,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2112,7 +2100,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2142,7 +2130,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2172,7 +2160,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2202,7 +2190,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2232,7 +2220,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2262,7 +2250,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2292,7 +2280,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2322,7 +2310,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2352,7 +2340,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2382,7 +2370,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2412,7 +2400,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2442,7 +2430,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2472,7 +2460,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2502,7 +2490,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2532,7 +2520,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2562,7 +2550,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2592,7 +2580,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2622,7 +2610,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2652,7 +2640,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2682,7 +2670,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2712,7 +2700,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2742,7 +2730,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2772,7 +2760,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2802,7 +2790,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2832,7 +2820,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2862,7 +2850,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2892,7 +2880,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2922,7 +2910,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2952,7 +2940,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -2982,7 +2970,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3012,7 +3000,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3042,7 +3030,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3072,7 +3060,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3102,7 +3090,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3132,7 +3120,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3162,7 +3150,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3192,7 +3180,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3222,7 +3210,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3252,7 +3240,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3282,7 +3270,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3312,7 +3300,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3342,7 +3330,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3372,7 +3360,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3402,7 +3390,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3432,7 +3420,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3462,7 +3450,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3492,7 +3480,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3522,7 +3510,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3552,7 +3540,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3582,7 +3570,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3612,7 +3600,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3642,7 +3630,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3672,7 +3660,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3702,7 +3690,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3732,7 +3720,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3762,7 +3750,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3792,7 +3780,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3822,7 +3810,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3852,7 +3840,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3882,7 +3870,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3912,7 +3900,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3942,7 +3930,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -3972,7 +3960,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4002,7 +3990,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4032,7 +4020,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4062,7 +4050,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4092,7 +4080,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4122,7 +4110,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4152,7 +4140,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4182,7 +4170,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4212,7 +4200,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
@@ -4244,110 +4232,110 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="I3" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="I4" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="I5" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="I6" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="I7" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="I8" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="I9" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="I10" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="I11" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="I12" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="I13" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="I14" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="I15" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="I16" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="I17" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="I18" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="I19" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="I20" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="I21" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="I22" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="I23" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="I24" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="I25" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="I26" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="I27" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="I28" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="I29" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="I30" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="I31" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="I32" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="I33" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="I34" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="I35" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="I36" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="I37" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="I38" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="I39" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="I40" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="I41" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="I42" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="I43" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="I44" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="I45" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="I46" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="I47" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="I48" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="I49" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="I50" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="I51" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="I52" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="I53" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="I54" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="I55" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="I56" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="I57" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="I58" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="I59" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="I60" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="I61" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="I62" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="I63" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="I64" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="I65" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="I66" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="I67" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="I68" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="I69" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="I70" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="I71" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="I72" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="I73" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="I74" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="I75" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="I76" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="I77" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="I78" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="I79" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="I80" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="I81" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="I82" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="I83" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="I84" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="I85" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="I86" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="I87" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="I88" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="I89" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="I90" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="I91" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="I92" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="I93" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="I94" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="I95" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="I96" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="I97" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="I98" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="I99" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="I100" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="I101" r:id="rId100" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="I3" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="I4" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I5" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I6" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I7" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I8" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I9" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I10" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I11" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I12" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="I13" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I14" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="I15" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I16" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="I17" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I18" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="I19" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="I20" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I21" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I22" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="I23" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="I24" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="I25" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="I26" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="I27" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="I28" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="I29" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="I30" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="I31" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="I32" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="I33" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="I34" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="I35" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="I36" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="I37" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="I38" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="I39" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="I40" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="I41" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="I42" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="I43" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="I44" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="I45" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="I46" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="I47" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="I48" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="I49" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="I50" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="I51" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="I52" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="I53" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="I54" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="I55" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="I56" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="I57" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="I58" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="I59" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="I60" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="I61" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="I62" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="I63" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="I64" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="I65" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="I66" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="I67" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="I68" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="I69" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="I70" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="I71" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="I72" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="I73" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="I74" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="I75" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="I76" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="I77" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="I78" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="I79" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="I80" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="I81" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="I82" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="I83" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="I84" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="I85" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="I86" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="I87" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="I88" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="I89" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="I90" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="I91" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="I92" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="I93" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="I94" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="I95" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="I96" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="I97" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="I98" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="I99" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="I100" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="I101" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="I2" r:id="rId100" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A736BAC9-60DF-4FD9-8691-3E1611B7D304}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 E7:J7 E4:J4 E5:J5 E6:J6 A3 A2 C2:J2 C3:J3 A10:J101 E8:J8 B9:J9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 E7:J7 E4:J4 E5:J5 E6:J6 A3 C3:J3 A10:J101 E8:J8 B9:J9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4355,19 +4343,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H66"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.3125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.03515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.4375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.078125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.078125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.98828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4393,7 +4381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4419,7 +4407,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4445,7 +4433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4471,7 +4459,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4497,7 +4485,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4523,7 +4511,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4546,7 +4534,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4569,7 +4557,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4592,7 +4580,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4615,7 +4603,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4638,7 +4626,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4661,7 +4649,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4684,7 +4672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4707,7 +4695,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4730,7 +4718,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4753,7 +4741,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4776,7 +4764,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4799,7 +4787,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4822,7 +4810,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4845,7 +4833,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4868,7 +4856,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4891,7 +4879,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4914,7 +4902,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4937,7 +4925,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4960,7 +4948,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4983,7 +4971,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5006,7 +4994,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5029,7 +5017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5052,7 +5040,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5075,7 +5063,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5098,7 +5086,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5121,7 +5109,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5144,7 +5132,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5167,7 +5155,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5190,7 +5178,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5213,7 +5201,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5236,7 +5224,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5259,7 +5247,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5282,7 +5270,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5305,7 +5293,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5328,7 +5316,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5351,7 +5339,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5374,7 +5362,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5397,7 +5385,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5420,7 +5408,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5443,7 +5431,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5466,7 +5454,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5489,7 +5477,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5512,7 +5500,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5535,7 +5523,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5558,7 +5546,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5581,7 +5569,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5604,7 +5592,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5627,7 +5615,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5650,7 +5638,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5673,7 +5661,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5696,7 +5684,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5719,7 +5707,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5742,7 +5730,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5765,7 +5753,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5788,7 +5776,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5811,7 +5799,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5834,7 +5822,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5857,7 +5845,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5880,7 +5868,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F892DD6E-BF63-4698-942B-CE64D4A55FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DA8D9C-05C3-486B-BBF0-219DCAE263B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="260">
   <si>
     <t>data__id</t>
   </si>
@@ -808,6 +808,12 @@
   </si>
   <si>
     <t>MS00T09548691713297</t>
+  </si>
+  <si>
+    <t>VIB _ 064</t>
+  </si>
+  <si>
+    <t>064933000</t>
   </si>
 </sst>
 </file>
@@ -1185,13 +1191,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.09765625" bestFit="1" customWidth="1"/>
@@ -1245,12 +1251,12 @@
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,5,0)),"-")</f>
+        <v>Techcombank</v>
       </c>
       <c r="F2" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>TCB</v>
       </c>
       <c r="G2">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
@@ -1283,12 +1289,12 @@
         <v>10</v>
       </c>
       <c r="E3" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,5,0)),"-")</f>
+        <v>Techcombank</v>
       </c>
       <c r="F3" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+        <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>TCB</v>
       </c>
       <c r="G3">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
@@ -1308,29 +1314,41 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
       <c r="E4" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$H,5,0)),"-")</f>
+        <v>VIB</v>
       </c>
       <c r="F4" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
+        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$H,3,0)),"-")</f>
+        <v>VIB</v>
       </c>
       <c r="G4">
-        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970407</v>
+        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
+        <v>970441</v>
       </c>
       <c r="H4" t="str">
-        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
+        <v>VIB</v>
       </c>
       <c r="I4" t="str">
-        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/TCB.png</v>
+        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
+        <v>https://cdn.vietqr.io/img/VIB.png</v>
       </c>
       <c r="J4" t="str">
-        <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Techcombank</v>
+        <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
+        <v>VIB</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1388,6 +1406,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="1"/>
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1441,10 +1460,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B9" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+      <c r="C9" s="1"/>
       <c r="E9" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1471,10 +1487,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B10" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="E10" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1501,10 +1514,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="E11" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1531,10 +1541,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B12" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+      <c r="C12" s="1"/>
       <c r="E12" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1561,10 +1568,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B13" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+      <c r="C13" s="1"/>
       <c r="E13" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1591,10 +1595,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B14" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+      <c r="C14" s="1"/>
       <c r="E14" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1621,10 +1622,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B15" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+      <c r="C15" s="1"/>
       <c r="E15" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1651,10 +1649,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B16" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+      <c r="C16" s="1"/>
       <c r="E16" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1680,11 +1675,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
       <c r="E17" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1710,11 +1702,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="1"/>
       <c r="E18" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1740,11 +1729,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="1"/>
       <c r="E19" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1770,11 +1756,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="1"/>
       <c r="E20" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1800,11 +1783,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="1"/>
       <c r="E21" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1830,11 +1810,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="1"/>
       <c r="E22" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1860,11 +1837,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="1"/>
       <c r="E23" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1890,11 +1864,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="1"/>
       <c r="E24" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1920,11 +1891,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="1"/>
       <c r="E25" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1950,11 +1918,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="1"/>
       <c r="E26" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1980,11 +1945,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="1"/>
       <c r="E27" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2010,11 +1972,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="1"/>
       <c r="E28" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2040,11 +1999,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="1"/>
       <c r="E29" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2070,11 +2026,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="1"/>
       <c r="E30" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2100,11 +2053,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="1"/>
       <c r="E31" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2130,11 +2080,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B32" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="1"/>
       <c r="E32" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2160,11 +2107,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B33" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C33" s="1"/>
       <c r="E33" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2190,11 +2134,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B34" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C34" s="1"/>
       <c r="E34" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2220,11 +2161,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B35" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C35" s="1"/>
       <c r="E35" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2250,11 +2188,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B36" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C36" s="1"/>
       <c r="E36" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2280,11 +2215,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B37" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C37" s="1"/>
       <c r="E37" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2310,11 +2242,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B38" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C38" s="1"/>
       <c r="E38" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2340,11 +2269,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B39" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C39" s="1"/>
       <c r="E39" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2370,11 +2296,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C40" s="1"/>
       <c r="E40" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2400,11 +2323,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B41" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C41" s="1"/>
       <c r="E41" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2430,11 +2350,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B42" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C42" s="1"/>
       <c r="E42" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2460,11 +2377,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B43" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C43" s="1"/>
       <c r="E43" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2490,11 +2404,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B44" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C44" s="1"/>
       <c r="E44" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2520,11 +2431,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B45" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="45" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C45" s="1"/>
       <c r="E45" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2550,11 +2458,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B46" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C46" s="1"/>
       <c r="E46" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2580,11 +2485,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B47" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C47" s="1"/>
       <c r="E47" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2610,11 +2512,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B48" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C48" s="1"/>
       <c r="E48" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2640,11 +2539,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B49" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C49" s="1"/>
       <c r="E49" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2670,11 +2566,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B50" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C50" s="1"/>
       <c r="E50" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2700,11 +2593,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B51" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C51" s="1"/>
       <c r="E51" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2730,11 +2620,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C52" s="1"/>
       <c r="E52" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2760,11 +2647,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C53" s="1"/>
       <c r="E53" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2790,11 +2674,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B54" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C54" s="1"/>
       <c r="E54" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2820,11 +2701,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B55" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C55" s="1"/>
       <c r="E55" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2850,11 +2728,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B56" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C56" s="1"/>
       <c r="E56" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2880,11 +2755,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B57" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C57" s="1"/>
       <c r="E57" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2910,11 +2782,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B58" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C58" s="1"/>
       <c r="E58" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2940,11 +2809,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B59" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C59" s="1"/>
       <c r="E59" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -2970,11 +2836,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B60" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C60" s="1"/>
       <c r="E60" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3000,11 +2863,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B61" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C61" s="1"/>
       <c r="E61" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3030,11 +2890,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B62" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="62" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C62" s="1"/>
       <c r="E62" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3060,11 +2917,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B63" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C63" s="1"/>
       <c r="E63" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3090,11 +2944,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B64" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C64" s="1"/>
       <c r="E64" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3120,11 +2971,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B65" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="65" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C65" s="1"/>
       <c r="E65" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3150,11 +2998,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B66" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="66" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C66" s="1"/>
       <c r="E66" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3180,11 +3025,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="67" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C67" s="1"/>
       <c r="E67" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3210,11 +3052,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="68" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C68" s="1"/>
       <c r="E68" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3240,11 +3079,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B69" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="69" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C69" s="1"/>
       <c r="E69" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3270,11 +3106,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B70" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="70" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C70" s="1"/>
       <c r="E70" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3300,11 +3133,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B71" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="71" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C71" s="1"/>
       <c r="E71" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3330,11 +3160,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B72" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="72" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C72" s="1"/>
       <c r="E72" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3360,11 +3187,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B73" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="73" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C73" s="1"/>
       <c r="E73" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3390,11 +3214,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B74" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="74" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C74" s="1"/>
       <c r="E74" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3420,11 +3241,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B75" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="75" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C75" s="1"/>
       <c r="E75" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3450,11 +3268,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B76" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C76" s="1"/>
       <c r="E76" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3480,11 +3295,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B77" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="77" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C77" s="1"/>
       <c r="E77" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3510,11 +3322,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B78" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="78" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C78" s="1"/>
       <c r="E78" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3540,11 +3349,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B79" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="79" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C79" s="1"/>
       <c r="E79" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3570,11 +3376,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B80" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="80" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C80" s="1"/>
       <c r="E80" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3600,11 +3403,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B81" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C81" s="1"/>
       <c r="E81" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3630,11 +3430,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B82" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C82" s="1"/>
       <c r="E82" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3660,11 +3457,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B83" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C83" s="1"/>
       <c r="E83" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3690,11 +3484,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B84" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C84" s="1"/>
       <c r="E84" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3720,11 +3511,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B85" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="85" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C85" s="1"/>
       <c r="E85" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3750,11 +3538,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B86" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C86" s="1"/>
       <c r="E86" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3780,11 +3565,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B87" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="87" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C87" s="1"/>
       <c r="E87" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3810,11 +3592,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B88" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C88" s="1"/>
       <c r="E88" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3840,11 +3619,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B89" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="89" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C89" s="1"/>
       <c r="E89" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3870,11 +3646,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B90" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="90" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C90" s="1"/>
       <c r="E90" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3900,11 +3673,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B91" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="91" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C91" s="1"/>
       <c r="E91" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3930,11 +3700,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B92" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="92" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C92" s="1"/>
       <c r="E92" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3960,11 +3727,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B93" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="93" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C93" s="1"/>
       <c r="E93" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -3990,11 +3754,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B94" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="94" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C94" s="1"/>
       <c r="E94" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4020,11 +3781,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B95" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C95" s="1"/>
       <c r="E95" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4050,11 +3808,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B96" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C96" s="1"/>
       <c r="E96" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4080,11 +3835,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B97" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="97" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C97" s="1"/>
       <c r="E97" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4110,11 +3862,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B98" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="98" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C98" s="1"/>
       <c r="E98" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4140,11 +3889,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B99" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="99" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C99" s="1"/>
       <c r="E99" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4170,11 +3916,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B100" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C100" s="1"/>
       <c r="E100" t="str">
         <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4200,142 +3943,111 @@
         <v>-</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E101" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F101" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G101" t="str">
-        <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H101" t="str">
-        <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I101" t="str">
-        <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J101" t="str">
-        <f>IFERROR((VLOOKUP(A101,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="I4" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="I5" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="I6" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="I7" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="I8" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="I9" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="I10" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="I11" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="I12" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="I13" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="I14" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="I15" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="I16" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="I17" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="I18" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="I19" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="I20" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="I21" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="I22" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="I23" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="I24" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="I25" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="I26" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="I27" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="I28" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="I29" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="I30" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="I31" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="I32" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="I33" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="I34" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="I35" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="I36" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="I37" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="I38" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="I39" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="I40" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="I41" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="I42" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="I43" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="I44" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="I45" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="I46" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="I47" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="I48" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="I49" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="I50" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="I51" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="I52" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="I53" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="I54" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="I55" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="I56" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="I57" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="I58" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="I59" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="I60" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="I61" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="I62" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="I63" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="I64" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="I65" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="I66" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="I67" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="I68" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="I69" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="I70" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="I71" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="I72" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="I73" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="I74" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="I75" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="I76" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="I77" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="I78" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="I79" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="I80" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="I81" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="I82" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="I83" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="I84" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="I85" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="I86" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="I87" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="I88" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="I89" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="I90" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="I91" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="I92" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="I93" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="I94" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="I95" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="I96" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="I97" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="I98" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="I99" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="I100" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="I101" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="I2" r:id="rId100" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A736BAC9-60DF-4FD9-8691-3E1611B7D304}"/>
+    <hyperlink ref="I2" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A736BAC9-60DF-4FD9-8691-3E1611B7D304}"/>
+    <hyperlink ref="I5" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FC483C29-EFD7-45F9-8637-43FE725BE5FB}"/>
+    <hyperlink ref="I6" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3037F1B3-7D07-4130-8250-4B15357E5AC9}"/>
+    <hyperlink ref="I7" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{82A650BB-F8E0-42D4-BE36-A7A141C71818}"/>
+    <hyperlink ref="I8" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{473C6134-DE24-4B20-8FD7-D2CD9342D8A3}"/>
+    <hyperlink ref="I9" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{6F2842FB-D25C-4036-8209-B3B4D598B72C}"/>
+    <hyperlink ref="I10" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A007BBFE-18CC-40B3-9DEC-E493FA0DBF3A}"/>
+    <hyperlink ref="I11" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{25BFC2CA-DD97-46D6-86F6-76CAF68C46F9}"/>
+    <hyperlink ref="I12" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{70B6733C-A364-4A17-91CB-820D85700782}"/>
+    <hyperlink ref="I13" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A8DC0463-148F-4F93-B1C6-B3971176DCFA}"/>
+    <hyperlink ref="I14" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3F0F0073-2FE5-471A-A917-6D1793AD8FB3}"/>
+    <hyperlink ref="I15" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E1AAC746-B9BE-41BD-95B7-A8EB5F9D4DDE}"/>
+    <hyperlink ref="I16" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E14DC72C-8DB0-4FDA-B2B9-F066B632879E}"/>
+    <hyperlink ref="I17" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D9D8BD23-88B9-4BE2-857C-69C2D8AFBE05}"/>
+    <hyperlink ref="I18" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EE60F1F9-0484-459E-9289-04E4A100CCB2}"/>
+    <hyperlink ref="I19" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BD0296BD-5656-4DB5-98B1-89D1471BF13D}"/>
+    <hyperlink ref="I20" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0F540F0E-ED4F-417D-A2FA-CCBA807A6C5F}"/>
+    <hyperlink ref="I21" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2194412E-5758-4891-834F-0A5C4493319E}"/>
+    <hyperlink ref="I22" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9A85045B-9E38-4C52-8AFB-96B265B753DB}"/>
+    <hyperlink ref="I23" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B21F88E8-E97E-4D92-9E0E-EB5B47ED56F7}"/>
+    <hyperlink ref="I24" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BAEC9E5E-FD92-452E-B74A-3E89907C4884}"/>
+    <hyperlink ref="I25" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E731EDD3-7E63-4D1B-AACA-34CD3B7D1EBC}"/>
+    <hyperlink ref="I26" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{24A6A49E-B638-4BFF-9619-77527C808407}"/>
+    <hyperlink ref="I27" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BFFE5303-942F-4168-B016-D94F94248193}"/>
+    <hyperlink ref="I28" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D1610055-CCD3-4C6F-98D1-4E3BA1D61304}"/>
+    <hyperlink ref="I29" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{014F45B6-9BA4-4D81-B41B-B67DE7AD2692}"/>
+    <hyperlink ref="I30" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{956FB275-5E8C-43DB-9EBA-D8B0FABFCAB2}"/>
+    <hyperlink ref="I31" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FE043BF2-DC9B-47B5-AC56-B550AD78F46D}"/>
+    <hyperlink ref="I32" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{6FF2AEEF-6CF0-4F90-A457-F5DEF4046869}"/>
+    <hyperlink ref="I33" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5A28C8E1-1765-4A02-9B3E-4E5357E849B6}"/>
+    <hyperlink ref="I34" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{63E35D65-0F53-4F4C-A1A7-A25E54327BE1}"/>
+    <hyperlink ref="I35" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1C706DF8-10DE-4BF3-A537-3BAB0C257450}"/>
+    <hyperlink ref="I36" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BB54CC40-6FFA-4A69-ACA2-D070F9A63B7F}"/>
+    <hyperlink ref="I37" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3F75A53D-2861-415E-AE61-C023BDDAFE4B}"/>
+    <hyperlink ref="I38" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C3C34807-5843-4E80-8D28-FC2EEF289683}"/>
+    <hyperlink ref="I39" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FAA28CCE-68DB-4C7F-B987-25F24B600A37}"/>
+    <hyperlink ref="I40" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A7671E40-1DB7-4B92-B132-A441465E989E}"/>
+    <hyperlink ref="I41" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A57D205B-3FC3-44D6-90F1-32D0A730054F}"/>
+    <hyperlink ref="I42" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{453D2E81-874B-484E-B04A-0B9CB52E2E43}"/>
+    <hyperlink ref="I43" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F31DDFB7-A35D-4BA8-9F7B-719DA05756FF}"/>
+    <hyperlink ref="I44" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{423EAA54-0894-41C8-9F4D-B55F71CF3176}"/>
+    <hyperlink ref="I45" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{658E66EE-12F1-4A96-9907-21BCF8D5FC6A}"/>
+    <hyperlink ref="I46" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{997577D7-D960-47C1-B734-FA5C713397CC}"/>
+    <hyperlink ref="I47" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C82672C3-6DA5-4BD0-9F2A-3840930DE60C}"/>
+    <hyperlink ref="I48" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B8B59294-D3D2-43C7-BFBA-3407D845B282}"/>
+    <hyperlink ref="I49" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EAE81EE4-606B-447C-A35C-17F78EE5F2F0}"/>
+    <hyperlink ref="I50" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1164904F-1564-40AE-948B-BA1F90BB6787}"/>
+    <hyperlink ref="I51" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B3DA6F1B-92A4-46DB-8C08-BEE9C0CA019D}"/>
+    <hyperlink ref="I52" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D5F7063C-6766-408C-8853-312D4E87418C}"/>
+    <hyperlink ref="I53" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D38856C2-08C9-4282-B8F6-A71D5D13951B}"/>
+    <hyperlink ref="I54" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AECDD36D-40F0-4552-BBE6-9A5395741630}"/>
+    <hyperlink ref="I55" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{7FCB4769-67F1-489A-B2F6-37CD06C44D86}"/>
+    <hyperlink ref="I56" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{982279E8-9083-42E0-9B78-773031FF78A1}"/>
+    <hyperlink ref="I57" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{65BD261B-214D-4634-9565-FEBEEEB99DFA}"/>
+    <hyperlink ref="I58" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8B05EB94-46DB-4818-A0D8-2ADFEC0D06BF}"/>
+    <hyperlink ref="I59" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{79C44819-50B8-40C8-9002-0D5D3203261A}"/>
+    <hyperlink ref="I60" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B01FBFDB-5A40-4ADF-8854-632EE3F92DDD}"/>
+    <hyperlink ref="I61" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8F9F88FE-76C1-4B90-959A-755C54CBB455}"/>
+    <hyperlink ref="I62" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E623343A-A2C5-4AE8-A30C-4BD3CBCF4B66}"/>
+    <hyperlink ref="I63" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3AAD2C0D-B15E-48D7-BE58-3748D23BFA49}"/>
+    <hyperlink ref="I64" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DA5A5C4A-28B6-4D7E-A280-4F00B9078FB9}"/>
+    <hyperlink ref="I65" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FBEC57B0-1803-4E5E-BD9B-97DA47D11DE7}"/>
+    <hyperlink ref="I66" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{6FD30569-042B-42F4-BBEB-D8220041AB44}"/>
+    <hyperlink ref="I67" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FF82E129-C47B-4106-B271-57C718F267FF}"/>
+    <hyperlink ref="I68" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DD0FE02F-798E-49DF-B735-1795AA5B78C7}"/>
+    <hyperlink ref="I69" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF31D429-6589-4AD2-8241-39BA86F4311F}"/>
+    <hyperlink ref="I70" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3AD57374-07B1-4F79-9334-DB87D1BEF43B}"/>
+    <hyperlink ref="I71" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C212843-0893-4CD4-8187-6DFB041640E3}"/>
+    <hyperlink ref="I72" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EC3DE583-B57C-4D62-9F61-40249BF3F214}"/>
+    <hyperlink ref="I73" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D98BD694-7641-41EC-8BB5-1E6D4B933DF3}"/>
+    <hyperlink ref="I74" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AB9DDEC2-2042-4684-9D72-65949AACD317}"/>
+    <hyperlink ref="I75" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B625E800-6646-4FA1-AF8F-BC7B7B133578}"/>
+    <hyperlink ref="I76" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C4C681E1-2F29-4327-B31F-E0FF93EDB5AB}"/>
+    <hyperlink ref="I77" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8B6FDDD1-D4D2-4778-91A0-0435A3B46D28}"/>
+    <hyperlink ref="I78" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E1E84E89-A99A-400C-BBFF-9EE006C2A576}"/>
+    <hyperlink ref="I79" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{374FAFC3-06D9-4D6C-9202-8D00A7FEBD94}"/>
+    <hyperlink ref="I80" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AB6BBEF8-B6C6-4EC6-96DE-CBD213EE5A18}"/>
+    <hyperlink ref="I81" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{18EEFAE6-325E-40EF-B532-04315FF21AFC}"/>
+    <hyperlink ref="I82" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{225511B4-5A2B-40AA-A0EF-8DD87232F924}"/>
+    <hyperlink ref="I83" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{7F3870A9-5F8A-485C-A19C-EBC77CBA9336}"/>
+    <hyperlink ref="I84" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E030B1F7-0423-446C-8694-5061CF5648C1}"/>
+    <hyperlink ref="I85" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{374F8266-C0AD-4B1E-80FA-7C8690B02642}"/>
+    <hyperlink ref="I86" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{290209E6-5C08-436D-BD62-1288981DE3B9}"/>
+    <hyperlink ref="I87" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1FCE90BE-F6EE-4130-B795-8F0CE7FFDA76}"/>
+    <hyperlink ref="I88" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{51ECC150-88DD-4E4B-B879-148AB8EDCC62}"/>
+    <hyperlink ref="I89" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AD73EBC7-A3F0-423F-B1DC-C2D0F9C6EF22}"/>
+    <hyperlink ref="I90" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2AB12A22-7F90-4B27-8BBC-A22B74EC5E2B}"/>
+    <hyperlink ref="I91" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E2738125-E834-4A3C-B6E4-013F1B19CC99}"/>
+    <hyperlink ref="I92" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AE1028EE-BFFE-4B5C-BD7F-7FBB339C784D}"/>
+    <hyperlink ref="I93" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4B5FBB30-F002-4263-B10E-C1420F7DEE10}"/>
+    <hyperlink ref="I94" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9852FE45-8185-4641-BE4B-4E107F531FBE}"/>
+    <hyperlink ref="I95" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{87465DF5-4611-4549-A9B9-34D112D52956}"/>
+    <hyperlink ref="I96" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BAEE5106-10E5-4D06-9E1B-B29D578656ED}"/>
+    <hyperlink ref="I97" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E561A5B5-39E6-4E11-AD5F-2E61B6EA89E4}"/>
+    <hyperlink ref="I98" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C3C466A5-6762-4583-8DAC-2CE0EFC7782C}"/>
+    <hyperlink ref="I99" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{23153672-78D8-4D94-AFC9-911081558E45}"/>
+    <hyperlink ref="I100" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{78EBB79B-FA99-4D55-A070-5F7B35EC8C38}"/>
+    <hyperlink ref="I3" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F0530477-D574-4DF7-8D42-DF853CB0590F}"/>
+    <hyperlink ref="I4" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{273F6283-649D-484E-A4C7-29A59CCA0C7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 E7:J7 E4:J4 E5:J5 E6:J6 A3 C3:J3 A10:J101 E8:J8 B9:J9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A3 C3:D3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DA8D9C-05C3-486B-BBF0-219DCAE263B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD85C564-08DB-4393-B5DB-2435AD8EACAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="258">
   <si>
     <t>data__id</t>
   </si>
@@ -808,12 +808,6 @@
   </si>
   <si>
     <t>MS00T09548691713297</t>
-  </si>
-  <si>
-    <t>VIB _ 064</t>
-  </si>
-  <si>
-    <t>064933000</t>
   </si>
 </sst>
 </file>
@@ -1314,51 +1308,40 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="E4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>VIB</v>
+        <v>-</v>
       </c>
       <c r="F4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VIB</v>
-      </c>
-      <c r="G4">
+        <v>-</v>
+      </c>
+      <c r="G4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970441</v>
+        <v>-</v>
       </c>
       <c r="H4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>VIB</v>
+        <v>-</v>
       </c>
       <c r="I4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/VIB.png</v>
+        <v>-</v>
       </c>
       <c r="J4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>VIB</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
       <c r="E5" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F5" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G5" t="str">
@@ -1381,11 +1364,11 @@
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
       <c r="E6" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F6" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G6" t="str">
@@ -1408,11 +1391,11 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="1"/>
       <c r="E7" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F7" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G7" t="str">
@@ -1435,11 +1418,11 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="E8" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" t="str">
@@ -1462,11 +1445,11 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C9" s="1"/>
       <c r="E9" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F9" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G9" t="str">
@@ -1489,11 +1472,11 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="E10" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F10" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G10" t="str">
@@ -1516,11 +1499,11 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="E11" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F11" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G11" t="str">
@@ -1543,11 +1526,11 @@
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="E12" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F12" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A12,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G12" t="str">
@@ -1570,11 +1553,11 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
       <c r="E13" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F13" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A13,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G13" t="str">
@@ -1597,11 +1580,11 @@
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="E14" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F14" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G14" t="str">
@@ -1624,11 +1607,11 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15" s="1"/>
       <c r="E15" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F15" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A15,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G15" t="str">
@@ -1651,11 +1634,11 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C16" s="1"/>
       <c r="E16" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F16" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A16,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G16" t="str">
@@ -1678,11 +1661,11 @@
     <row r="17" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C17" s="1"/>
       <c r="E17" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F17" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G17" t="str">
@@ -1705,11 +1688,11 @@
     <row r="18" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C18" s="1"/>
       <c r="E18" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F18" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G18" t="str">
@@ -1732,11 +1715,11 @@
     <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="1"/>
       <c r="E19" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F19" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G19" t="str">
@@ -1759,11 +1742,11 @@
     <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
       <c r="E20" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F20" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G20" t="str">
@@ -1786,11 +1769,11 @@
     <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
       <c r="E21" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F21" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G21" t="str">
@@ -1813,11 +1796,11 @@
     <row r="22" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C22" s="1"/>
       <c r="E22" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F22" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G22" t="str">
@@ -1840,11 +1823,11 @@
     <row r="23" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C23" s="1"/>
       <c r="E23" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F23" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G23" t="str">
@@ -1867,11 +1850,11 @@
     <row r="24" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C24" s="1"/>
       <c r="E24" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F24" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G24" t="str">
@@ -1894,11 +1877,11 @@
     <row r="25" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C25" s="1"/>
       <c r="E25" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F25" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G25" t="str">
@@ -1921,11 +1904,11 @@
     <row r="26" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C26" s="1"/>
       <c r="E26" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F26" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G26" t="str">
@@ -1948,11 +1931,11 @@
     <row r="27" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C27" s="1"/>
       <c r="E27" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F27" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G27" t="str">
@@ -1975,11 +1958,11 @@
     <row r="28" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C28" s="1"/>
       <c r="E28" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F28" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G28" t="str">
@@ -2002,11 +1985,11 @@
     <row r="29" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C29" s="1"/>
       <c r="E29" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F29" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G29" t="str">
@@ -2029,11 +2012,11 @@
     <row r="30" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C30" s="1"/>
       <c r="E30" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F30" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G30" t="str">
@@ -2056,11 +2039,11 @@
     <row r="31" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="E31" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F31" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G31" t="str">
@@ -2083,11 +2066,11 @@
     <row r="32" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="E32" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F32" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G32" t="str">
@@ -2110,11 +2093,11 @@
     <row r="33" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="E33" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F33" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A33,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G33" t="str">
@@ -2137,11 +2120,11 @@
     <row r="34" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="E34" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F34" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A34,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G34" t="str">
@@ -2164,11 +2147,11 @@
     <row r="35" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="E35" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F35" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A35,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G35" t="str">
@@ -2191,11 +2174,11 @@
     <row r="36" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="E36" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F36" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A36,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G36" t="str">
@@ -2218,11 +2201,11 @@
     <row r="37" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="E37" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F37" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A37,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G37" t="str">
@@ -2245,11 +2228,11 @@
     <row r="38" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="E38" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F38" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A38,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G38" t="str">
@@ -2272,11 +2255,11 @@
     <row r="39" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="E39" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F39" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A39,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G39" t="str">
@@ -2299,11 +2282,11 @@
     <row r="40" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="E40" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F40" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A40,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G40" t="str">
@@ -2326,11 +2309,11 @@
     <row r="41" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="E41" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F41" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A41,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G41" t="str">
@@ -2353,11 +2336,11 @@
     <row r="42" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="E42" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F42" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A42,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G42" t="str">
@@ -2380,11 +2363,11 @@
     <row r="43" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="E43" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F43" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A43,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G43" t="str">
@@ -2407,11 +2390,11 @@
     <row r="44" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="E44" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F44" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A44,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G44" t="str">
@@ -2434,11 +2417,11 @@
     <row r="45" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="E45" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F45" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A45,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G45" t="str">
@@ -2461,11 +2444,11 @@
     <row r="46" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="E46" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F46" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A46,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G46" t="str">
@@ -2488,11 +2471,11 @@
     <row r="47" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="E47" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F47" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A47,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G47" t="str">
@@ -2515,11 +2498,11 @@
     <row r="48" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="E48" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F48" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A48,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G48" t="str">
@@ -2542,11 +2525,11 @@
     <row r="49" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="E49" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F49" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A49,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G49" t="str">
@@ -2569,11 +2552,11 @@
     <row r="50" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="E50" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F50" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A50,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G50" t="str">
@@ -2596,11 +2579,11 @@
     <row r="51" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="E51" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F51" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A51,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G51" t="str">
@@ -2623,11 +2606,11 @@
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="E52" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F52" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A52,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G52" t="str">
@@ -2650,11 +2633,11 @@
     <row r="53" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C53" s="1"/>
       <c r="E53" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F53" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A53,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G53" t="str">
@@ -2677,11 +2660,11 @@
     <row r="54" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C54" s="1"/>
       <c r="E54" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F54" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A54,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G54" t="str">
@@ -2704,11 +2687,11 @@
     <row r="55" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C55" s="1"/>
       <c r="E55" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F55" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A55,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G55" t="str">
@@ -2731,11 +2714,11 @@
     <row r="56" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C56" s="1"/>
       <c r="E56" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F56" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A56,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G56" t="str">
@@ -2758,11 +2741,11 @@
     <row r="57" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C57" s="1"/>
       <c r="E57" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F57" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A57,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G57" t="str">
@@ -2785,11 +2768,11 @@
     <row r="58" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C58" s="1"/>
       <c r="E58" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F58" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A58,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G58" t="str">
@@ -2812,11 +2795,11 @@
     <row r="59" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C59" s="1"/>
       <c r="E59" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F59" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A59,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G59" t="str">
@@ -2839,11 +2822,11 @@
     <row r="60" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C60" s="1"/>
       <c r="E60" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F60" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A60,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G60" t="str">
@@ -2866,11 +2849,11 @@
     <row r="61" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C61" s="1"/>
       <c r="E61" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F61" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A61,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G61" t="str">
@@ -2893,11 +2876,11 @@
     <row r="62" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C62" s="1"/>
       <c r="E62" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F62" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A62,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G62" t="str">
@@ -2920,11 +2903,11 @@
     <row r="63" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C63" s="1"/>
       <c r="E63" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F63" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A63,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G63" t="str">
@@ -2947,11 +2930,11 @@
     <row r="64" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C64" s="1"/>
       <c r="E64" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F64" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A64,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G64" t="str">
@@ -2974,11 +2957,11 @@
     <row r="65" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C65" s="1"/>
       <c r="E65" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F65" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A65,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G65" t="str">
@@ -3001,11 +2984,11 @@
     <row r="66" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C66" s="1"/>
       <c r="E66" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F66" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A66,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G66" t="str">
@@ -3028,11 +3011,11 @@
     <row r="67" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C67" s="1"/>
       <c r="E67" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F67" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A67,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G67" t="str">
@@ -3055,11 +3038,11 @@
     <row r="68" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C68" s="1"/>
       <c r="E68" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F68" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A68,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G68" t="str">
@@ -3082,11 +3065,11 @@
     <row r="69" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C69" s="1"/>
       <c r="E69" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F69" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A69,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G69" t="str">
@@ -3109,11 +3092,11 @@
     <row r="70" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C70" s="1"/>
       <c r="E70" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F70" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A70,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G70" t="str">
@@ -3136,11 +3119,11 @@
     <row r="71" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C71" s="1"/>
       <c r="E71" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F71" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A71,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G71" t="str">
@@ -3163,11 +3146,11 @@
     <row r="72" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C72" s="1"/>
       <c r="E72" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F72" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A72,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G72" t="str">
@@ -3190,11 +3173,11 @@
     <row r="73" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C73" s="1"/>
       <c r="E73" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F73" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A73,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G73" t="str">
@@ -3217,11 +3200,11 @@
     <row r="74" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C74" s="1"/>
       <c r="E74" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F74" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A74,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G74" t="str">
@@ -3244,11 +3227,11 @@
     <row r="75" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C75" s="1"/>
       <c r="E75" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F75" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A75,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G75" t="str">
@@ -3271,11 +3254,11 @@
     <row r="76" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C76" s="1"/>
       <c r="E76" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F76" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A76,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G76" t="str">
@@ -3298,11 +3281,11 @@
     <row r="77" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C77" s="1"/>
       <c r="E77" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F77" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A77,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G77" t="str">
@@ -3325,11 +3308,11 @@
     <row r="78" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C78" s="1"/>
       <c r="E78" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F78" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A78,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G78" t="str">
@@ -3352,11 +3335,11 @@
     <row r="79" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C79" s="1"/>
       <c r="E79" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F79" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A79,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G79" t="str">
@@ -3379,11 +3362,11 @@
     <row r="80" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C80" s="1"/>
       <c r="E80" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F80" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A80,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G80" t="str">
@@ -3406,11 +3389,11 @@
     <row r="81" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C81" s="1"/>
       <c r="E81" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F81" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A81,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G81" t="str">
@@ -3433,11 +3416,11 @@
     <row r="82" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C82" s="1"/>
       <c r="E82" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F82" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A82,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G82" t="str">
@@ -3460,11 +3443,11 @@
     <row r="83" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C83" s="1"/>
       <c r="E83" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F83" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A83,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G83" t="str">
@@ -3487,11 +3470,11 @@
     <row r="84" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C84" s="1"/>
       <c r="E84" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F84" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A84,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G84" t="str">
@@ -3514,11 +3497,11 @@
     <row r="85" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C85" s="1"/>
       <c r="E85" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F85" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A85,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G85" t="str">
@@ -3541,11 +3524,11 @@
     <row r="86" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C86" s="1"/>
       <c r="E86" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F86" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A86,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G86" t="str">
@@ -3568,11 +3551,11 @@
     <row r="87" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C87" s="1"/>
       <c r="E87" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F87" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A87,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G87" t="str">
@@ -3595,11 +3578,11 @@
     <row r="88" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C88" s="1"/>
       <c r="E88" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F88" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A88,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G88" t="str">
@@ -3622,11 +3605,11 @@
     <row r="89" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C89" s="1"/>
       <c r="E89" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F89" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A89,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G89" t="str">
@@ -3649,11 +3632,11 @@
     <row r="90" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C90" s="1"/>
       <c r="E90" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F90" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A90,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G90" t="str">
@@ -3676,11 +3659,11 @@
     <row r="91" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C91" s="1"/>
       <c r="E91" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F91" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A91,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G91" t="str">
@@ -3703,11 +3686,11 @@
     <row r="92" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C92" s="1"/>
       <c r="E92" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F92" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A92,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G92" t="str">
@@ -3730,11 +3713,11 @@
     <row r="93" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C93" s="1"/>
       <c r="E93" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F93" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A93,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G93" t="str">
@@ -3757,11 +3740,11 @@
     <row r="94" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C94" s="1"/>
       <c r="E94" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F94" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A94,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G94" t="str">
@@ -3784,11 +3767,11 @@
     <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="1"/>
       <c r="E95" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F95" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A95,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G95" t="str">
@@ -3811,11 +3794,11 @@
     <row r="96" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C96" s="1"/>
       <c r="E96" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F96" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A96,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G96" t="str">
@@ -3838,11 +3821,11 @@
     <row r="97" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C97" s="1"/>
       <c r="E97" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F97" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A97,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G97" t="str">
@@ -3865,11 +3848,11 @@
     <row r="98" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C98" s="1"/>
       <c r="E98" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F98" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A98,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G98" t="str">
@@ -3892,11 +3875,11 @@
     <row r="99" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C99" s="1"/>
       <c r="E99" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F99" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A99,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G99" t="str">
@@ -3919,11 +3902,11 @@
     <row r="100" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C100" s="1"/>
       <c r="E100" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F100" t="str">
-        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(A100,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G100" t="str">
@@ -3946,104 +3929,104 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A736BAC9-60DF-4FD9-8691-3E1611B7D304}"/>
-    <hyperlink ref="I5" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FC483C29-EFD7-45F9-8637-43FE725BE5FB}"/>
-    <hyperlink ref="I6" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3037F1B3-7D07-4130-8250-4B15357E5AC9}"/>
-    <hyperlink ref="I7" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{82A650BB-F8E0-42D4-BE36-A7A141C71818}"/>
-    <hyperlink ref="I8" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{473C6134-DE24-4B20-8FD7-D2CD9342D8A3}"/>
-    <hyperlink ref="I9" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{6F2842FB-D25C-4036-8209-B3B4D598B72C}"/>
-    <hyperlink ref="I10" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A007BBFE-18CC-40B3-9DEC-E493FA0DBF3A}"/>
-    <hyperlink ref="I11" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{25BFC2CA-DD97-46D6-86F6-76CAF68C46F9}"/>
-    <hyperlink ref="I12" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{70B6733C-A364-4A17-91CB-820D85700782}"/>
-    <hyperlink ref="I13" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A8DC0463-148F-4F93-B1C6-B3971176DCFA}"/>
-    <hyperlink ref="I14" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3F0F0073-2FE5-471A-A917-6D1793AD8FB3}"/>
-    <hyperlink ref="I15" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E1AAC746-B9BE-41BD-95B7-A8EB5F9D4DDE}"/>
-    <hyperlink ref="I16" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E14DC72C-8DB0-4FDA-B2B9-F066B632879E}"/>
-    <hyperlink ref="I17" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D9D8BD23-88B9-4BE2-857C-69C2D8AFBE05}"/>
-    <hyperlink ref="I18" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EE60F1F9-0484-459E-9289-04E4A100CCB2}"/>
-    <hyperlink ref="I19" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BD0296BD-5656-4DB5-98B1-89D1471BF13D}"/>
-    <hyperlink ref="I20" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0F540F0E-ED4F-417D-A2FA-CCBA807A6C5F}"/>
-    <hyperlink ref="I21" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2194412E-5758-4891-834F-0A5C4493319E}"/>
-    <hyperlink ref="I22" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9A85045B-9E38-4C52-8AFB-96B265B753DB}"/>
-    <hyperlink ref="I23" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B21F88E8-E97E-4D92-9E0E-EB5B47ED56F7}"/>
-    <hyperlink ref="I24" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BAEC9E5E-FD92-452E-B74A-3E89907C4884}"/>
-    <hyperlink ref="I25" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E731EDD3-7E63-4D1B-AACA-34CD3B7D1EBC}"/>
-    <hyperlink ref="I26" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{24A6A49E-B638-4BFF-9619-77527C808407}"/>
-    <hyperlink ref="I27" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BFFE5303-942F-4168-B016-D94F94248193}"/>
-    <hyperlink ref="I28" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D1610055-CCD3-4C6F-98D1-4E3BA1D61304}"/>
-    <hyperlink ref="I29" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{014F45B6-9BA4-4D81-B41B-B67DE7AD2692}"/>
-    <hyperlink ref="I30" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{956FB275-5E8C-43DB-9EBA-D8B0FABFCAB2}"/>
-    <hyperlink ref="I31" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FE043BF2-DC9B-47B5-AC56-B550AD78F46D}"/>
-    <hyperlink ref="I32" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{6FF2AEEF-6CF0-4F90-A457-F5DEF4046869}"/>
-    <hyperlink ref="I33" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5A28C8E1-1765-4A02-9B3E-4E5357E849B6}"/>
-    <hyperlink ref="I34" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{63E35D65-0F53-4F4C-A1A7-A25E54327BE1}"/>
-    <hyperlink ref="I35" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1C706DF8-10DE-4BF3-A537-3BAB0C257450}"/>
-    <hyperlink ref="I36" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BB54CC40-6FFA-4A69-ACA2-D070F9A63B7F}"/>
-    <hyperlink ref="I37" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3F75A53D-2861-415E-AE61-C023BDDAFE4B}"/>
-    <hyperlink ref="I38" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C3C34807-5843-4E80-8D28-FC2EEF289683}"/>
-    <hyperlink ref="I39" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FAA28CCE-68DB-4C7F-B987-25F24B600A37}"/>
-    <hyperlink ref="I40" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A7671E40-1DB7-4B92-B132-A441465E989E}"/>
-    <hyperlink ref="I41" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A57D205B-3FC3-44D6-90F1-32D0A730054F}"/>
-    <hyperlink ref="I42" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{453D2E81-874B-484E-B04A-0B9CB52E2E43}"/>
-    <hyperlink ref="I43" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F31DDFB7-A35D-4BA8-9F7B-719DA05756FF}"/>
-    <hyperlink ref="I44" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{423EAA54-0894-41C8-9F4D-B55F71CF3176}"/>
-    <hyperlink ref="I45" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{658E66EE-12F1-4A96-9907-21BCF8D5FC6A}"/>
-    <hyperlink ref="I46" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{997577D7-D960-47C1-B734-FA5C713397CC}"/>
-    <hyperlink ref="I47" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C82672C3-6DA5-4BD0-9F2A-3840930DE60C}"/>
-    <hyperlink ref="I48" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B8B59294-D3D2-43C7-BFBA-3407D845B282}"/>
-    <hyperlink ref="I49" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EAE81EE4-606B-447C-A35C-17F78EE5F2F0}"/>
-    <hyperlink ref="I50" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1164904F-1564-40AE-948B-BA1F90BB6787}"/>
-    <hyperlink ref="I51" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B3DA6F1B-92A4-46DB-8C08-BEE9C0CA019D}"/>
-    <hyperlink ref="I52" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D5F7063C-6766-408C-8853-312D4E87418C}"/>
-    <hyperlink ref="I53" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D38856C2-08C9-4282-B8F6-A71D5D13951B}"/>
-    <hyperlink ref="I54" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AECDD36D-40F0-4552-BBE6-9A5395741630}"/>
-    <hyperlink ref="I55" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{7FCB4769-67F1-489A-B2F6-37CD06C44D86}"/>
-    <hyperlink ref="I56" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{982279E8-9083-42E0-9B78-773031FF78A1}"/>
-    <hyperlink ref="I57" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{65BD261B-214D-4634-9565-FEBEEEB99DFA}"/>
-    <hyperlink ref="I58" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8B05EB94-46DB-4818-A0D8-2ADFEC0D06BF}"/>
-    <hyperlink ref="I59" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{79C44819-50B8-40C8-9002-0D5D3203261A}"/>
-    <hyperlink ref="I60" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B01FBFDB-5A40-4ADF-8854-632EE3F92DDD}"/>
-    <hyperlink ref="I61" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8F9F88FE-76C1-4B90-959A-755C54CBB455}"/>
-    <hyperlink ref="I62" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E623343A-A2C5-4AE8-A30C-4BD3CBCF4B66}"/>
-    <hyperlink ref="I63" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3AAD2C0D-B15E-48D7-BE58-3748D23BFA49}"/>
-    <hyperlink ref="I64" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DA5A5C4A-28B6-4D7E-A280-4F00B9078FB9}"/>
-    <hyperlink ref="I65" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FBEC57B0-1803-4E5E-BD9B-97DA47D11DE7}"/>
-    <hyperlink ref="I66" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{6FD30569-042B-42F4-BBEB-D8220041AB44}"/>
-    <hyperlink ref="I67" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FF82E129-C47B-4106-B271-57C718F267FF}"/>
-    <hyperlink ref="I68" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DD0FE02F-798E-49DF-B735-1795AA5B78C7}"/>
-    <hyperlink ref="I69" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF31D429-6589-4AD2-8241-39BA86F4311F}"/>
-    <hyperlink ref="I70" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3AD57374-07B1-4F79-9334-DB87D1BEF43B}"/>
-    <hyperlink ref="I71" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C212843-0893-4CD4-8187-6DFB041640E3}"/>
-    <hyperlink ref="I72" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EC3DE583-B57C-4D62-9F61-40249BF3F214}"/>
-    <hyperlink ref="I73" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D98BD694-7641-41EC-8BB5-1E6D4B933DF3}"/>
-    <hyperlink ref="I74" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AB9DDEC2-2042-4684-9D72-65949AACD317}"/>
-    <hyperlink ref="I75" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B625E800-6646-4FA1-AF8F-BC7B7B133578}"/>
-    <hyperlink ref="I76" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C4C681E1-2F29-4327-B31F-E0FF93EDB5AB}"/>
-    <hyperlink ref="I77" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8B6FDDD1-D4D2-4778-91A0-0435A3B46D28}"/>
-    <hyperlink ref="I78" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E1E84E89-A99A-400C-BBFF-9EE006C2A576}"/>
-    <hyperlink ref="I79" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{374FAFC3-06D9-4D6C-9202-8D00A7FEBD94}"/>
-    <hyperlink ref="I80" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AB6BBEF8-B6C6-4EC6-96DE-CBD213EE5A18}"/>
-    <hyperlink ref="I81" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{18EEFAE6-325E-40EF-B532-04315FF21AFC}"/>
-    <hyperlink ref="I82" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{225511B4-5A2B-40AA-A0EF-8DD87232F924}"/>
-    <hyperlink ref="I83" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{7F3870A9-5F8A-485C-A19C-EBC77CBA9336}"/>
-    <hyperlink ref="I84" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E030B1F7-0423-446C-8694-5061CF5648C1}"/>
-    <hyperlink ref="I85" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{374F8266-C0AD-4B1E-80FA-7C8690B02642}"/>
-    <hyperlink ref="I86" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{290209E6-5C08-436D-BD62-1288981DE3B9}"/>
-    <hyperlink ref="I87" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1FCE90BE-F6EE-4130-B795-8F0CE7FFDA76}"/>
-    <hyperlink ref="I88" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{51ECC150-88DD-4E4B-B879-148AB8EDCC62}"/>
-    <hyperlink ref="I89" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AD73EBC7-A3F0-423F-B1DC-C2D0F9C6EF22}"/>
-    <hyperlink ref="I90" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2AB12A22-7F90-4B27-8BBC-A22B74EC5E2B}"/>
-    <hyperlink ref="I91" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E2738125-E834-4A3C-B6E4-013F1B19CC99}"/>
-    <hyperlink ref="I92" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AE1028EE-BFFE-4B5C-BD7F-7FBB339C784D}"/>
-    <hyperlink ref="I93" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4B5FBB30-F002-4263-B10E-C1420F7DEE10}"/>
-    <hyperlink ref="I94" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9852FE45-8185-4641-BE4B-4E107F531FBE}"/>
-    <hyperlink ref="I95" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{87465DF5-4611-4549-A9B9-34D112D52956}"/>
-    <hyperlink ref="I96" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BAEE5106-10E5-4D06-9E1B-B29D578656ED}"/>
-    <hyperlink ref="I97" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E561A5B5-39E6-4E11-AD5F-2E61B6EA89E4}"/>
-    <hyperlink ref="I98" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C3C466A5-6762-4583-8DAC-2CE0EFC7782C}"/>
-    <hyperlink ref="I99" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{23153672-78D8-4D94-AFC9-911081558E45}"/>
-    <hyperlink ref="I100" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{78EBB79B-FA99-4D55-A070-5F7B35EC8C38}"/>
-    <hyperlink ref="I3" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F0530477-D574-4DF7-8D42-DF853CB0590F}"/>
-    <hyperlink ref="I4" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{273F6283-649D-484E-A4C7-29A59CCA0C7D}"/>
+    <hyperlink ref="I3" r:id="rId2" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F0530477-D574-4DF7-8D42-DF853CB0590F}"/>
+    <hyperlink ref="I4" r:id="rId3" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{273F6283-649D-484E-A4C7-29A59CCA0C7D}"/>
+    <hyperlink ref="I5" r:id="rId4" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A41E4240-BCEF-479C-BEAB-B8D3AED48653}"/>
+    <hyperlink ref="I6" r:id="rId5" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D8025520-9FF4-42A2-BE55-6D41131FE8DA}"/>
+    <hyperlink ref="I7" r:id="rId6" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{60521FBE-C7B3-453E-BB18-CC04410C8706}"/>
+    <hyperlink ref="I8" r:id="rId7" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B897AB61-5820-4D49-8698-B0785B135C65}"/>
+    <hyperlink ref="I9" r:id="rId8" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C5BEC92-1284-4EF0-9797-DAF2888C3239}"/>
+    <hyperlink ref="I10" r:id="rId9" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{16A340E0-A969-42AC-B426-CD91AA4C6A22}"/>
+    <hyperlink ref="I11" r:id="rId10" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{45D085AB-567B-4467-9F84-02C5A6EF9F64}"/>
+    <hyperlink ref="I12" r:id="rId11" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F68827AF-5262-4CBB-82F5-09D83C30279A}"/>
+    <hyperlink ref="I13" r:id="rId12" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{33ABCA84-678F-4A16-89A7-096BFC44BDB5}"/>
+    <hyperlink ref="I14" r:id="rId13" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CBBB603B-0E17-497D-BC3C-FD2F20D965CF}"/>
+    <hyperlink ref="I15" r:id="rId14" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1F60E6C7-E7AB-473F-92F5-37A065BAA452}"/>
+    <hyperlink ref="I16" r:id="rId15" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8F63AA06-BACF-40F8-9E1F-B60E3DB8C718}"/>
+    <hyperlink ref="I17" r:id="rId16" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{58919ADB-DC6B-4497-A599-63D967BE9450}"/>
+    <hyperlink ref="I18" r:id="rId17" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF25DCC2-60B4-476A-9D89-EE7FEDEEB320}"/>
+    <hyperlink ref="I19" r:id="rId18" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E5492BB1-8B91-4AF1-9FA4-8E3F2EB92B7D}"/>
+    <hyperlink ref="I20" r:id="rId19" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1AD2F0AC-9999-41C7-8CCD-878937BF3BC4}"/>
+    <hyperlink ref="I21" r:id="rId20" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{12DCE658-4B8C-4CDD-B226-6E1EA9FD191B}"/>
+    <hyperlink ref="I22" r:id="rId21" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B8EABC92-D4D3-4189-BC96-CB1A3271860E}"/>
+    <hyperlink ref="I23" r:id="rId22" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{62E7D2AB-E43B-493F-AEDD-B0619ED09DF7}"/>
+    <hyperlink ref="I24" r:id="rId23" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8C06C5D7-E81B-4778-95D4-44C1B58D3A54}"/>
+    <hyperlink ref="I25" r:id="rId24" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1BAA07EF-8CD1-4856-8621-3707FC37DF29}"/>
+    <hyperlink ref="I26" r:id="rId25" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{7F9E10C8-BE5C-4D92-BCDB-FFC1A9DA7C88}"/>
+    <hyperlink ref="I27" r:id="rId26" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D4B631DA-6915-496E-AE37-F8B5BF78DBAF}"/>
+    <hyperlink ref="I28" r:id="rId27" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{129932F5-709C-421C-8E68-2C34AAF2E941}"/>
+    <hyperlink ref="I29" r:id="rId28" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{54EF08EA-9A4A-4FF1-9A1A-22A92B55F4C7}"/>
+    <hyperlink ref="I30" r:id="rId29" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5340CAF9-AE26-4B42-B17B-96BD3640EEC9}"/>
+    <hyperlink ref="I31" r:id="rId30" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0A597762-5C41-491C-BC67-5E7F21FFBB28}"/>
+    <hyperlink ref="I32" r:id="rId31" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9276FF84-EFA3-40FF-8DD5-6700939BCFF9}"/>
+    <hyperlink ref="I33" r:id="rId32" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B5A00277-4BC3-4D1F-977A-B28A51DD1843}"/>
+    <hyperlink ref="I34" r:id="rId33" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{55F7A1C5-B489-4313-B347-7936704F1C98}"/>
+    <hyperlink ref="I35" r:id="rId34" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{846BE347-040D-4761-B5EB-6DD56D05AFF5}"/>
+    <hyperlink ref="I36" r:id="rId35" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DB493597-178F-4719-A52B-158DECC614D1}"/>
+    <hyperlink ref="I37" r:id="rId36" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E109D920-06B3-41ED-A9B5-7AB2D4F1EDFA}"/>
+    <hyperlink ref="I38" r:id="rId37" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8B9A3E9D-8469-4F0E-8CD1-A2F076F36BAF}"/>
+    <hyperlink ref="I39" r:id="rId38" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2D026533-91B8-4C27-BB43-2989C64DDE4D}"/>
+    <hyperlink ref="I40" r:id="rId39" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D160AAB0-9F97-42CE-A5F5-EA2FF9B071A8}"/>
+    <hyperlink ref="I41" r:id="rId40" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A11EE06D-C869-4DD9-8AD8-49DE8AF292E0}"/>
+    <hyperlink ref="I42" r:id="rId41" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{52A932FE-7E33-4945-872C-2E984A660094}"/>
+    <hyperlink ref="I43" r:id="rId42" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5F2F8EAC-3365-4BFA-BA31-674EB781CD47}"/>
+    <hyperlink ref="I44" r:id="rId43" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{68A376B4-3CD7-4D04-8A3F-02823C79ADF0}"/>
+    <hyperlink ref="I45" r:id="rId44" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{AF305C97-1FEC-4319-B5CD-C3B3B0B5A5BC}"/>
+    <hyperlink ref="I46" r:id="rId45" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{D676EC3C-0882-4DE5-81EF-ED95D470665A}"/>
+    <hyperlink ref="I47" r:id="rId46" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{970B51C9-9A74-4402-A5F6-3E224A4EFAE9}"/>
+    <hyperlink ref="I48" r:id="rId47" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{383E60FE-66F0-4BDC-A784-C4BD6EF8D3E5}"/>
+    <hyperlink ref="I49" r:id="rId48" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{71EB0BD5-B7BE-4788-A01D-B1710A1458D0}"/>
+    <hyperlink ref="I50" r:id="rId49" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{74832FDC-DACB-49B6-B84D-364FA34BEE63}"/>
+    <hyperlink ref="I51" r:id="rId50" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C73BC4E-0A2B-4BE8-A6EC-DF192CB19750}"/>
+    <hyperlink ref="I52" r:id="rId51" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{0008829D-9F50-4B6D-911B-86BA2D5122B6}"/>
+    <hyperlink ref="I53" r:id="rId52" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FEEF9362-8118-4B81-B2CD-FA6B59DC4FF1}"/>
+    <hyperlink ref="I54" r:id="rId53" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1CF3322E-D920-4713-8774-19AEEA2DF2E6}"/>
+    <hyperlink ref="I55" r:id="rId54" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B9F995AA-DF18-4DD3-997F-FF7D2C7B09E8}"/>
+    <hyperlink ref="I56" r:id="rId55" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{39F9FE12-59A1-48E0-9AE4-E86F7BCD238E}"/>
+    <hyperlink ref="I57" r:id="rId56" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C8771D77-1163-4E0B-9462-FE2EC847AF5D}"/>
+    <hyperlink ref="I58" r:id="rId57" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4CF04455-D9C4-4F57-9948-EF6F30D3F377}"/>
+    <hyperlink ref="I59" r:id="rId58" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E0CDDD97-9444-43EA-8976-D421658673D5}"/>
+    <hyperlink ref="I60" r:id="rId59" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{2AC7A3C2-700B-41FC-BBA0-D7B340615512}"/>
+    <hyperlink ref="I61" r:id="rId60" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{6E1413C3-0255-4BAE-9837-6902F7AD3E24}"/>
+    <hyperlink ref="I62" r:id="rId61" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{75F33EB7-D174-4156-B390-443936E23B8B}"/>
+    <hyperlink ref="I63" r:id="rId62" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1607A2DA-E241-46CF-9D05-EBC67F0F8B78}"/>
+    <hyperlink ref="I64" r:id="rId63" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{ECA34B61-3DFE-4A70-A642-E76DB3F3B430}"/>
+    <hyperlink ref="I65" r:id="rId64" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5BF84784-BC3C-4CBD-A840-E727B41C14CA}"/>
+    <hyperlink ref="I66" r:id="rId65" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{EE79F3D1-6128-4208-8438-89D13AA68300}"/>
+    <hyperlink ref="I67" r:id="rId66" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CBE9A6B6-82D3-4619-976E-73C8F61F6DCD}"/>
+    <hyperlink ref="I68" r:id="rId67" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3256AF57-41BF-418F-BF53-6BBC7E8F26F5}"/>
+    <hyperlink ref="I69" r:id="rId68" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{CD19C544-D89A-4980-BA54-7E90B0624979}"/>
+    <hyperlink ref="I70" r:id="rId69" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{945249F1-DF87-4B12-89DD-9796C6EF59C8}"/>
+    <hyperlink ref="I71" r:id="rId70" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8C83FDBB-D4AC-4DD3-B697-332288E2149D}"/>
+    <hyperlink ref="I72" r:id="rId71" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{5E9D8A9D-A297-45D3-B607-8134C069A4C5}"/>
+    <hyperlink ref="I73" r:id="rId72" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A3CA3A50-8178-4165-A0F0-2A1D178DBC15}"/>
+    <hyperlink ref="I74" r:id="rId73" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{3D31A66C-8427-49D8-923C-74658B721596}"/>
+    <hyperlink ref="I75" r:id="rId74" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{18F662CF-ADB0-47E4-82F8-C5AD9268DEA7}"/>
+    <hyperlink ref="I76" r:id="rId75" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C9729947-6525-4281-87D8-F1FD561F4BFE}"/>
+    <hyperlink ref="I77" r:id="rId76" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BDDC023D-8F3A-4790-BCEE-BD63CE15DCD7}"/>
+    <hyperlink ref="I78" r:id="rId77" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{7F62AEA8-2661-4F33-8597-2A2BFFCFE663}"/>
+    <hyperlink ref="I79" r:id="rId78" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{30E834EF-2990-420E-8953-DB2A3372A3EB}"/>
+    <hyperlink ref="I80" r:id="rId79" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FBB3E5DD-8C8D-40B9-AA8F-FC8E527E3632}"/>
+    <hyperlink ref="I81" r:id="rId80" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{F9459E45-8723-400B-976E-F20A693728C2}"/>
+    <hyperlink ref="I82" r:id="rId81" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{BE770DF8-22E8-4821-ADE9-7385206470B5}"/>
+    <hyperlink ref="I83" r:id="rId82" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{DD07E92A-0F0F-41FF-868A-B1781B195E67}"/>
+    <hyperlink ref="I84" r:id="rId83" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{55B11F17-A4F5-43AC-8309-FBD9C7A22A84}"/>
+    <hyperlink ref="I85" r:id="rId84" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{C821DE14-8627-43FC-AB05-B7D0F6C12E6A}"/>
+    <hyperlink ref="I86" r:id="rId85" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{850B0BE6-93FD-49C8-A9A3-D3F251CAC794}"/>
+    <hyperlink ref="I87" r:id="rId86" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{6F37F144-320C-4A37-A342-381C64BDB7A3}"/>
+    <hyperlink ref="I88" r:id="rId87" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{4C25CDF5-9BA1-4D29-B574-7ECFD10E1F7E}"/>
+    <hyperlink ref="I89" r:id="rId88" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{B8316516-7366-49A6-BAF4-D00469C26FE3}"/>
+    <hyperlink ref="I90" r:id="rId89" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{9912C1D8-BE91-48DE-84DC-1EBE1F5930B8}"/>
+    <hyperlink ref="I91" r:id="rId90" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{8A6EE7E2-0E14-43F5-9FD7-07EB06ED1AB1}"/>
+    <hyperlink ref="I92" r:id="rId91" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{1360511B-DB14-4D94-B2FB-30EC5250FE06}"/>
+    <hyperlink ref="I93" r:id="rId92" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{483B41F2-F38E-48D7-A5DF-EC852D2CDB30}"/>
+    <hyperlink ref="I94" r:id="rId93" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{A6D28E6A-33A4-4CB2-BC40-A482115A4D3E}"/>
+    <hyperlink ref="I95" r:id="rId94" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{45E15F1C-773C-46F4-A0F4-CAFA665DB9D4}"/>
+    <hyperlink ref="I96" r:id="rId95" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{111F1A8F-B1BB-4DCD-9364-A170B2E27D63}"/>
+    <hyperlink ref="I97" r:id="rId96" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{FFED413A-2AB9-49AC-8D6B-9A48EF7B9328}"/>
+    <hyperlink ref="I98" r:id="rId97" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{13D9C0FA-6DC3-4A53-8FFB-39A05D5DCC34}"/>
+    <hyperlink ref="I99" r:id="rId98" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{550CBE30-E716-482C-8E3B-B90B0E17CBBA}"/>
+    <hyperlink ref="I100" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E5F2760B-3918-4B77-B8F8-66F3A483A2D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD85C564-08DB-4393-B5DB-2435AD8EACAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957B9A24-4492-4198-A7DD-DE30C0004429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -5656,7 +5656,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H66" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H45 A47:H66 B46:H46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957B9A24-4492-4198-A7DD-DE30C0004429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF408A0D-FDBD-4D5E-8D71-41F2577C304E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="262">
   <si>
     <t>data__id</t>
   </si>
@@ -808,6 +808,18 @@
   </si>
   <si>
     <t>MS00T09548691713297</t>
+  </si>
+  <si>
+    <t>VIB_064</t>
+  </si>
+  <si>
+    <t>064933000</t>
+  </si>
+  <si>
+    <t>VIB_052</t>
+  </si>
+  <si>
+    <t>052004</t>
   </si>
 </sst>
 </file>
@@ -1308,57 +1320,79 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="1"/>
+      <c r="A4">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
       <c r="E4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>VIB</v>
       </c>
       <c r="F4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G4" t="str">
+        <v>VIB</v>
+      </c>
+      <c r="G4">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970441</v>
       </c>
       <c r="H4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>VIB</v>
       </c>
       <c r="I4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/VIB.png</v>
       </c>
       <c r="J4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>VIB</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="1"/>
+      <c r="A5">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>VIB</v>
       </c>
       <c r="F5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G5" t="str">
+        <v>VIB</v>
+      </c>
+      <c r="G5">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970441</v>
       </c>
       <c r="H5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>VIB</v>
       </c>
       <c r="I5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/VIB.png</v>
       </c>
       <c r="J5" t="str">
         <f>IFERROR((VLOOKUP(A5,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>VIB</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF408A0D-FDBD-4D5E-8D71-41F2577C304E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D935621E-98C6-4BF7-A249-25B26C4543F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -69,9 +69,6 @@
     <t>Huynh Tran Tuan Kiet</t>
   </si>
   <si>
-    <t>Templa</t>
-  </si>
-  <si>
     <t>Ngân hàng TMCP An Bình</t>
   </si>
   <si>
@@ -820,6 +817,9 @@
   </si>
   <si>
     <t>052004</t>
+  </si>
+  <si>
+    <t>Template</t>
   </si>
 </sst>
 </file>
@@ -1248,10 +1248,10 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1286,7 +1286,7 @@
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C3">
         <v>44699999999</v>
@@ -1324,10 +1324,10 @@
         <v>45</v>
       </c>
       <c r="B4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1362,10 +1362,10 @@
         <v>45</v>
       </c>
       <c r="B5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -4107,7 +4107,7 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -4115,25 +4115,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
       </c>
       <c r="D2">
         <v>970425</v>
       </c>
       <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4141,25 +4141,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
       </c>
       <c r="D3">
         <v>970416</v>
       </c>
       <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -4167,25 +4167,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
       </c>
       <c r="D4">
         <v>970409</v>
       </c>
       <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -4193,25 +4193,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
       </c>
       <c r="D5">
         <v>970418</v>
       </c>
       <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -4219,25 +4219,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
       </c>
       <c r="D6">
         <v>970438</v>
       </c>
       <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -4245,22 +4245,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
         <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
       </c>
       <c r="D7">
         <v>970444</v>
       </c>
       <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -4268,22 +4268,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
         <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
       </c>
       <c r="D8">
         <v>422589</v>
       </c>
       <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -4291,22 +4291,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
       </c>
       <c r="D9">
         <v>796500</v>
       </c>
       <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
         <v>44</v>
       </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -4314,22 +4314,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
         <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
       </c>
       <c r="D10">
         <v>970406</v>
       </c>
       <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
         <v>47</v>
       </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -4337,22 +4337,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
         <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
       </c>
       <c r="D11">
         <v>970431</v>
       </c>
       <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
         <v>51</v>
       </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -4360,22 +4360,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
         <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
       </c>
       <c r="D12">
         <v>970408</v>
       </c>
       <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
         <v>55</v>
       </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -4383,22 +4383,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
         <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
       </c>
       <c r="D13">
         <v>970437</v>
       </c>
       <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
         <v>59</v>
       </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -4406,22 +4406,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
         <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
       </c>
       <c r="D14">
         <v>970442</v>
       </c>
       <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
         <v>63</v>
       </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -4429,22 +4429,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
         <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
       </c>
       <c r="D15">
         <v>458761</v>
       </c>
       <c r="E15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s">
         <v>66</v>
       </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -4452,22 +4452,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
         <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
       </c>
       <c r="D16">
         <v>970455</v>
       </c>
       <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
         <v>70</v>
       </c>
-      <c r="F16" t="s">
-        <v>71</v>
-      </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -4475,22 +4475,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
         <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
       </c>
       <c r="D17">
         <v>970456</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -4498,22 +4498,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" t="s">
         <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
       </c>
       <c r="D18">
         <v>970415</v>
       </c>
       <c r="E18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" t="s">
         <v>77</v>
       </c>
-      <c r="F18" t="s">
-        <v>78</v>
-      </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -4521,22 +4521,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
         <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
       </c>
       <c r="D19">
         <v>970434</v>
       </c>
       <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
         <v>81</v>
       </c>
-      <c r="F19" t="s">
-        <v>82</v>
-      </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -4544,22 +4544,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
         <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
       </c>
       <c r="D20">
         <v>970452</v>
       </c>
       <c r="E20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" t="s">
         <v>85</v>
       </c>
-      <c r="F20" t="s">
-        <v>86</v>
-      </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -4567,22 +4567,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
         <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>88</v>
       </c>
       <c r="D21">
         <v>970449</v>
       </c>
       <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" t="s">
         <v>89</v>
       </c>
-      <c r="F21" t="s">
-        <v>90</v>
-      </c>
       <c r="G21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -4590,22 +4590,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
         <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>92</v>
       </c>
       <c r="D22">
         <v>970422</v>
       </c>
       <c r="E22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" t="s">
         <v>93</v>
       </c>
-      <c r="F22" t="s">
-        <v>94</v>
-      </c>
       <c r="G22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -4613,22 +4613,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
         <v>95</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
       </c>
       <c r="D23">
         <v>970426</v>
       </c>
       <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" t="s">
         <v>96</v>
       </c>
-      <c r="F23" t="s">
-        <v>97</v>
-      </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -4636,22 +4636,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="s">
         <v>98</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
       </c>
       <c r="D24">
         <v>970428</v>
       </c>
       <c r="E24" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" t="s">
         <v>100</v>
       </c>
-      <c r="F24" t="s">
-        <v>101</v>
-      </c>
       <c r="G24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -4659,22 +4659,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" t="s">
         <v>102</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
       </c>
       <c r="D25">
         <v>970419</v>
       </c>
       <c r="E25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" t="s">
         <v>103</v>
       </c>
-      <c r="F25" t="s">
-        <v>104</v>
-      </c>
       <c r="G25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -4682,22 +4682,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" t="s">
         <v>105</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
       </c>
       <c r="D26">
         <v>801011</v>
       </c>
       <c r="E26" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" t="s">
         <v>107</v>
       </c>
-      <c r="F26" t="s">
-        <v>108</v>
-      </c>
       <c r="G26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -4705,22 +4705,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s">
         <v>109</v>
-      </c>
-      <c r="C27" t="s">
-        <v>110</v>
       </c>
       <c r="D27">
         <v>970448</v>
       </c>
       <c r="E27" t="s">
+        <v>109</v>
+      </c>
+      <c r="F27" t="s">
         <v>110</v>
       </c>
-      <c r="F27" t="s">
-        <v>111</v>
-      </c>
       <c r="G27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -4728,22 +4728,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" t="s">
         <v>112</v>
-      </c>
-      <c r="C28" t="s">
-        <v>113</v>
       </c>
       <c r="D28">
         <v>970414</v>
       </c>
       <c r="E28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" t="s">
         <v>113</v>
       </c>
-      <c r="F28" t="s">
-        <v>114</v>
-      </c>
       <c r="G28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -4751,22 +4751,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
         <v>115</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
       </c>
       <c r="D29">
         <v>970439</v>
       </c>
       <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" t="s">
         <v>117</v>
       </c>
-      <c r="F29" t="s">
-        <v>118</v>
-      </c>
       <c r="G29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -4774,22 +4774,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" t="s">
         <v>119</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
       </c>
       <c r="D30">
         <v>970430</v>
       </c>
       <c r="E30" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" t="s">
         <v>121</v>
       </c>
-      <c r="F30" t="s">
-        <v>122</v>
-      </c>
       <c r="G30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -4797,22 +4797,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" t="s">
         <v>123</v>
-      </c>
-      <c r="C31" t="s">
-        <v>124</v>
       </c>
       <c r="D31">
         <v>970412</v>
       </c>
       <c r="E31" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" t="s">
         <v>125</v>
       </c>
-      <c r="F31" t="s">
-        <v>126</v>
-      </c>
       <c r="G31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -4820,22 +4820,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" t="s">
         <v>127</v>
-      </c>
-      <c r="C32" t="s">
-        <v>128</v>
       </c>
       <c r="D32">
         <v>970429</v>
       </c>
       <c r="E32" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" t="s">
         <v>128</v>
       </c>
-      <c r="F32" t="s">
-        <v>129</v>
-      </c>
       <c r="G32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -4843,22 +4843,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" t="s">
         <v>130</v>
-      </c>
-      <c r="C33" t="s">
-        <v>131</v>
       </c>
       <c r="D33">
         <v>970410</v>
       </c>
       <c r="E33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F33" t="s">
         <v>132</v>
       </c>
-      <c r="F33" t="s">
-        <v>133</v>
-      </c>
       <c r="G33" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -4866,22 +4866,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
         <v>134</v>
-      </c>
-      <c r="C34" t="s">
-        <v>135</v>
       </c>
       <c r="D34">
         <v>970440</v>
       </c>
       <c r="E34" t="s">
+        <v>135</v>
+      </c>
+      <c r="F34" t="s">
         <v>136</v>
       </c>
-      <c r="F34" t="s">
-        <v>137</v>
-      </c>
       <c r="G34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -4889,22 +4889,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" t="s">
         <v>138</v>
-      </c>
-      <c r="C35" t="s">
-        <v>139</v>
       </c>
       <c r="D35">
         <v>970400</v>
       </c>
       <c r="E35" t="s">
+        <v>139</v>
+      </c>
+      <c r="F35" t="s">
         <v>140</v>
       </c>
-      <c r="F35" t="s">
-        <v>141</v>
-      </c>
       <c r="G35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -4912,22 +4912,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" t="s">
         <v>142</v>
-      </c>
-      <c r="C36" t="s">
-        <v>143</v>
       </c>
       <c r="D36">
         <v>970443</v>
       </c>
       <c r="E36" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36" t="s">
         <v>143</v>
       </c>
-      <c r="F36" t="s">
-        <v>144</v>
-      </c>
       <c r="G36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -4935,22 +4935,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" t="s">
         <v>145</v>
-      </c>
-      <c r="C37" t="s">
-        <v>146</v>
       </c>
       <c r="D37">
         <v>970403</v>
       </c>
       <c r="E37" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" t="s">
         <v>147</v>
       </c>
-      <c r="F37" t="s">
-        <v>148</v>
-      </c>
       <c r="G37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -4958,22 +4958,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" t="s">
         <v>149</v>
-      </c>
-      <c r="C38" t="s">
-        <v>150</v>
       </c>
       <c r="D38">
         <v>970424</v>
       </c>
       <c r="E38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" t="s">
         <v>151</v>
       </c>
-      <c r="F38" t="s">
-        <v>152</v>
-      </c>
       <c r="G38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -4981,22 +4981,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" t="s">
         <v>153</v>
-      </c>
-      <c r="C39" t="s">
-        <v>154</v>
       </c>
       <c r="D39">
         <v>970407</v>
       </c>
       <c r="E39" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" t="s">
         <v>155</v>
       </c>
-      <c r="F39" t="s">
-        <v>156</v>
-      </c>
       <c r="G39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -5004,22 +5004,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" t="s">
         <v>157</v>
-      </c>
-      <c r="C40" t="s">
-        <v>158</v>
       </c>
       <c r="D40">
         <v>970423</v>
       </c>
       <c r="E40" t="s">
+        <v>158</v>
+      </c>
+      <c r="F40" t="s">
         <v>159</v>
       </c>
-      <c r="F40" t="s">
-        <v>160</v>
-      </c>
       <c r="G40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -5027,22 +5027,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" t="s">
         <v>161</v>
-      </c>
-      <c r="C41" t="s">
-        <v>162</v>
       </c>
       <c r="D41">
         <v>970458</v>
       </c>
       <c r="E41" t="s">
+        <v>162</v>
+      </c>
+      <c r="F41" t="s">
         <v>163</v>
       </c>
-      <c r="F41" t="s">
-        <v>164</v>
-      </c>
       <c r="G41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -5050,22 +5050,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" t="s">
         <v>165</v>
-      </c>
-      <c r="C42" t="s">
-        <v>166</v>
       </c>
       <c r="D42">
         <v>970427</v>
       </c>
       <c r="E42" t="s">
+        <v>166</v>
+      </c>
+      <c r="F42" t="s">
         <v>167</v>
       </c>
-      <c r="F42" t="s">
-        <v>168</v>
-      </c>
       <c r="G42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -5073,22 +5073,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" t="s">
         <v>169</v>
-      </c>
-      <c r="C43" t="s">
-        <v>170</v>
       </c>
       <c r="D43">
         <v>970405</v>
       </c>
       <c r="E43" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" t="s">
         <v>171</v>
       </c>
-      <c r="F43" t="s">
-        <v>172</v>
-      </c>
       <c r="G43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -5096,22 +5096,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" t="s">
         <v>173</v>
-      </c>
-      <c r="C44" t="s">
-        <v>174</v>
       </c>
       <c r="D44">
         <v>970436</v>
       </c>
       <c r="E44" t="s">
+        <v>174</v>
+      </c>
+      <c r="F44" t="s">
         <v>175</v>
       </c>
-      <c r="F44" t="s">
-        <v>176</v>
-      </c>
       <c r="G44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -5119,22 +5119,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>176</v>
+      </c>
+      <c r="C45" t="s">
         <v>177</v>
-      </c>
-      <c r="C45" t="s">
-        <v>178</v>
       </c>
       <c r="D45">
         <v>970454</v>
       </c>
       <c r="E45" t="s">
+        <v>178</v>
+      </c>
+      <c r="F45" t="s">
         <v>179</v>
       </c>
-      <c r="F45" t="s">
-        <v>180</v>
-      </c>
       <c r="G45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -5142,22 +5142,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" t="s">
         <v>181</v>
-      </c>
-      <c r="C46" t="s">
-        <v>182</v>
       </c>
       <c r="D46">
         <v>970441</v>
       </c>
       <c r="E46" t="s">
+        <v>181</v>
+      </c>
+      <c r="F46" t="s">
         <v>182</v>
       </c>
-      <c r="F46" t="s">
-        <v>183</v>
-      </c>
       <c r="G46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -5165,22 +5165,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" t="s">
         <v>184</v>
-      </c>
-      <c r="C47" t="s">
-        <v>185</v>
       </c>
       <c r="D47">
         <v>970433</v>
       </c>
       <c r="E47" t="s">
+        <v>185</v>
+      </c>
+      <c r="F47" t="s">
         <v>186</v>
       </c>
-      <c r="F47" t="s">
-        <v>187</v>
-      </c>
       <c r="G47" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -5188,22 +5188,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" t="s">
         <v>188</v>
-      </c>
-      <c r="C48" t="s">
-        <v>189</v>
       </c>
       <c r="D48">
         <v>970432</v>
       </c>
       <c r="E48" t="s">
+        <v>189</v>
+      </c>
+      <c r="F48" t="s">
         <v>190</v>
       </c>
-      <c r="F48" t="s">
-        <v>191</v>
-      </c>
       <c r="G48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -5211,22 +5211,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C49" t="s">
         <v>192</v>
-      </c>
-      <c r="C49" t="s">
-        <v>193</v>
       </c>
       <c r="D49">
         <v>970421</v>
       </c>
       <c r="E49" t="s">
+        <v>192</v>
+      </c>
+      <c r="F49" t="s">
         <v>193</v>
       </c>
-      <c r="F49" t="s">
-        <v>194</v>
-      </c>
       <c r="G49" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -5234,22 +5234,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>194</v>
+      </c>
+      <c r="C50" t="s">
         <v>195</v>
-      </c>
-      <c r="C50" t="s">
-        <v>196</v>
       </c>
       <c r="D50">
         <v>970457</v>
       </c>
       <c r="E50" t="s">
+        <v>196</v>
+      </c>
+      <c r="F50" t="s">
         <v>197</v>
       </c>
-      <c r="F50" t="s">
-        <v>198</v>
-      </c>
       <c r="G50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -5257,22 +5257,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>198</v>
+      </c>
+      <c r="C51" t="s">
         <v>199</v>
-      </c>
-      <c r="C51" t="s">
-        <v>200</v>
       </c>
       <c r="D51">
         <v>970462</v>
       </c>
       <c r="E51" t="s">
+        <v>200</v>
+      </c>
+      <c r="F51" t="s">
         <v>201</v>
       </c>
-      <c r="F51" t="s">
-        <v>202</v>
-      </c>
       <c r="G51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -5280,22 +5280,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>202</v>
+      </c>
+      <c r="C52" t="s">
         <v>203</v>
-      </c>
-      <c r="C52" t="s">
-        <v>204</v>
       </c>
       <c r="D52">
         <v>970463</v>
       </c>
       <c r="E52" t="s">
+        <v>204</v>
+      </c>
+      <c r="F52" t="s">
         <v>205</v>
       </c>
-      <c r="F52" t="s">
-        <v>206</v>
-      </c>
       <c r="G52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -5303,22 +5303,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>206</v>
+      </c>
+      <c r="C53" t="s">
         <v>207</v>
-      </c>
-      <c r="C53" t="s">
-        <v>208</v>
       </c>
       <c r="D53">
         <v>970446</v>
       </c>
       <c r="E53" t="s">
+        <v>207</v>
+      </c>
+      <c r="F53" t="s">
         <v>208</v>
       </c>
-      <c r="F53" t="s">
-        <v>209</v>
-      </c>
       <c r="G53" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -5326,22 +5326,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54" t="s">
         <v>210</v>
-      </c>
-      <c r="C54" t="s">
-        <v>211</v>
       </c>
       <c r="D54">
         <v>546034</v>
       </c>
       <c r="E54" t="s">
+        <v>210</v>
+      </c>
+      <c r="F54" t="s">
         <v>211</v>
       </c>
-      <c r="F54" t="s">
-        <v>212</v>
-      </c>
       <c r="G54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -5349,22 +5349,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" t="s">
         <v>213</v>
-      </c>
-      <c r="C55" t="s">
-        <v>214</v>
       </c>
       <c r="D55">
         <v>546035</v>
       </c>
       <c r="E55" t="s">
+        <v>213</v>
+      </c>
+      <c r="F55" t="s">
         <v>214</v>
       </c>
-      <c r="F55" t="s">
-        <v>215</v>
-      </c>
       <c r="G55" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -5372,22 +5372,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>215</v>
+      </c>
+      <c r="C56" t="s">
         <v>216</v>
-      </c>
-      <c r="C56" t="s">
-        <v>217</v>
       </c>
       <c r="D56">
         <v>668888</v>
       </c>
       <c r="E56" t="s">
+        <v>216</v>
+      </c>
+      <c r="F56" t="s">
         <v>217</v>
       </c>
-      <c r="F56" t="s">
-        <v>218</v>
-      </c>
       <c r="G56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -5395,22 +5395,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>218</v>
+      </c>
+      <c r="C57" t="s">
         <v>219</v>
-      </c>
-      <c r="C57" t="s">
-        <v>220</v>
       </c>
       <c r="D57">
         <v>971011</v>
       </c>
       <c r="E57" t="s">
+        <v>220</v>
+      </c>
+      <c r="F57" t="s">
         <v>221</v>
       </c>
-      <c r="F57" t="s">
-        <v>222</v>
-      </c>
       <c r="G57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -5418,22 +5418,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>222</v>
+      </c>
+      <c r="C58" t="s">
         <v>223</v>
-      </c>
-      <c r="C58" t="s">
-        <v>224</v>
       </c>
       <c r="D58">
         <v>971005</v>
       </c>
       <c r="E58" t="s">
+        <v>224</v>
+      </c>
+      <c r="F58" t="s">
         <v>225</v>
       </c>
-      <c r="F58" t="s">
-        <v>226</v>
-      </c>
       <c r="G58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -5441,22 +5441,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>226</v>
+      </c>
+      <c r="C59" t="s">
         <v>227</v>
-      </c>
-      <c r="C59" t="s">
-        <v>228</v>
       </c>
       <c r="D59">
         <v>963388</v>
       </c>
       <c r="E59" t="s">
+        <v>228</v>
+      </c>
+      <c r="F59" t="s">
         <v>229</v>
       </c>
-      <c r="F59" t="s">
-        <v>230</v>
-      </c>
       <c r="G59" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -5464,22 +5464,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>230</v>
+      </c>
+      <c r="C60" t="s">
         <v>231</v>
-      </c>
-      <c r="C60" t="s">
-        <v>232</v>
       </c>
       <c r="D60">
         <v>533948</v>
       </c>
       <c r="E60" t="s">
+        <v>232</v>
+      </c>
+      <c r="F60" t="s">
         <v>233</v>
       </c>
-      <c r="F60" t="s">
-        <v>234</v>
-      </c>
       <c r="G60" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -5487,22 +5487,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" t="s">
         <v>235</v>
-      </c>
-      <c r="C61" t="s">
-        <v>236</v>
       </c>
       <c r="D61">
         <v>970466</v>
       </c>
       <c r="E61" t="s">
+        <v>236</v>
+      </c>
+      <c r="F61" t="s">
         <v>237</v>
       </c>
-      <c r="F61" t="s">
-        <v>238</v>
-      </c>
       <c r="G61" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -5510,22 +5510,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" t="s">
         <v>239</v>
-      </c>
-      <c r="C62" t="s">
-        <v>240</v>
       </c>
       <c r="D62">
         <v>970467</v>
       </c>
       <c r="E62" t="s">
+        <v>239</v>
+      </c>
+      <c r="F62" t="s">
         <v>240</v>
       </c>
-      <c r="F62" t="s">
-        <v>241</v>
-      </c>
       <c r="G62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -5533,22 +5533,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>241</v>
+      </c>
+      <c r="C63" t="s">
         <v>242</v>
-      </c>
-      <c r="C63" t="s">
-        <v>243</v>
       </c>
       <c r="D63">
         <v>977777</v>
       </c>
       <c r="E63" t="s">
+        <v>242</v>
+      </c>
+      <c r="F63" t="s">
         <v>243</v>
       </c>
-      <c r="F63" t="s">
-        <v>244</v>
-      </c>
       <c r="G63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -5556,22 +5556,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>244</v>
+      </c>
+      <c r="C64" t="s">
         <v>245</v>
-      </c>
-      <c r="C64" t="s">
-        <v>246</v>
       </c>
       <c r="D64">
         <v>999888</v>
       </c>
       <c r="E64" t="s">
+        <v>245</v>
+      </c>
+      <c r="F64" t="s">
         <v>246</v>
       </c>
-      <c r="F64" t="s">
-        <v>247</v>
-      </c>
       <c r="G64" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -5579,22 +5579,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>247</v>
+      </c>
+      <c r="C65" t="s">
         <v>248</v>
-      </c>
-      <c r="C65" t="s">
-        <v>249</v>
       </c>
       <c r="D65">
         <v>971133</v>
       </c>
       <c r="E65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -5602,22 +5602,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>250</v>
+      </c>
+      <c r="C66" t="s">
         <v>251</v>
-      </c>
-      <c r="C66" t="s">
-        <v>252</v>
       </c>
       <c r="D66">
         <v>971025</v>
       </c>
       <c r="E66" t="s">
+        <v>252</v>
+      </c>
+      <c r="F66" t="s">
         <v>253</v>
       </c>
-      <c r="F66" t="s">
-        <v>254</v>
-      </c>
       <c r="G66" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -5690,7 +5690,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H45 A47:H66 B46:H46" numberStoredAsText="1"/>
+    <ignoredError sqref="A3:G4 A47:H66 B46:H46 A1:G1 A6:H6 A5:G5 A8:H45 A7:G7 A2:G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D935621E-98C6-4BF7-A249-25B26C4543F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D8C712-920B-42F7-A0C8-3778E92A4BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="265">
   <si>
     <t>data__id</t>
   </si>
@@ -798,28 +798,37 @@
     <t>https://cdn.vietqr.io/img/momo.png</t>
   </si>
   <si>
-    <t>TCB_446</t>
-  </si>
-  <si>
     <t>TCB -iPanDa</t>
   </si>
   <si>
     <t>MS00T09548691713297</t>
   </si>
   <si>
-    <t>VIB_064</t>
-  </si>
-  <si>
     <t>064933000</t>
   </si>
   <si>
-    <t>VIB_052</t>
-  </si>
-  <si>
     <t>052004</t>
   </si>
   <si>
     <t>Template</t>
+  </si>
+  <si>
+    <t>TCB_999</t>
+  </si>
+  <si>
+    <t>VIB_000</t>
+  </si>
+  <si>
+    <t>VIB_004</t>
+  </si>
+  <si>
+    <t>Green Cofee</t>
+  </si>
+  <si>
+    <t>MOMO_IPA_HUYNHKIET</t>
+  </si>
+  <si>
+    <t>PMC2605818000000089</t>
   </si>
 </sst>
 </file>
@@ -1248,10 +1257,10 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1286,7 +1295,7 @@
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C3">
         <v>44699999999</v>
@@ -1324,10 +1333,10 @@
         <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1362,10 +1371,10 @@
         <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1396,30 +1405,41 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="1"/>
+      <c r="A6">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
       <c r="F6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G6" t="str">
+        <v>momo</v>
+      </c>
+      <c r="G6">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>971025</v>
       </c>
       <c r="H6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
       <c r="I6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/momo.png</v>
       </c>
       <c r="J6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1450,7 +1470,6 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="1"/>
       <c r="E8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4107,7 +4126,7 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D8C712-920B-42F7-A0C8-3778E92A4BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49D9443-2C54-4FA1-9D39-920FCA4B8D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="258">
   <si>
     <t>data__id</t>
   </si>
@@ -798,9 +798,6 @@
     <t>https://cdn.vietqr.io/img/momo.png</t>
   </si>
   <si>
-    <t>TCB -iPanDa</t>
-  </si>
-  <si>
     <t>MS00T09548691713297</t>
   </si>
   <si>
@@ -811,24 +808,6 @@
   </si>
   <si>
     <t>Template</t>
-  </si>
-  <si>
-    <t>TCB_999</t>
-  </si>
-  <si>
-    <t>VIB_000</t>
-  </si>
-  <si>
-    <t>VIB_004</t>
-  </si>
-  <si>
-    <t>Green Cofee</t>
-  </si>
-  <si>
-    <t>MOMO_IPA_HUYNHKIET</t>
-  </si>
-  <si>
-    <t>PMC2605818000000089</t>
   </si>
 </sst>
 </file>
@@ -864,9 +843,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1256,11 +1238,8 @@
       <c r="A2">
         <v>38</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1292,89 +1271,80 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C3">
-        <v>44699999999</v>
+        <v>43</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1031451081</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="F3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>TCB</v>
+        <v>VCB</v>
       </c>
       <c r="G3">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970407</v>
+        <v>970436</v>
       </c>
       <c r="H3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="I3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/TCB.png</v>
+        <v>https://cdn.vietqr.io/img/VCB.png</v>
       </c>
       <c r="J3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
-        <v>260</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>256</v>
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>44699999999</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>VIB</v>
+        <v>Techcombank</v>
       </c>
       <c r="F4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VIB</v>
+        <v>TCB</v>
       </c>
       <c r="G4">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970441</v>
+        <v>970407</v>
       </c>
       <c r="H4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>VIB</v>
+        <v>Techcombank</v>
       </c>
       <c r="I4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/VIB.png</v>
+        <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J4" t="str">
         <f>IFERROR((VLOOKUP(A4,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>VIB</v>
+        <v>Techcombank</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>45</v>
       </c>
-      <c r="B5" t="s">
-        <v>261</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1406,40 +1376,37 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s">
-        <v>262</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>263</v>
+        <v>256</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
       </c>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>MoMo</v>
+        <v>VIB</v>
       </c>
       <c r="F6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>momo</v>
+        <v>VIB</v>
       </c>
       <c r="G6">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>971025</v>
+        <v>970441</v>
       </c>
       <c r="H6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>MoMo</v>
+        <v>VIB</v>
       </c>
       <c r="I6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/momo.png</v>
+        <v>https://cdn.vietqr.io/img/VIB.png</v>
       </c>
       <c r="J6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>MoMo</v>
+        <v>VIB</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1496,7 +1463,6 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="1"/>
       <c r="E9" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1523,7 +1489,6 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="1"/>
       <c r="E10" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1550,7 +1515,6 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="1"/>
       <c r="E11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -4083,7 +4047,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 A3 C3:D3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4126,7 +4090,7 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49D9443-2C54-4FA1-9D39-920FCA4B8D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FEE9E5-B9FB-4420-B3F1-C9A7AA6444A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="262">
   <si>
     <t>data__id</t>
   </si>
@@ -808,6 +808,18 @@
   </si>
   <si>
     <t>Template</t>
+  </si>
+  <si>
+    <t>iPA</t>
+  </si>
+  <si>
+    <t>Tech - 999</t>
+  </si>
+  <si>
+    <t>VIB - 000</t>
+  </si>
+  <si>
+    <t>VIB - 004</t>
   </si>
 </sst>
 </file>
@@ -1238,6 +1250,9 @@
       <c r="A2">
         <v>38</v>
       </c>
+      <c r="B2" t="s">
+        <v>258</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>254</v>
       </c>
@@ -1273,6 +1288,9 @@
       <c r="A3">
         <v>43</v>
       </c>
+      <c r="B3" t="s">
+        <v>174</v>
+      </c>
       <c r="C3" s="2">
         <v>1031451081</v>
       </c>
@@ -1308,6 +1326,9 @@
       <c r="A4">
         <v>38</v>
       </c>
+      <c r="B4" t="s">
+        <v>259</v>
+      </c>
       <c r="C4">
         <v>44699999999</v>
       </c>
@@ -1343,6 +1364,9 @@
       <c r="A5">
         <v>45</v>
       </c>
+      <c r="B5" t="s">
+        <v>260</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>255</v>
       </c>
@@ -1377,6 +1401,9 @@
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>261</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>256</v>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FEE9E5-B9FB-4420-B3F1-C9A7AA6444A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52107831-0D37-4EF5-ACDF-90811C10E001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4212" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="265">
   <si>
     <t>data__id</t>
   </si>
@@ -820,6 +820,15 @@
   </si>
   <si>
     <t>VIB - 004</t>
+  </si>
+  <si>
+    <t>MoMo_Duy Khoi</t>
+  </si>
+  <si>
+    <t>0865106459</t>
+  </si>
+  <si>
+    <t>Phan Le Duy Khoi</t>
   </si>
 </sst>
 </file>
@@ -1437,30 +1446,41 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="1"/>
+      <c r="A7">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D7" t="s">
+        <v>264</v>
+      </c>
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
       <c r="F7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G7" t="str">
+        <v>momo</v>
+      </c>
+      <c r="G7">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>971025</v>
       </c>
       <c r="H7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
       <c r="I7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/momo.png</v>
       </c>
       <c r="J7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52107831-0D37-4EF5-ACDF-90811C10E001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F883C38-5559-4C49-A2BC-FC3F05961830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4212" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="267">
   <si>
     <t>data__id</t>
   </si>
@@ -829,6 +829,12 @@
   </si>
   <si>
     <t>Phan Le Duy Khoi</t>
+  </si>
+  <si>
+    <t>Viettel Money</t>
+  </si>
+  <si>
+    <t>9704229201938100000</t>
   </si>
 </sst>
 </file>
@@ -864,12 +870,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1262,7 +1270,7 @@
       <c r="B2" t="s">
         <v>258</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>254</v>
       </c>
       <c r="D2" t="s">
@@ -1300,7 +1308,7 @@
       <c r="B3" t="s">
         <v>174</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>1031451081</v>
       </c>
       <c r="D3" t="s">
@@ -1338,7 +1346,7 @@
       <c r="B4" t="s">
         <v>259</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>44699999999</v>
       </c>
       <c r="D4" t="s">
@@ -1376,7 +1384,7 @@
       <c r="B5" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>255</v>
       </c>
       <c r="D5" t="s">
@@ -1414,7 +1422,7 @@
       <c r="B6" t="s">
         <v>261</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>256</v>
       </c>
       <c r="D6" t="s">
@@ -1446,70 +1454,72 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>65</v>
-      </c>
-      <c r="B7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D7" t="s">
-        <v>264</v>
-      </c>
+      <c r="C7" s="2"/>
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>MoMo</v>
+        <v>-</v>
       </c>
       <c r="F7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>momo</v>
-      </c>
-      <c r="G7">
+        <v>-</v>
+      </c>
+      <c r="G7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>971025</v>
+        <v>-</v>
       </c>
       <c r="H7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>MoMo</v>
+        <v>-</v>
       </c>
       <c r="I7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/momo.png</v>
+        <v>-</v>
       </c>
       <c r="J7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>MoMo</v>
+        <v>-</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
       <c r="E8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
       <c r="F8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G8" t="str">
+        <v>MB</v>
+      </c>
+      <c r="G8">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970422</v>
       </c>
       <c r="H8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
       <c r="I8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/MB.png</v>
       </c>
       <c r="J8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="4"/>
       <c r="E9" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1536,6 +1546,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="4"/>
       <c r="E10" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1562,29 +1573,41 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11" t="s">
+        <v>264</v>
+      </c>
       <c r="E11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
       <c r="F11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G11" t="str">
+        <v>momo</v>
+      </c>
+      <c r="G11">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>971025</v>
       </c>
       <c r="H11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
       <c r="I11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/momo.png</v>
       </c>
       <c r="J11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>MoMo</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -4093,6 +4116,7 @@
     <hyperlink ref="I100" r:id="rId99" display="https://cdn.vietqr.io/img/ABB.png" xr:uid="{E5F2760B-3918-4B77-B8F8-66F3A483A2D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId100"/>
   <ignoredErrors>
     <ignoredError sqref="A1:J1" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F883C38-5559-4C49-A2BC-FC3F05961830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD7049D-1382-4735-9700-F3F7653A6AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -822,12 +822,6 @@
     <t>VIB - 004</t>
   </si>
   <si>
-    <t>MoMo_Duy Khoi</t>
-  </si>
-  <si>
-    <t>0865106459</t>
-  </si>
-  <si>
     <t>Phan Le Duy Khoi</t>
   </si>
   <si>
@@ -835,6 +829,12 @@
   </si>
   <si>
     <t>9704229201938100000</t>
+  </si>
+  <si>
+    <t>PhanLe Duy Khoi</t>
+  </si>
+  <si>
+    <t>105878043349</t>
   </si>
 </sst>
 </file>
@@ -1485,10 +1485,10 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1574,40 +1574,40 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" t="s">
         <v>262</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D11" t="s">
-        <v>264</v>
       </c>
       <c r="E11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>MoMo</v>
+        <v>VietinBank</v>
       </c>
       <c r="F11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>momo</v>
+        <v>ICB</v>
       </c>
       <c r="G11">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>971025</v>
+        <v>970415</v>
       </c>
       <c r="H11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>MoMo</v>
+        <v>VietinBank</v>
       </c>
       <c r="I11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/momo.png</v>
+        <v>https://cdn.vietqr.io/img/ICB.png</v>
       </c>
       <c r="J11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>MoMo</v>
+        <v>VietinBank</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD7049D-1382-4735-9700-F3F7653A6AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BB683F-D84C-459D-8199-9B7D90EC88AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -828,13 +828,13 @@
     <t>Viettel Money</t>
   </si>
   <si>
-    <t>9704229201938100000</t>
-  </si>
-  <si>
     <t>PhanLe Duy Khoi</t>
   </si>
   <si>
     <t>105878043349</t>
+  </si>
+  <si>
+    <t>9704229201938102578</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1488,7 @@
         <v>263</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1577,10 +1577,10 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="D11" t="s">
         <v>262</v>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BB683F-D84C-459D-8199-9B7D90EC88AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4212" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BB683F-D84C-459D-8199-9B7D90EC88AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186906BF-6532-4C7F-AF43-290339F87D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4212" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="266">
   <si>
     <t>data__id</t>
   </si>
@@ -811,9 +811,6 @@
   </si>
   <si>
     <t>iPA</t>
-  </si>
-  <si>
-    <t>Tech - 999</t>
   </si>
   <si>
     <t>VIB - 000</t>
@@ -1344,7 +1341,7 @@
         <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>154</v>
       </c>
       <c r="C4" s="4">
         <v>44699999999</v>
@@ -1382,7 +1379,7 @@
         <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>255</v>
@@ -1420,7 +1417,7 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>256</v>
@@ -1485,10 +1482,10 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1577,13 +1574,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="D11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,5,0)),"-")</f>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186906BF-6532-4C7F-AF43-290339F87D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B82EC7D-4B6B-4E98-B9AA-C1EFD92B197A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1262,78 +1262,78 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>254</v>
+        <v>174</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1031451081</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="F2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>TCB</v>
+        <v>VCB</v>
       </c>
       <c r="G2">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970407</v>
+        <v>970436</v>
       </c>
       <c r="H2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="I2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/TCB.png</v>
+        <v>https://cdn.vietqr.io/img/VCB.png</v>
       </c>
       <c r="J2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1031451081</v>
+        <v>258</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="F3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VCB</v>
+        <v>TCB</v>
       </c>
       <c r="G3">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970436</v>
+        <v>970407</v>
       </c>
       <c r="H3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="I3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/VCB.png</v>
+        <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -1662,7 +1662,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="1"/>
+      <c r="C14" s="2"/>
       <c r="E14" t="str">
         <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B82EC7D-4B6B-4E98-B9AA-C1EFD92B197A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EAA429-3870-4A33-A511-88817FC8686A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="264">
   <si>
     <t>data__id</t>
   </si>
@@ -804,21 +804,12 @@
     <t>064933000</t>
   </si>
   <si>
-    <t>052004</t>
-  </si>
-  <si>
     <t>Template</t>
   </si>
   <si>
     <t>iPA</t>
   </si>
   <si>
-    <t>VIB - 000</t>
-  </si>
-  <si>
-    <t>VIB - 004</t>
-  </si>
-  <si>
     <t>Phan Le Duy Khoi</t>
   </si>
   <si>
@@ -832,6 +823,9 @@
   </si>
   <si>
     <t>9704229201938102578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIB </t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1297,7 @@
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>254</v>
@@ -1379,7 +1373,7 @@
         <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>255</v>
@@ -1413,41 +1407,30 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
+      <c r="C6" s="2"/>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>VIB</v>
+        <v>-</v>
       </c>
       <c r="F6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VIB</v>
-      </c>
-      <c r="G6">
+        <v>-</v>
+      </c>
+      <c r="G6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970441</v>
+        <v>-</v>
       </c>
       <c r="H6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>VIB</v>
+        <v>-</v>
       </c>
       <c r="I6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/VIB.png</v>
+        <v>-</v>
       </c>
       <c r="J6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>VIB</v>
+        <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1482,10 +1465,10 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1574,13 +1557,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,5,0)),"-")</f>
@@ -4158,7 +4141,7 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EAA429-3870-4A33-A511-88817FC8686A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3062DFE-E2CA-4369-8DD0-4DA128D69F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1256,78 +1256,78 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1031451081</v>
+        <v>257</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="F2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VCB</v>
+        <v>TCB</v>
       </c>
       <c r="G2">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970436</v>
+        <v>970407</v>
       </c>
       <c r="H2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="I2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/VCB.png</v>
+        <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>254</v>
+        <v>174</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1031451081</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="F3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>TCB</v>
+        <v>VCB</v>
       </c>
       <c r="G3">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970407</v>
+        <v>970436</v>
       </c>
       <c r="H3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="I3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/TCB.png</v>
+        <v>https://cdn.vietqr.io/img/VCB.png</v>
       </c>
       <c r="J3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -1407,7 +1407,6 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="2"/>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3062DFE-E2CA-4369-8DD0-4DA128D69F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E94DA6-4919-42FF-9612-EC0E2F67A0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5604" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -1407,94 +1407,105 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
       <c r="E6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
       <c r="F6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G6" t="str">
+        <v>MB</v>
+      </c>
+      <c r="G6">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970422</v>
       </c>
       <c r="H6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
       <c r="I6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/MB.png</v>
       </c>
       <c r="J6" t="str">
         <f>IFERROR((VLOOKUP(A6,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="2"/>
+      <c r="A7">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" t="s">
+        <v>258</v>
+      </c>
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>VietinBank</v>
       </c>
       <c r="F7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G7" t="str">
+        <v>ICB</v>
+      </c>
+      <c r="G7">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970415</v>
       </c>
       <c r="H7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>VietinBank</v>
       </c>
       <c r="I7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/ICB.png</v>
       </c>
       <c r="J7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>VietinBank</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>259</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
       <c r="E8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>MBBank</v>
+        <v>-</v>
       </c>
       <c r="F8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>MB</v>
-      </c>
-      <c r="G8">
+        <v>-</v>
+      </c>
+      <c r="G8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970422</v>
+        <v>-</v>
       </c>
       <c r="H8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>MBBank</v>
+        <v>-</v>
       </c>
       <c r="I8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/MB.png</v>
+        <v>-</v>
       </c>
       <c r="J8" t="str">
         <f>IFERROR((VLOOKUP(A8,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>MBBank</v>
+        <v>-</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1552,41 +1563,29 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D11" t="s">
-        <v>258</v>
-      </c>
       <c r="E11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>VietinBank</v>
+        <v>-</v>
       </c>
       <c r="F11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>ICB</v>
-      </c>
-      <c r="G11">
+        <v>-</v>
+      </c>
+      <c r="G11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970415</v>
+        <v>-</v>
       </c>
       <c r="H11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>VietinBank</v>
+        <v>-</v>
       </c>
       <c r="I11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/ICB.png</v>
+        <v>-</v>
       </c>
       <c r="J11" t="str">
         <f>IFERROR((VLOOKUP(A11,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>VietinBank</v>
+        <v>-</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E94DA6-4919-42FF-9612-EC0E2F67A0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B0E465-2343-43EA-9282-60164ACDA807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5604" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List_bank" sheetId="1" r:id="rId1"/>
@@ -1256,78 +1256,78 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>254</v>
+        <v>174</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1031451081</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="F2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>TCB</v>
+        <v>VCB</v>
       </c>
       <c r="G2">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970407</v>
+        <v>970436</v>
       </c>
       <c r="H2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="I2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/TCB.png</v>
+        <v>https://cdn.vietqr.io/img/VCB.png</v>
       </c>
       <c r="J2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1031451081</v>
+        <v>257</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="F3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VCB</v>
+        <v>TCB</v>
       </c>
       <c r="G3">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970436</v>
+        <v>970407</v>
       </c>
       <c r="H3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="I3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/VCB.png</v>
+        <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B0E465-2343-43EA-9282-60164ACDA807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6DAEA9-F5CA-41F7-87D2-20EE9D09F91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="266">
   <si>
     <t>data__id</t>
   </si>
@@ -826,6 +826,12 @@
   </si>
   <si>
     <t xml:space="preserve">VIB </t>
+  </si>
+  <si>
+    <t>1031451081</t>
+  </si>
+  <si>
+    <t>44699999999</t>
   </si>
 </sst>
 </file>
@@ -861,9 +867,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1212,7 +1217,8 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.69921875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.69921875" bestFit="1" customWidth="1"/>
@@ -1229,7 +1235,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1261,8 +1267,8 @@
       <c r="B2" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="3">
-        <v>1031451081</v>
+      <c r="C2" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1299,7 +1305,7 @@
       <c r="B3" t="s">
         <v>257</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D3" t="s">
@@ -1337,8 +1343,8 @@
       <c r="B4" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="4">
-        <v>44699999999</v>
+      <c r="C4" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1375,7 +1381,7 @@
       <c r="B5" t="s">
         <v>263</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D5" t="s">
@@ -1413,7 +1419,7 @@
       <c r="B6" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>262</v>
       </c>
       <c r="D6" t="s">
@@ -1445,41 +1451,29 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>260</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D7" t="s">
-        <v>258</v>
-      </c>
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>VietinBank</v>
+        <v>-</v>
       </c>
       <c r="F7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>ICB</v>
-      </c>
-      <c r="G7">
+        <v>-</v>
+      </c>
+      <c r="G7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970415</v>
+        <v>-</v>
       </c>
       <c r="H7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>VietinBank</v>
+        <v>-</v>
       </c>
       <c r="I7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/ICB.png</v>
+        <v>-</v>
       </c>
       <c r="J7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>VietinBank</v>
+        <v>-</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1509,7 +1503,6 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="4"/>
       <c r="E9" t="str">
         <f>IFERROR((VLOOKUP(A9,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1536,7 +1529,6 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="4"/>
       <c r="E10" t="str">
         <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1643,7 +1635,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="2"/>
+      <c r="C14" s="1"/>
       <c r="E14" t="str">
         <f>IFERROR((VLOOKUP(A14,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
@@ -1723,7 +1715,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C17" s="1"/>
       <c r="E17" t="str">
         <f>IFERROR((VLOOKUP(A17,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1750,34 +1742,45 @@
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="1"/>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>260</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" t="s">
+        <v>258</v>
+      </c>
       <c r="E18" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>VietinBank</v>
       </c>
       <c r="F18" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G18" t="str">
+        <v>ICB</v>
+      </c>
+      <c r="G18">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970415</v>
       </c>
       <c r="H18" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>VietinBank</v>
       </c>
       <c r="I18" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/ICB.png</v>
       </c>
       <c r="J18" t="str">
         <f>IFERROR((VLOOKUP(A18,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+        <v>VietinBank</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C19" s="1"/>
       <c r="E19" t="str">
         <f>IFERROR((VLOOKUP(A19,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1804,7 +1807,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
       <c r="E20" t="str">
         <f>IFERROR((VLOOKUP(A20,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1831,7 +1834,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
       <c r="E21" t="str">
         <f>IFERROR((VLOOKUP(A21,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1858,7 +1861,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C22" s="1"/>
       <c r="E22" t="str">
         <f>IFERROR((VLOOKUP(A22,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1885,7 +1888,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C23" s="1"/>
       <c r="E23" t="str">
         <f>IFERROR((VLOOKUP(A23,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1912,7 +1915,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C24" s="1"/>
       <c r="E24" t="str">
         <f>IFERROR((VLOOKUP(A24,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1939,7 +1942,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C25" s="1"/>
       <c r="E25" t="str">
         <f>IFERROR((VLOOKUP(A25,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1966,7 +1969,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C26" s="1"/>
       <c r="E26" t="str">
         <f>IFERROR((VLOOKUP(A26,'API - io'!$A:$H,5,0)),"-")</f>
@@ -1993,7 +1996,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C27" s="1"/>
       <c r="E27" t="str">
         <f>IFERROR((VLOOKUP(A27,'API - io'!$A:$H,5,0)),"-")</f>
@@ -2020,7 +2023,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C28" s="1"/>
       <c r="E28" t="str">
         <f>IFERROR((VLOOKUP(A28,'API - io'!$A:$H,5,0)),"-")</f>
@@ -2047,7 +2050,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C29" s="1"/>
       <c r="E29" t="str">
         <f>IFERROR((VLOOKUP(A29,'API - io'!$A:$H,5,0)),"-")</f>
@@ -2074,7 +2077,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C30" s="1"/>
       <c r="E30" t="str">
         <f>IFERROR((VLOOKUP(A30,'API - io'!$A:$H,5,0)),"-")</f>
@@ -2101,7 +2104,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="E31" t="str">
         <f>IFERROR((VLOOKUP(A31,'API - io'!$A:$H,5,0)),"-")</f>
@@ -2128,7 +2131,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="E32" t="str">
         <f>IFERROR((VLOOKUP(A32,'API - io'!$A:$H,5,0)),"-")</f>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6DAEA9-F5CA-41F7-87D2-20EE9D09F91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AA82C3-646F-40DD-8C78-4E25EE577BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1262,78 +1262,78 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="F2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>VCB</v>
+        <v>TCB</v>
       </c>
       <c r="G2">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970436</v>
+        <v>970407</v>
       </c>
       <c r="H2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
       <c r="I2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/VCB.png</v>
+        <v>https://cdn.vietqr.io/img/TCB.png</v>
       </c>
       <c r="J2" t="str">
         <f>IFERROR((VLOOKUP(A2,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Vietcombank</v>
+        <v>Techcombank</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>254</v>
+        <v>174</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="F3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>TCB</v>
+        <v>VCB</v>
       </c>
       <c r="G3">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>970407</v>
+        <v>970436</v>
       </c>
       <c r="H3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
       <c r="I3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>https://cdn.vietqr.io/img/TCB.png</v>
+        <v>https://cdn.vietqr.io/img/VCB.png</v>
       </c>
       <c r="J3" t="str">
         <f>IFERROR((VLOOKUP(A3,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>Techcombank</v>
+        <v>Vietcombank</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -1530,27 +1530,27 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E10" t="str">
-        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$H,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="F10" t="str">
-        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$H,3,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$H,3,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="G10" t="str">
-        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,4,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$G,4,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="H10" t="str">
-        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,5,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$G,5,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="I10" t="str">
-        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,6,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$G,6,0)),"-")</f>
         <v>-</v>
       </c>
       <c r="J10" t="str">
-        <f>IFERROR((VLOOKUP(A10,'API - io'!$A:$G,7,0)),"-")</f>
+        <f>IFERROR((VLOOKUP(#REF!,'API - io'!$A:$G,7,0)),"-")</f>
         <v>-</v>
       </c>
     </row>

--- a/VietQR.xlsx
+++ b/VietQR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\qr_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AA82C3-646F-40DD-8C78-4E25EE577BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409DD4F2-259F-47BD-89A6-E821E30E87D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="267">
   <si>
     <t>data__id</t>
   </si>
@@ -832,6 +832,9 @@
   </si>
   <si>
     <t>44699999999</t>
+  </si>
+  <si>
+    <t>4610052004</t>
   </si>
 </sst>
 </file>
@@ -1451,29 +1454,41 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
       <c r="E7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,5,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
       <c r="F7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$H,3,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G7" t="str">
+        <v>MB</v>
+      </c>
+      <c r="G7">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,4,0)),"-")</f>
-        <v>-</v>
+        <v>970422</v>
       </c>
       <c r="H7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,5,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
       <c r="I7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,6,0)),"-")</f>
-        <v>-</v>
+        <v>https://cdn.vietqr.io/img/MB.png</v>
       </c>
       <c r="J7" t="str">
         <f>IFERROR((VLOOKUP(A7,'API - io'!$A:$G,7,0)),"-")</f>
-        <v>-</v>
+        <v>MBBank</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
